--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J889"/>
+  <dimension ref="A1:J899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>歌名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>歌名翻译</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>原唱</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>语言</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>歌切</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
@@ -539,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/17，2025/09/02，2025/09/07，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11</t>
+          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/02，2025/09/07，2025/09/17，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -583,7 +571,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05</t>
+          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -594,7 +582,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -631,7 +619,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/25，2025/03/28，2025/04/17，2025/05/03，2025/05/09，2025/05/16，2025/05/30，2025/06/14，2025/06/19，2025/07/05，2025/07/18，2025/08/21，2025/08/25，2025/09/05，2025/09/22，2025/09/26，2026/01/19，2026/01/21，2026/03/04，2026/04/16，2026/06/06，2026/06/18，2026/06/23</t>
+          <t>2025/03/02，2025/03/25，2025/03/28，2025/04/17，2025/05/03，2025/05/09，2025/05/16，2025/05/30，2025/06/14，2025/06/19，2025/07/05，2025/07/18，2025/08/21，2025/08/25，2025/09/05，2025/09/22，2025/09/26，2026/01/19，2026/01/21，2026/03/04，2026/04/16，2026/06/06，2026/06/18，2026/06/23，2026/08/25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -642,7 +630,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -675,7 +663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08</t>
+          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/8/28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -686,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -839,7 +827,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09，2026/07/31</t>
+          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09，2026/07/31，2026/08/25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -850,7 +838,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -963,7 +951,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27</t>
+          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -974,7 +962,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1003,7 +991,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/8/28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1014,7 +1002,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1283,7 +1271,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/8/28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1294,7 +1282,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1323,7 +1311,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09</t>
+          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1334,7 +1322,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1363,7 +1351,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15</t>
+          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/8/28，2026/8/28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1374,7 +1362,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1443,7 +1431,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/8/16</t>
+          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/08/16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1523,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31</t>
+          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31，2026/08/25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1534,7 +1522,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1563,7 +1551,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31</t>
+          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/8/28</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1574,7 +1562,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1643,7 +1631,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/12，2025/09/17，2025/09/02，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27</t>
+          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1654,7 +1642,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1683,7 +1671,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11</t>
+          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1694,7 +1682,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2255,7 +2243,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2266,7 +2254,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2635,7 +2623,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/05/04，2025/05/18，2025/06/09，2025/08/04，2025/08/16，2025/09/18，2025/10/17，2025/11/21，2025/11/28，2026/05/10</t>
+          <t>2025/03/07，2025/03/28，2025/05/04，2025/05/18，2025/06/09，2025/08/04，2025/08/16，2025/09/18，2025/10/17，2025/11/21，2025/11/28，2026/05/10，2026/8/27</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2646,7 +2634,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2755,7 +2743,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25</t>
+          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25，2026/08/25</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2766,7 +2754,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2883,7 +2871,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27</t>
+          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27，2026/08/18</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2894,7 +2882,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2923,7 +2911,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/04，2025/04/12，2025/04/18，2025/04/24，2025/06/17，2025/06/19，2025/07/11，2025/07/18，2025/08/28，2025/09/05，2025/09/08，2025/09/27，2025/10/03，2025/12/11，2025/12/30，2026/01/21，2026/01/25，2026/02/10，2026/02/23，2026/03/06，2026/03/22，2026/04/24</t>
+          <t>2025/03/07，2025/04/04，2025/04/12，2025/04/18，2025/04/24，2025/06/17，2025/06/19，2025/07/11，2025/07/18，2025/08/28，2025/09/05，2025/09/08，2025/09/27，2025/10/03，2025/12/11，2025/12/30，2026/01/21，2026/01/25，2026/02/10，2026/02/23，2026/03/06，2026/03/22，2026/04/24，2026/08/19</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -2934,7 +2922,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2963,7 +2951,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/8/28</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2974,7 +2962,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3091,7 +3079,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18</t>
+          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18，2026/08/21，2026/8/28</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -3102,7 +3090,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3171,7 +3159,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27</t>
+          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/8/28</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3182,7 +3170,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3211,7 +3199,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10</t>
+          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10，2026/8/28</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3222,7 +3210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3339,7 +3327,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07</t>
+          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3350,7 +3338,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3503,7 +3491,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08</t>
+          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3514,7 +3502,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3631,7 +3619,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/05/05，2025/05/13，2025/05/24，2025/08/12，2025/08/30，2025/11/26</t>
+          <t>2025/03/10，2025/05/05，2025/05/13，2025/05/24，2025/08/12，2025/08/30，2025/11/26，2026/08/21</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3642,7 +3630,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3671,7 +3659,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/05/03，2025/06/19，2026/01/19，2026/06/23</t>
+          <t>2025/03/12，2025/05/03，2025/06/19，2026/01/19，2026/06/23，2026/08/21</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -3682,7 +3670,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3875,7 +3863,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19，2026/08/05，2026/08/05</t>
+          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19，2026/08/05，2026/08/05，2026/08/19</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -3886,7 +3874,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3967,7 +3955,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/19，2025/08/16，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09</t>
+          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/16，2025/08/19，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -4287,7 +4275,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22</t>
+          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22，2026/8/28</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -4298,7 +4286,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4407,7 +4395,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4418,7 +4406,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4607,7 +4595,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/14，2025/04/14，2025/05/26，2025/06/02，2025/06/12，2025/06/23，2025/07/06，2025/07/10，2025/07/25，2025/08/23，2025/09/20，2025/11/09，2026/03/25，2026/04/26，2026/06/15</t>
+          <t>2025/03/14，2025/03/14，2025/04/14，2025/05/26，2025/06/02，2025/06/12，2025/06/23，2025/07/06，2025/07/10，2025/07/25，2025/08/23，2025/09/20，2025/11/09，2026/03/25，2026/04/26，2026/06/15，2026/08/25</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4618,7 +4606,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4767,7 +4755,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26</t>
+          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4778,7 +4766,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5099,7 +5087,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31</t>
+          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31，2026/08/21，2026/8/28</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -5110,7 +5098,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5139,7 +5127,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17</t>
+          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5150,7 +5138,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5219,7 +5207,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31</t>
+          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31，2026/8/27</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -5230,7 +5218,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5259,7 +5247,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23，2026/08/02</t>
+          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23，2026/08/02，2026/8/27</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -5270,7 +5258,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5619,7 +5607,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18</t>
+          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18，2026/08/25，2026/8/28</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -5630,7 +5618,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5659,7 +5647,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/05/12，2025/06/23，2025/09/04，2025/12/23，2026/05/05，2026/07/16</t>
+          <t>2025/03/15，2025/05/12，2025/06/23，2025/09/04，2025/12/23，2026/05/05，2026/07/16，2026/08/25</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -5670,7 +5658,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5699,7 +5687,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23</t>
+          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5710,7 +5698,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5739,7 +5727,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5750,7 +5738,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6059,7 +6047,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/12，2025/09/02，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05</t>
+          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/02，2025/09/12，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6099,7 +6087,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6110,7 +6098,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6139,7 +6127,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08，2026/8/16</t>
+          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08，2026/08/16</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -6259,7 +6247,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/05，2025/04/24，2025/05/12，2025/06/19，2025/07/11，2025/07/31，2025/09/03，2025/09/20，2025/10/17，2025/11/09，2025/11/21，2026/01/15</t>
+          <t>2025/03/19，2025/04/05，2025/04/24，2025/05/12，2025/06/19，2025/07/11，2025/07/31，2025/09/03，2025/09/20，2025/10/17，2025/11/09，2025/11/21，2026/01/15，2026/8/27</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -6270,7 +6258,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6419,7 +6407,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17</t>
+          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -6430,7 +6418,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6499,7 +6487,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11</t>
+          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/8/28，2026/8/28</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -6510,7 +6498,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6539,7 +6527,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20</t>
+          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20，2026/8/28</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -6550,7 +6538,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6579,7 +6567,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/06/03，2026/8/16</t>
+          <t>2025/03/20，2025/06/03，2026/08/16</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -6663,7 +6651,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18</t>
+          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -6674,7 +6662,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6743,7 +6731,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/23，2025/07/21，2025/08/08，2025/09/05，2026/01/29</t>
+          <t>2025/03/20，2025/05/23，2025/07/21，2025/08/08，2025/09/05，2026/01/29，2026/08/25</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -6754,7 +6742,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6823,7 +6811,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/8/28</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6834,7 +6822,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6987,7 +6975,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28，2026/8/16</t>
+          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28，2026/08/16</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -7027,7 +7015,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12</t>
+          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/8/27</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -7038,7 +7026,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7223,7 +7211,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23</t>
+          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23，2026/08/25</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -7234,7 +7222,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7423,7 +7411,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/03/29，2025/04/25，2025/05/30，2025/06/22，2025/07/18，2025/09/03，2025/09/13，2026/04/16</t>
+          <t>2025/03/21，2025/03/29，2025/04/25，2025/05/30，2025/06/22，2025/07/18，2025/09/03，2025/09/13，2026/04/16，2026/08/23</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -7434,7 +7422,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7499,7 +7487,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/09/28</t>
+          <t>2025/03/21，2025/09/28，2026/8/27</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -7510,7 +7498,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -7539,7 +7527,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/8/28</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7550,7 +7538,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7623,7 +7611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7634,7 +7622,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7747,7 +7735,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27</t>
+          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/8/28</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -7758,7 +7746,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7867,7 +7855,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09</t>
+          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -7878,7 +7866,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7907,7 +7895,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08</t>
+          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08，2026/8/28，2026/8/28</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -7918,7 +7906,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8147,7 +8135,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/12，2025/09/11，2025/10/31，2026/01/09，2026/07/05</t>
+          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -8587,7 +8575,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23</t>
+          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -8598,7 +8586,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -8867,7 +8855,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15</t>
+          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15，2026/8/28</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -8878,7 +8866,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -8907,7 +8895,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28</t>
+          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -8918,7 +8906,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9034,12 +9022,12 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Connie Talbot</t>
+          <t>Bruno Mars</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/22，2025/04/28，2025/06/30，2026/03/06</t>
+          <t>2025/03/27，2025/04/22，2025/04/28，2025/06/30，2026/03/06，2026/08/25</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -9050,7 +9038,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -9435,7 +9423,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/03，2025/07/24，2025/09/28，2025/10/31，2025/11/13，2026/01/14</t>
+          <t>2025/03/28，2025/05/03，2025/07/24，2025/09/28，2025/10/31，2025/11/13，2026/01/14，2026/08/18</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -9446,7 +9434,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -9475,7 +9463,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31</t>
+          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/8/28</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -9486,7 +9474,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9671,7 +9659,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/8/16</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9751,7 +9739,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01</t>
+          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01，2026/8/28</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -9762,7 +9750,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9831,7 +9819,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/05/08，2025/05/20，2025/05/26，2025/06/05，2025/06/22，2025/07/10，2025/07/11，2025/07/22，2025/08/07，2025/09/17，2025/09/24，2025/10/23，2025/11/01，2025/11/13，2026/07/16，2026/07/25</t>
+          <t>2025/03/29，2025/05/08，2025/05/20，2025/05/26，2025/06/05，2025/06/22，2025/07/10，2025/07/11，2025/07/22，2025/08/07，2025/09/17，2025/09/24，2025/10/23，2025/11/01，2025/11/13，2026/07/16，2026/07/25，2026/08/25</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -9842,7 +9830,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -9955,7 +9943,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02</t>
+          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/8/28</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -9966,7 +9954,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -9995,7 +9983,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -10006,7 +9994,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10035,7 +10023,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/8/27</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10046,7 +10034,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10163,7 +10151,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/07/13，2025/10/20，2026/8/16</t>
+          <t>2025/03/30，2025/07/13，2025/10/20，2026/08/16</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -10203,7 +10191,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/06/17，2025/09/28，2025/10/20，2025/10/31，2026/01/16，2026/06/14，2026/06/17</t>
+          <t>2025/03/30，2025/06/17，2025/09/28，2025/10/20，2025/10/31，2026/01/16，2026/06/14，2026/06/17，2026/08/21</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -10214,7 +10202,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -10243,7 +10231,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17</t>
+          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17，2026/08/25</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -10254,7 +10242,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -10283,7 +10271,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19</t>
+          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -10294,7 +10282,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -10363,7 +10351,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16</t>
+          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16，2026/8/27</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -10374,7 +10362,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10403,7 +10391,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31</t>
+          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31，2026/8/28</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -10414,7 +10402,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10483,7 +10471,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28</t>
+          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28，2026/8/28</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -10494,7 +10482,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -10559,7 +10547,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07</t>
+          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -10570,7 +10558,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -10639,7 +10627,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20</t>
+          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20，2026/8/27</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -10650,7 +10638,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -10759,7 +10747,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28</t>
+          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28，2026/08/18</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -10770,7 +10758,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -10799,7 +10787,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13</t>
+          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13，2026/08/21</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -10810,7 +10798,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -10839,7 +10827,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20，2026/08/02</t>
+          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20，2026/08/02，2026/08/21</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -10850,7 +10838,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -10879,7 +10867,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/05/10，2025/09/04，2025/09/10，2025/09/28，2025/11/26，2026/01/19，2026/05/10</t>
+          <t>2025/04/01，2025/05/10，2025/09/04，2025/09/10，2025/09/28，2025/11/26，2026/01/19，2026/05/10，2026/08/18</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -10890,7 +10878,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -10919,7 +10907,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16</t>
+          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16，2026/08/23，2026/8/28</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -10930,7 +10918,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -10959,7 +10947,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16</t>
+          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16，2026/8/27，2026/8/27</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -10970,7 +10958,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -10999,7 +10987,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/12，2025/05/26，2025/08/26，2025/08/16，2025/10/05，2026/05/04</t>
+          <t>2025/04/02，2025/05/12，2025/05/26，2025/08/16，2025/08/26，2025/10/05，2026/05/04，2026/08/25</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -11010,7 +10998,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -11039,7 +11027,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/18，2025/05/26，2025/09/21，2025/10/07，2026/01/15</t>
+          <t>2025/04/02，2025/04/18，2025/05/26，2025/09/21，2025/10/07，2026/01/15，2026/08/25</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -11050,7 +11038,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -11239,7 +11227,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/13，2025/05/29，2025/09/04，2025/09/21，2025/10/22，2026/01/01，2026/01/15，2026/05/05，2026/8/16</t>
+          <t>2025/04/02，2025/05/13，2025/05/29，2025/09/04，2025/09/21，2025/10/22，2026/01/01，2026/01/15，2026/05/05，2026/08/16</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -11479,7 +11467,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/8/28</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11490,7 +11478,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11683,7 +11671,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22</t>
+          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/8/28</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11694,7 +11682,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -11723,7 +11711,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/27，2026/8/16</t>
+          <t>2025/04/03，2025/04/27，2026/08/16</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -12195,7 +12183,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/8/16</t>
+          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/08/16</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -12315,7 +12303,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/8/28</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12326,7 +12314,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -12759,7 +12747,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09</t>
+          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -12770,7 +12758,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -12799,7 +12787,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25，2026/08/02</t>
+          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25，2026/08/02，2026/08/21</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -12810,7 +12798,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -12839,7 +12827,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08</t>
+          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -12850,7 +12838,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12879,7 +12867,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/05/08，2025/05/20，2025/05/30，2025/06/16，2025/08/29，2025/09/12，2025/10/09，2025/10/16，2025/11/18，2026/02/04，2026/02/14，2026/04/15，2026/06/13，2026/07/07，2026/07/28</t>
+          <t>2025/04/07，2025/04/17，2025/05/08，2025/05/20，2025/05/30，2025/06/16，2025/08/29，2025/09/12，2025/10/09，2025/10/16，2025/11/18，2026/02/04，2026/02/14，2026/04/15，2026/06/13，2026/07/07，2026/07/28，2026/8/28</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -12890,7 +12878,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -12919,7 +12907,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02</t>
+          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/8/28</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -12930,7 +12918,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -13079,7 +13067,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06，2026/08/07</t>
+          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06，2026/08/07，2026/08/23</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -13090,7 +13078,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -13239,7 +13227,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20</t>
+          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20，2026/8/28</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -13250,7 +13238,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -13315,7 +13303,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/18，2025/06/09，2025/07/07，2025/08/26，2025/09/03，2025/09/13，2025/10/17，2025/10/30，2025/11/21，2025/12/17，2026/04/19</t>
+          <t>2025/04/11，2025/05/18，2025/06/09，2025/07/07，2025/08/26，2025/09/03，2025/09/13，2025/10/17，2025/10/30，2025/11/21，2025/12/17，2026/04/19，2026/8/27</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -13326,7 +13314,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -13399,7 +13387,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18</t>
+          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -13410,7 +13398,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -13475,7 +13463,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/12，2025/09/11，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15，2026/08/02</t>
+          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/11，2025/09/12，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15，2026/08/02</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -13831,7 +13819,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/02，2025/06/12，2025/09/27，2025/11/09，2025/12/19，2026/01/01，2026/02/17，2026/07/09，2026/07/27</t>
+          <t>2025/04/11，2025/06/02，2025/06/12，2025/09/27，2025/11/09，2025/12/19，2026/01/01，2026/02/17，2026/07/09，2026/07/27，2026/08/21</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -13842,7 +13830,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -13911,7 +13899,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2025/04/12，2025/04/28，2025/07/10，2025/09/08，2025/09/07</t>
+          <t>2025/04/12，2025/04/28，2025/07/10，2025/09/07，2025/09/08</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
@@ -13987,7 +13975,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27</t>
+          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/8/28</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -13998,7 +13986,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -14327,7 +14315,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20</t>
+          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20，2026/8/27</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -14338,7 +14326,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -14447,7 +14435,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17</t>
+          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17，2026/08/21</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -14458,7 +14446,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -14775,7 +14763,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/01，2025/05/26，2025/07/03，2025/07/27，2025/09/18，2025/10/17，2025/11/21，2026/01/12，2026/01/24，2026/02/19，2026/02/23，2026/03/24，2026/05/04，2026/07/07</t>
+          <t>2025/04/17，2025/05/01，2025/05/26，2025/07/03，2025/07/27，2025/09/18，2025/10/17，2025/11/21，2026/01/12，2026/01/24，2026/02/19，2026/02/23，2026/03/24，2026/05/04，2026/07/07，2026/08/25</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -14786,7 +14774,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -14895,7 +14883,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/31，2025/06/03，2025/06/14，2025/09/10，2026/03/28</t>
+          <t>2025/04/17，2025/05/31，2025/06/03，2025/06/14，2025/09/10，2026/03/28，2026/8/28</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -14906,7 +14894,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -15255,7 +15243,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25，2026/08/11</t>
+          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25，2026/08/11，2026/08/25</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -15266,7 +15254,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -15663,7 +15651,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/19，2025/07/25，2025/08/07，2025/09/15，2025/09/29，2026/01/05，2026/02/14，2026/04/09，2026/06/20</t>
+          <t>2025/04/21，2025/05/19，2025/07/25，2025/08/07，2025/09/15，2025/09/29，2026/01/05，2026/02/14，2026/04/09，2026/06/20，2026/08/23</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
@@ -15674,7 +15662,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -15855,7 +15843,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/09/22，2026/03/29，2026/06/10</t>
+          <t>2025/04/24，2025/09/22，2026/03/29，2026/06/10，2026/8/28</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -15866,7 +15854,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -16355,7 +16343,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31</t>
+          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31，2026/08/25</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -16366,7 +16354,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -17195,7 +17183,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09，2026/8/16</t>
+          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09，2026/08/16</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -17235,7 +17223,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/07/18，2025/08/02，2025/10/16，2026/05/01</t>
+          <t>2025/05/03，2025/07/18，2025/08/02，2025/10/16，2026/05/01，2026/8/27</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -17246,7 +17234,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -17355,7 +17343,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2025/05/03</t>
+          <t>2025/05/03，2026/8/27</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -17366,7 +17354,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -17555,7 +17543,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23</t>
+          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/8/28</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -17566,7 +17554,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -18191,7 +18179,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03，2026/08/07</t>
+          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03，2026/08/07，2026/08/23</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -18202,7 +18190,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -18231,7 +18219,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10</t>
+          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10，2026/8/28，2026/8/28</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -18242,7 +18230,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -18431,7 +18419,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18442,7 +18430,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -18511,7 +18499,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/12/16，2025/12/24，2026/8/16</t>
+          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -18675,7 +18663,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/31，2025/06/07，2025/06/10，2025/08/02，2025/10/07，2025/12/06，2026/03/22，2026/05/01，2026/8/16</t>
+          <t>2025/05/22，2025/05/31，2025/06/07，2025/06/10，2025/08/02，2025/10/07，2025/12/06，2026/03/22，2026/05/01，2026/08/16</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -18755,7 +18743,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/12，2025/09/02，2025/12/05，2026/04/09，2026/05/10</t>
+          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -19047,7 +19035,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/05/29，2025/09/17，2025/09/02，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07</t>
+          <t>2025/05/23，2025/05/29，2025/09/02，2025/09/17，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07，2026/08/25</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -19058,7 +19046,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -19247,7 +19235,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/8/16</t>
+          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/08/16</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -19447,7 +19435,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16</t>
+          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16，2026/08/23</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -19458,7 +19446,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -19527,7 +19515,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/08/21</t>
+          <t>2025/05/30，2025/08/21，2026/08/18</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -19538,7 +19526,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -19567,7 +19555,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/08/23，2025/10/11，2026/8/16</t>
+          <t>2025/05/30，2025/08/23，2025/10/11，2026/08/16</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -19767,7 +19755,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28，2026/08/03</t>
+          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28，2026/08/03，2026/08/23</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -19778,7 +19766,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -19807,7 +19795,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2025/05/31，2025/06/02，2025/06/23，2025/09/15，2025/09/27，2025/10/17，2026/8/16</t>
+          <t>2025/05/31，2025/06/02，2025/06/23，2025/09/15，2025/09/27，2025/10/17，2026/08/16</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -20611,7 +20599,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/06/07，2025/06/12，2025/06/28，2025/08/13，2025/09/11，2025/09/30，2025/11/27</t>
+          <t>2025/06/02，2025/06/07，2025/06/12，2025/06/28，2025/08/13，2025/09/11，2025/09/30，2025/11/27，2026/8/27</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -20622,7 +20610,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -20651,7 +20639,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/10/20，2025/11/01，2026/03/05，2026/04/14</t>
+          <t>2025/06/02，2025/10/20，2025/11/01，2026/03/05，2026/04/14，2026/08/23</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -20662,7 +20650,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -20887,7 +20875,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>2025/06/07，2025/11/24</t>
+          <t>2025/06/07，2025/11/24，2026/08/18</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -20898,7 +20886,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -21211,7 +21199,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>2025/06/13，2025/07/25，2026/05/05</t>
+          <t>2025/06/13，2025/07/25，2026/05/05，2026/08/25</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -21222,7 +21210,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -21291,7 +21279,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31</t>
+          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31，2026/08/21</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -21302,7 +21290,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -21411,7 +21399,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>2025/06/17，2026/06/26</t>
+          <t>2025/06/17，2026/06/26，2026/08/21</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -21422,7 +21410,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -22175,7 +22163,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/19，2026/01/19，2026/8/16</t>
+          <t>2025/06/23，2025/10/19，2026/01/19，2026/08/16</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -22375,7 +22363,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08</t>
+          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08，2026/08/18</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -22386,7 +22374,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -22419,7 +22407,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17</t>
+          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17，2026/08/25</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -22430,7 +22418,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -22711,7 +22699,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/8/16</t>
+          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -22751,7 +22739,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>2025/06/29，2026/08/11</t>
+          <t>2025/06/29，2026/08/11，2026/08/21</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -22762,7 +22750,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -23423,7 +23411,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09</t>
+          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09，2026/8/28</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -23434,7 +23422,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -23703,7 +23691,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>2025/07/11，2025/07/15，2025/07/15，2025/08/04，2025/09/28，2025/10/05，2026/01/09，2026/03/07，2026/03/08，2026/06/14</t>
+          <t>2025/07/11，2025/07/15，2025/07/15，2025/08/04，2025/09/28，2025/10/05，2026/01/09，2026/03/07，2026/03/08，2026/06/14，2026/8/27</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -23714,7 +23702,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -23903,7 +23891,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26</t>
+          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/8/27</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -23914,7 +23902,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -23983,7 +23971,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28</t>
+          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28，2026/8/28</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -23994,7 +23982,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -24063,7 +24051,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23</t>
+          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23，2026/8/28</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -24074,7 +24062,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -24451,7 +24439,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/17，2025/09/11，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26</t>
+          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/11，2025/09/17，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -24575,7 +24563,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/09/24，2025/10/28，2025/11/12，2025/12/16，2026/01/14，2026/01/30，2026/06/10，2026/07/26</t>
+          <t>2025/07/26，2025/09/24，2025/10/28，2025/11/12，2025/12/16，2026/01/14，2026/01/30，2026/06/10，2026/07/26，2026/08/21</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -24586,7 +24574,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -24735,7 +24723,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22</t>
+          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22，2026/8/27</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -24746,7 +24734,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -25007,7 +24995,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31</t>
+          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31，2026/08/25</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -25018,7 +25006,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -25371,7 +25359,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>2025/08/26，2025/08/16，2025/11/13，2025/12/09，2026/01/29，2026/02/19，2026/03/31</t>
+          <t>2025/08/16，2025/08/26，2025/11/13，2025/12/09，2026/01/29，2026/02/19，2026/03/31</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -26311,7 +26299,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/8/28</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26322,7 +26310,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -26387,7 +26375,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>2025/09/17，2025/09/15，2025/09/22，2025/09/29，2025/09/29，2025/10/10，2025/10/28，2025/12/02，2026/01/05，2026/03/13，2026/06/23</t>
+          <t>2025/09/15，2025/09/17，2025/09/22，2025/09/29，2025/09/29，2025/10/10，2025/10/28，2025/12/02，2026/01/05，2026/03/13，2026/06/23</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -26427,7 +26415,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>2025/09/17，2025/10/11，2025/10/13，2025/10/20，2025/10/25，2025/11/21，2025/12/17，2026/02/23，2026/03/17，2026/03/25，2026/05/23</t>
+          <t>2025/09/17，2025/10/11，2025/10/13，2025/10/20，2025/10/25，2025/11/21，2025/12/17，2026/02/23，2026/03/17，2026/03/25，2026/05/23，2026/8/27</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -26438,7 +26426,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -26895,7 +26883,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26906,7 +26894,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -26975,7 +26963,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/09/22，2026/08/19</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -26986,7 +26974,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -27087,7 +27075,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>2025/09/22，2025/10/09，2025/12/05，2026/8/16</t>
+          <t>2025/09/22，2025/10/09，2025/12/05，2026/08/16</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -27275,7 +27263,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31</t>
+          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -27286,7 +27274,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -27667,7 +27655,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>2025/09/30，2025/10/01，2025/10/11，2025/10/17，2025/10/26，2026/8/16</t>
+          <t>2025/09/30，2025/10/01，2025/10/11，2025/10/17，2025/10/26，2026/08/16</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -28475,7 +28463,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>2025/10/18</t>
+          <t>2025/10/18，2026/08/25</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -28486,7 +28474,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -28591,7 +28579,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>2025/10/23，2026/8/16</t>
+          <t>2025/10/23，2026/08/16，2026/08/21</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -28602,12 +28590,12 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>BV1gabm6ZEH1</t>
+          <t>BV1GHb16oEuk，BV1gabm6ZEH1</t>
         </is>
       </c>
       <c r="J702" t="inlineStr"/>
@@ -28631,7 +28619,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>2025/10/23，2025/10/25，2025/12/12，2026/01/19，2026/03/28</t>
+          <t>2025/10/23，2025/10/25，2025/12/12，2026/01/19，2026/03/28，2026/08/21</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -28642,7 +28630,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -29059,7 +29047,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/8/16</t>
+          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -30411,7 +30399,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/8/16</t>
+          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/08/16</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -30875,7 +30863,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07</t>
+          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/8/28</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -30886,7 +30874,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -30915,7 +30903,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30926,7 +30914,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -30955,7 +30943,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/05，2026/01/19，2026/01/21，2026/01/22，2026/01/24，2026/02/07，2026/02/19，2026/02/24，2026/02/24，2026/02/25，2026/03/06，2026/03/25，2026/04/11，2026/04/20，2026/05/15，2026/06/19，2026/07/18</t>
+          <t>2025/12/26，2026/01/05，2026/01/19，2026/01/21，2026/01/22，2026/01/24，2026/02/07，2026/02/19，2026/02/24，2026/02/24，2026/02/25，2026/03/06，2026/03/25，2026/04/11，2026/04/20，2026/05/15，2026/06/19，2026/07/18，2026/08/21，2026/8/28</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
@@ -30966,7 +30954,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -31039,7 +31027,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01</t>
+          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/8/28</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -31050,7 +31038,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -31463,7 +31451,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07</t>
+          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07，2026/08/23</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
@@ -31474,7 +31462,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -31547,7 +31535,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>2026/01/25</t>
+          <t>2026/01/25，2026/08/19</t>
         </is>
       </c>
       <c r="F778" t="inlineStr"/>
@@ -31558,10 +31546,14 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I778" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>BV18u8n6QEXN</t>
+        </is>
+      </c>
       <c r="J778" t="inlineStr">
         <is>
           <t>游戏</t>
@@ -31907,7 +31899,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31918,7 +31910,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -32075,7 +32067,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19</t>
+          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19，2026/08/25</t>
         </is>
       </c>
       <c r="F791" t="inlineStr"/>
@@ -32086,7 +32078,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -32355,7 +32347,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01</t>
+          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/8/27</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
@@ -32366,7 +32358,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -33379,7 +33371,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08</t>
+          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -33390,7 +33382,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -33475,7 +33467,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07，2026/08/09</t>
+          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07，2026/08/09，2026/08/25</t>
         </is>
       </c>
       <c r="F825" t="inlineStr"/>
@@ -33486,7 +33478,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -34583,7 +34575,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11</t>
+          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11，2026/08/25</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -34594,7 +34586,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -34879,7 +34871,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16</t>
+          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23</t>
         </is>
       </c>
       <c r="F859" t="inlineStr"/>
@@ -34890,7 +34882,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -35327,7 +35319,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>2026/06/20</t>
+          <t>2026/06/20，2026/08/23</t>
         </is>
       </c>
       <c r="F870" t="inlineStr"/>
@@ -35338,7 +35330,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -35451,7 +35443,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>2026/06/25，2026/07/09，2026/07/18，2026/07/31</t>
+          <t>2026/06/25，2026/07/09，2026/07/18，2026/07/31，2026/08/25</t>
         </is>
       </c>
       <c r="F873" t="inlineStr"/>
@@ -35462,7 +35454,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -35615,7 +35607,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11</t>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/8/28</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
@@ -35626,7 +35618,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -35735,7 +35727,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/8/28</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -35746,7 +35738,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -35935,7 +35927,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11</t>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
@@ -35946,7 +35938,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -36015,7 +36007,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>2026/08/05，2025/05/03</t>
+          <t>2025/05/03，2026/08/05</t>
         </is>
       </c>
       <c r="F887" t="inlineStr"/>
@@ -36055,7 +36047,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/08/11</t>
+          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25</t>
         </is>
       </c>
       <c r="F888" t="inlineStr"/>
@@ -36066,10 +36058,14 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I888" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>BV1oBui6sEzT</t>
+        </is>
+      </c>
       <c r="J888" t="inlineStr"/>
     </row>
     <row r="889">
@@ -36105,8 +36101,412 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I889" t="inlineStr"/>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>BV1DQui61EPb</t>
+        </is>
+      </c>
       <c r="J889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>迷宫</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr"/>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>step.jad依加</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>2026/08/18，2026/08/19，2026/08/23</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>BV1UL836dEFE</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>爱你但说不出口</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr"/>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Karencici</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>BV1e1836KEbJ</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>写一首歌April 5,1969</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr"/>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>顺子</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>BV1xw8G6sEvA</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Black Sheep</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr"/>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Gin Wigmore</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>BV1Ps836DEGr</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Get Jinxed</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Agnete Kjolsund</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>BV1t58n6EEBo</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>涅槃</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>英雄联盟/Cailin Russo/Chrissy Costanza</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>2026/08/19，2026/08/21</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr"/>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>BV1zA8B6SEvE</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>才二十三</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr"/>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>方大同</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>2026/08/23，2026/08/25</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>BV1Ko886rE7j</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>入秋的第一场雨真让人矫情</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr"/>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>ChiliChill</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>BV1cs886YEQS</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>芭蕉夜雨</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr"/>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>ChiliChill</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>2026/08/23</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>BV1ns886YEqh</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>summer vibe</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr"/>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Walk off the Earth</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr"/>
+      <c r="J899" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J899"/>
+  <dimension ref="A1:J904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23</t>
+          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23，2026/8/30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/8/30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04</t>
+          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04，2026/8/30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/05/05，2025/05/13，2025/05/24，2025/08/12，2025/08/30，2025/11/26，2026/08/21</t>
+          <t>2025/03/10，2025/05/05，2025/05/13，2025/05/24，2025/08/12，2025/08/30，2025/11/26，2026/08/21，2026/8/30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/17，2025/05/04，2025/05/13，2025/07/22，2025/09/05，2025/09/28，2026/06/03</t>
+          <t>2025/03/13，2025/04/17，2025/05/04，2025/05/13，2025/07/22，2025/09/05，2025/09/28，2026/06/03，2026/8/30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/8/30</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25</t>
+          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/8/30</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/10/11，2025/11/14</t>
+          <t>2025/03/14，2025/10/11，2025/11/14，2026/8/30</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25</t>
+          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/8/30</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28</t>
+          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/8/30</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26，2026/08/02</t>
+          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26，2026/08/02，2026/8/30</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/02，2025/09/12，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05</t>
+          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/02，2025/09/12，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05，2026/8/30</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/8/30</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25</t>
+          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/8/30</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08</t>
+          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08，2026/8/30</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/12，2025/12/07，2026/04/24</t>
+          <t>2025/03/21，2025/05/12，2025/12/07，2026/04/24，2026/8/30</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/24，2025/11/27，2026/04/14，2026/06/10</t>
+          <t>2025/03/25，2025/09/24，2025/11/27，2026/04/14，2026/06/10，2026/8/30</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/09，2025/05/29，2025/07/24，2025/09/04，2025/10/24，2025/11/19，2026/03/25，2026/04/09，2026/05/10，2026/06/10</t>
+          <t>2025/03/27，2025/05/09，2025/05/29，2025/07/24，2025/09/04，2025/10/24，2025/11/19，2026/03/25，2026/04/09，2026/05/10，2026/06/10，2026/8/30</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/23，2025/06/13，2025/06/26，2025/07/11，2025/09/18，2025/11/03，2025/12/23，2025/12/26，2026/01/24，2026/06/03，2026/07/18</t>
+          <t>2025/03/28，2025/05/23，2025/06/13，2025/06/26，2025/07/11，2025/09/18，2025/11/03，2025/12/23，2025/12/26，2026/01/24，2026/06/03，2026/07/18，2026/8/30，2026/8/30</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/8/28</t>
+          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/8/28，2026/8/30</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18</t>
+          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18，2026/8/30</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2025/03/30</t>
+          <t>2025/03/30，2026/8/30</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/27，2025/07/24，2026/01/01，2026/06/14</t>
+          <t>2025/04/02，2025/05/27，2025/07/24，2026/01/01，2026/06/14，2026/8/30</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/13，2025/05/10，2025/05/26，2025/06/02，2025/06/05，2025/06/17，2025/08/04，2025/09/10，2025/09/30，2025/10/16，2025/11/17，2025/12/06，2025/12/31，2026/04/26，2026/07/22</t>
+          <t>2025/04/02，2025/04/13，2025/05/10，2025/05/26，2025/06/02，2025/06/05，2025/06/17，2025/08/04，2025/09/10，2025/09/30，2025/10/16，2025/11/17，2025/12/06，2025/12/31，2026/04/26，2026/07/22，2026/8/30</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/06/20，2025/09/19，2025/10/12，2026/03/09，2026/03/13，2026/03/17，2026/05/01，2026/06/18</t>
+          <t>2025/04/03，2025/06/20，2025/09/19，2025/10/12，2026/03/09，2026/03/13，2026/03/17，2026/05/01，2026/06/18，2026/8/30</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20</t>
+          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20，2026/8/30</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/05/12，2025/05/18，2025/06/20，2025/07/05，2025/07/14，2025/12/23，2026/01/30，2026/04/09</t>
+          <t>2025/04/04，2025/05/12，2025/05/18，2025/06/20，2025/07/05，2025/07/14，2025/12/23，2026/01/30，2026/04/09，2026/8/30</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/08/16</t>
+          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/08/16，2026/8/30</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09</t>
+          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09，2026/8/30</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -12678,7 +12678,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23</t>
+          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/8/30</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2025/04/12</t>
+          <t>2025/04/12，2026/8/30</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01</t>
+          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01，2026/8/30</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/06/17，2025/08/28</t>
+          <t>2025/04/19，2025/06/17，2025/08/28，2026/8/30</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2025/05/01，2025/08/12，2025/08/26，2025/11/24，2026/06/20</t>
+          <t>2025/05/01，2025/08/12，2025/08/26，2025/11/24，2026/06/20，2026/8/30</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25</t>
+          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25，2026/8/30</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -18499,7 +18499,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16</t>
+          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16，2026/8/30</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -18510,7 +18510,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10</t>
+          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10，2026/8/30</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -18754,7 +18754,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2025/05/23</t>
+          <t>2025/05/23，2026/8/30</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -19086,7 +19086,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20</t>
+          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/8/30</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/8/30</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21770,7 +21770,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>2025/06/23</t>
+          <t>2025/06/23，2026/8/30</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -22094,7 +22094,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16</t>
+          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16，2026/8/30</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -22739,7 +22739,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>2025/06/29，2026/08/11，2026/08/21</t>
+          <t>2025/06/29，2026/08/11，2026/08/21，2026/8/30</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -22750,7 +22750,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -22819,7 +22819,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2025/06/29</t>
+          <t>2025/06/29，2026/8/30</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -22830,7 +22830,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>2025/06/29</t>
+          <t>2025/06/29，2026/8/30</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -22870,7 +22870,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/8/28</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/8/28，2026/8/30</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -27263,7 +27263,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19</t>
+          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19，2026/8/30</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -27274,7 +27274,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -34655,7 +34655,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/08/02</t>
+          <t>2026/05/01，2026/08/02，2026/8/30</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -34666,7 +34666,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/08/19，2026/08/23</t>
+          <t>2026/08/18，2026/08/19，2026/08/23，2026/8/30</t>
         </is>
       </c>
       <c r="F890" t="inlineStr"/>
@@ -36138,7 +36138,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>summer vibe</t>
+          <t>Summer Vibe</t>
         </is>
       </c>
       <c r="C899" t="inlineStr"/>
@@ -36505,8 +36505,212 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I899" t="inlineStr"/>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>BV1mY496eEud</t>
+        </is>
+      </c>
       <c r="J899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>All About That Bass</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr"/>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Meghan Trainor</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>2026/8/30</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>BV1y4th6AEz2</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Last Friday Night</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr"/>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Katy Perry</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>2026/8/30</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>BV12Hth6iEup</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Tik Tok</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr"/>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Kesha</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>2026/8/30，2026/8/30</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>BV1w8th6wERB</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Honeymoon Avenue</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr"/>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Ariana Grande</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>2026/8/30</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>BV1k8th6cEpk</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Love Me Like You Do</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr"/>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Ellie Goulding</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>2026/8/30</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>BV12wta6uEUK</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J904"/>
+  <dimension ref="A1:J905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,7 +703,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09</t>
+          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09，2026/9/2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08</t>
+          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08，2026/9/2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01</t>
+          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01，2026/9/2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/05/03，2025/05/08，2025/06/05，2025/06/19，2025/07/15，2025/09/08，2025/10/07，2025/10/17，2025/10/23，2025/12/24</t>
+          <t>2025/03/04，2025/04/18，2025/05/03，2025/05/08，2025/06/05，2025/06/19，2025/07/15，2025/09/08，2025/10/07，2025/10/17，2025/10/23，2025/12/24，2026/9/2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17</t>
+          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17，2026/9/2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26</t>
+          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26，2026/9/2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/8/28</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/8/28，2026/9/2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20，2026/07/30</t>
+          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20，2026/07/30，2026/9/2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16</t>
+          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/9/2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23，2026/07/31</t>
+          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23，2026/07/31，2026/9/2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02</t>
+          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02，2026/9/2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11</t>
+          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/9/2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/08，2025/04/18，2025/05/12，2025/05/23，2025/06/27，2025/07/24，2025/08/28，2025/10/11，2025/10/31，2025/11/24，2025/12/19，2026/02/02，2026/04/19，2026/07/25</t>
+          <t>2025/03/19，2025/04/08，2025/04/18，2025/05/12，2025/05/23，2025/06/27，2025/07/24，2025/08/28，2025/10/11，2025/10/31，2025/11/24，2025/12/19，2026/02/02，2026/04/19，2026/07/25，2026/9/2</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27</t>
+          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/9/2</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/9/2</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/9/2</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27</t>
+          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/9/2</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/06/02，2025/06/29，2025/07/24，2025/07/26，2025/08/21，2025/11/09，2025/12/16</t>
+          <t>2025/04/04，2025/06/02，2025/06/29，2025/07/24，2025/07/26，2025/08/21，2025/11/09，2025/12/16，2026/9/2</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27</t>
+          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/9/2</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/21，2025/04/22，2025/04/25，2025/04/26，2025/04/29，2025/05/08，2025/05/12，2025/05/22，2025/05/30，2025/06/06，2025/06/08，2025/06/28，2025/07/13，2025/08/12，2025/08/24，2025/09/07，2025/09/30，2025/10/05，2025/11/21，2025/12/17，2026/01/14，2026/01/23，2026/02/12，2026/03/31，2026/06/18，2026/07/17</t>
+          <t>2025/04/13，2025/04/21，2025/04/22，2025/04/25，2025/04/26，2025/04/29，2025/05/08，2025/05/12，2025/05/22，2025/05/30，2025/06/06，2025/06/08，2025/06/28，2025/07/13，2025/08/12，2025/08/24，2025/09/07，2025/09/30，2025/10/05，2025/11/21，2025/12/17，2026/01/14，2026/01/23，2026/02/12，2026/03/31，2026/06/18，2026/07/17，2026/9/2</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16</t>
+          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16，2026/9/2</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06</t>
+          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/9/2</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27</t>
+          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27，2026/9/2</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07</t>
+          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/9/2</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -17830,7 +17830,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31</t>
+          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/9/2</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>2025/05/26，2025/07/03，2025/09/15</t>
+          <t>2025/05/26，2025/07/03，2025/09/15，2026/9/2</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>2025/06/17，2025/09/24</t>
+          <t>2025/06/17，2025/09/24，2026/9/2</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/23，2026/07/09</t>
+          <t>2025/06/23，2025/10/23，2026/07/09，2026/9/2</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -22054,7 +22054,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/09/19，2025/11/22，2026/07/22</t>
+          <t>2025/06/29，2025/09/19，2025/11/22，2026/07/22，2026/9/2</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06</t>
+          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06，2026/9/2</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -23186,7 +23186,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>2025/10/13，2025/10/18，2026/03/15，2026/08/09</t>
+          <t>2025/10/13，2025/10/18，2026/03/15，2026/08/09，2026/9/2</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -28230,7 +28230,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16</t>
+          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16，2026/9/2</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -29058,7 +29058,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25</t>
+          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/9/2</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -29482,7 +29482,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -30047,7 +30047,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07</t>
+          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07，2026/9/2</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -30058,7 +30058,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -30087,7 +30087,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/11/28，2026/9/2</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -30098,10 +30098,14 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I741" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>BV1Q6to6JEEx</t>
+        </is>
+      </c>
       <c r="J741" t="inlineStr"/>
     </row>
     <row r="742">
@@ -30903,7 +30907,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/9/2</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30914,7 +30918,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -31939,7 +31943,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02</t>
+          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02，2026/9/2</t>
         </is>
       </c>
       <c r="F788" t="inlineStr"/>
@@ -31950,7 +31954,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -34235,7 +34239,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25</t>
+          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25，2026/9/2</t>
         </is>
       </c>
       <c r="F844" t="inlineStr"/>
@@ -34246,7 +34250,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -35666,7 +35670,11 @@
           <t>BV1Xx3P6cEfK</t>
         </is>
       </c>
-      <c r="J878" t="inlineStr"/>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -35767,7 +35775,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03</t>
+          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/9/2</t>
         </is>
       </c>
       <c r="F881" t="inlineStr"/>
@@ -35778,7 +35786,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -35786,7 +35794,11 @@
           <t>BV19x3P6cENj</t>
         </is>
       </c>
-      <c r="J881" t="inlineStr"/>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>动漫</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -36411,7 +36423,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>2026/08/23</t>
+          <t>2026/08/23，2026/9/2</t>
         </is>
       </c>
       <c r="F897" t="inlineStr"/>
@@ -36422,7 +36434,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -36531,7 +36543,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>2026/8/30</t>
+          <t>2026/8/30，2026/9/2</t>
         </is>
       </c>
       <c r="F900" t="inlineStr"/>
@@ -36542,7 +36554,7 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -36711,6 +36723,46 @@
         </is>
       </c>
       <c r="J904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>California King Bed</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr"/>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Rihanna</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>2026/9/2</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>BV15eto6sEMB</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J905"/>
+  <dimension ref="A1:J906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/8/28</t>
+          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/8/28，2026/9/4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/8/28</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/8/28，2026/9/4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/9/4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21</t>
+          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21，2026/9/4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/16，2025/08/19，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09</t>
+          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/16，2025/08/19，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09，2026/9/4</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/8/30</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/8/30，2026/9/4</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22</t>
+          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22，2026/9/4</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19</t>
+          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19，2026/9/4</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22</t>
+          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/9/4</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/8/30</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/8/30，2026/9/4</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09</t>
+          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09，2026/9/4</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/9/4</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10</t>
+          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10，2026/9/4</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27</t>
+          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27，2026/9/4</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05</t>
+          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05，2026/9/4</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/9/4</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09</t>
+          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09，2026/9/4</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/9/4</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09</t>
+          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09，2026/9/4</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -10525,7 +10525,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>BV12Wth6NEcs</t>
+        </is>
+      </c>
       <c r="J249" t="inlineStr"/>
     </row>
     <row r="250">
@@ -10547,7 +10551,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18</t>
+          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18，2026/9/4</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -10558,7 +10562,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -11427,7 +11431,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/03，2025/04/08，2025/05/26，2025/07/18，2025/08/16，2025/09/30，2025/11/26，2026/01/23，2026/02/18，2026/03/12，2026/06/10</t>
+          <t>2025/04/02，2025/04/03，2025/04/08，2025/05/26，2025/07/18，2025/08/16，2025/09/30，2025/11/26，2026/01/23，2026/02/18，2026/03/12，2026/06/10，2026/9/4</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -11438,7 +11442,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -11791,7 +11795,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03</t>
+          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03，2026/9/4</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -11802,7 +11806,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12667,7 +12671,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09，2026/8/30</t>
+          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09，2026/8/30，2026/9/4</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -12678,7 +12682,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -13859,7 +13863,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2025/04/12，2025/07/14，2025/09/24，2025/09/28，2025/11/09，2026/04/24</t>
+          <t>2025/04/12，2025/07/14，2025/09/24，2025/09/28，2025/11/09，2026/04/24，2026/9/4</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -13870,7 +13874,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -13939,7 +13943,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2025/04/12，2026/8/30</t>
+          <t>2025/04/12，2026/8/30，2026/9/4</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -13950,10 +13954,14 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>BV1xbtW6UEw8</t>
+        </is>
+      </c>
       <c r="J335" t="inlineStr"/>
     </row>
     <row r="336">
@@ -13975,7 +13983,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/8/28</t>
+          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/8/28，2026/9/4</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -13986,7 +13994,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -14151,7 +14159,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23</t>
+          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/9/4</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -14162,7 +14170,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -15611,7 +15619,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/9/2</t>
+          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/9/2，2026/9/4</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -15622,7 +15630,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -16827,7 +16835,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14，2026/08/02</t>
+          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14，2026/08/02，2026/9/4</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -16838,7 +16846,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -17543,7 +17551,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/8/28</t>
+          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/8/28，2026/9/4</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -17554,7 +17562,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -18419,7 +18427,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/9/4</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18430,7 +18438,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -22699,7 +22707,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16，2026/8/30</t>
+          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16，2026/8/30，2026/9/4</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -22710,7 +22718,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -25115,7 +25123,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13，2026/08/07</t>
+          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13，2026/08/07，2026/9/4</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -25126,7 +25134,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -26883,7 +26891,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/9/4</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26894,7 +26902,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -27499,7 +27507,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>2025/09/28</t>
+          <t>2025/09/28，2026/9/4</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -27510,10 +27518,14 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I675" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>BV1Datr6zEvQ</t>
+        </is>
+      </c>
       <c r="J675" t="inlineStr"/>
     </row>
     <row r="676">
@@ -28579,7 +28591,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>2025/10/23，2026/08/16，2026/08/21</t>
+          <t>2025/10/23，2026/08/16，2026/08/21，2026/9/4</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -28590,7 +28602,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -30831,7 +30843,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2025/12/19，2026/9/4</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -30842,10 +30854,14 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I760" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>BV1getr6uEAQ</t>
+        </is>
+      </c>
       <c r="J760" t="inlineStr"/>
     </row>
     <row r="761">
@@ -31623,7 +31639,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>2026/01/25，2026/01/30，2026/02/02，2026/02/08，2026/02/19，2026/02/23，2026/02/25，2026/03/12，2026/03/28，2026/04/12，2026/04/20，2026/06/26，2026/07/22</t>
+          <t>2026/01/25，2026/01/30，2026/02/02，2026/02/08，2026/02/19，2026/02/23，2026/02/25，2026/03/12，2026/03/28，2026/04/12，2026/04/20，2026/06/26，2026/07/22，2026/9/4</t>
         </is>
       </c>
       <c r="F780" t="inlineStr"/>
@@ -31634,7 +31650,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -34919,7 +34935,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02</t>
+          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02，2026/9/4</t>
         </is>
       </c>
       <c r="F860" t="inlineStr"/>
@@ -34930,7 +34946,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -35119,7 +35135,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27</t>
+          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/9/4</t>
         </is>
       </c>
       <c r="F865" t="inlineStr"/>
@@ -35130,7 +35146,7 @@
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
@@ -36763,6 +36779,46 @@
         </is>
       </c>
       <c r="J905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>willow</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Taylor Swift</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>2026/9/4</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>BV1Setr6MEBW</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J906"/>
+  <dimension ref="A1:J909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/02，2025/09/07，2025/09/17，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11</t>
+          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/02，2025/09/07，2025/09/17，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11，2026/09/12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/8/28，2026/9/4</t>
+          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/08/28，2026/09/04，2026/09/13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09，2026/9/2</t>
+          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09，2026/09/02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08，2026/9/2</t>
+          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08，2026/09/02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/04/29，2026/06/25</t>
+          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/04/29，2026/06/25，2026/09/12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31</t>
+          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31，2026/09/11，2026/09/13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18</t>
+          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18，2026/09/06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/8/28，2026/9/4</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17</t>
+          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17，2026/09/06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/03，2025/04/17，2025/05/22，2025/06/03，2025/07/24，2025/08/12，2025/09/03，2025/10/10，2025/11/09，2025/11/10，2026/03/13，2026/06/03</t>
+          <t>2025/03/04，2025/04/03，2025/04/17，2025/05/22，2025/06/03，2025/07/24，2025/08/12，2025/09/03，2025/10/10，2025/11/09，2025/11/10，2026/03/13，2026/06/03，2026/09/08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/9/4</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/29，2025/05/20，2025/07/13，2025/07/25，2025/07/31，2025/10/09，2025/12/02，2026/01/09，2026/03/21，2026/07/19</t>
+          <t>2025/03/04，2025/04/29，2025/05/20，2025/07/13，2025/07/25，2025/07/31，2025/10/09，2025/12/02，2026/01/09，2026/03/21，2026/07/19，2026/09/13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/8/28</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/8/28，2026/8/28</t>
+          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/08/28，2026/08/28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/8/28</t>
+          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/08/28，2026/09/06</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21，2026/9/4</t>
+          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21，2026/09/04，2026/09/06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01，2026/9/2</t>
+          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01，2026/09/02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23，2026/8/30</t>
+          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23，2026/08/30，2026/08/30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/05/03，2025/05/08，2025/06/05，2025/06/19，2025/07/15，2025/09/08，2025/10/07，2025/10/17，2025/10/23，2025/12/24，2026/9/2</t>
+          <t>2025/03/04，2025/04/18，2025/05/03，2025/05/08，2025/06/05，2025/06/19，2025/07/15，2025/09/08，2025/10/07，2025/10/17，2025/10/23，2025/12/24，2026/09/02，2026/09/12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17，2026/9/2</t>
+          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17，2026/09/02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26，2026/9/2</t>
+          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26，2026/09/02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/21，2025/04/19，2025/05/11，2025/06/03，2026/01/19，2026/01/25，2026/02/25，2026/04/01，2026/07/27</t>
+          <t>2025/03/06，2025/03/21，2025/04/19，2025/05/11，2025/06/03，2026/01/19，2026/01/25，2026/02/25，2026/04/01，2026/07/27，2026/09/08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/03，2025/04/14，2025/05/05，2025/05/15，2025/05/29，2025/06/20，2025/06/27，2025/08/07，2025/08/24，2025/09/17，2025/10/16，2025/11/10，2025/12/09，2025/12/17，2026/01/21，2026/02/12，2026/02/25，2026/07/27</t>
+          <t>2025/03/06，2025/04/03，2025/04/14，2025/05/05，2025/05/15，2025/05/29，2025/06/20，2025/06/27，2025/08/07，2025/08/24，2025/09/17，2025/10/16，2025/11/10，2025/12/09，2025/12/17，2026/01/21，2026/02/12，2026/02/25，2026/07/27，2026/09/08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19，2026/09/05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/17，2025/05/18，2025/05/30，2025/06/06，2025/06/21，2025/06/27，2025/07/24，2025/08/24，2025/09/10，2025/09/30，2025/10/23，2025/11/10，2026/01/15，2026/02/14，2026/03/22，2026/05/20</t>
+          <t>2025/03/06，2025/04/17，2025/05/18，2025/05/30，2025/06/06，2025/06/21，2025/06/27，2025/07/24，2025/08/24，2025/09/10，2025/09/30，2025/10/23，2025/11/10，2026/01/15，2026/02/14，2026/03/22，2026/05/20，2026/09/13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/27，2025/04/07，2025/04/12，2025/04/22，2025/04/26，2025/05/05，2025/05/19，2025/06/03，2025/06/09，2025/07/18，2025/07/22，2025/09/10，2025/09/19，2025/10/16，2025/12/24，2026/06/20</t>
+          <t>2025/03/07，2025/03/27，2025/04/07，2025/04/12，2025/04/22，2025/04/26，2025/05/05，2025/05/19，2025/06/03，2025/06/09，2025/07/18，2025/07/22，2025/09/10，2025/09/19，2025/10/16，2025/12/24，2026/06/20，2026/08/27</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/05/04，2025/05/18，2025/06/09，2025/08/04，2025/08/16，2025/09/18，2025/10/17，2025/11/21，2025/11/28，2026/05/10，2026/8/27</t>
+          <t>2025/03/07，2025/03/28，2025/05/04，2025/05/18，2025/06/09，2025/08/04，2025/08/16，2025/09/18，2025/10/17，2025/11/21，2025/11/28，2026/05/10，2026/08/27</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/8/30</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25，2026/08/25</t>
+          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25，2026/08/25，2026/09/06</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07</t>
+          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07，2026/09/11</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/8/28，2026/9/2</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/08/28，2026/09/02，2026/09/11</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28</t>
+          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28，2026/09/06</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18，2026/08/21，2026/8/28</t>
+          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18，2026/08/21，2026/08/28</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04，2026/8/30</t>
+          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04，2026/08/30</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/8/28</t>
+          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10，2026/8/28</t>
+          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10，2026/08/28，2026/09/08</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/11，2025/05/20，2025/06/16，2025/06/24，2025/08/29，2025/09/12，2025/10/12，2026/01/09，2026/05/20</t>
+          <t>2025/03/09，2025/04/04，2025/04/11，2025/05/20，2025/06/16，2025/06/24，2025/08/29，2025/09/12，2025/10/12，2026/01/09，2026/05/20，2026/09/13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25</t>
+          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25，2026/09/08</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20，2026/07/30，2026/9/2</t>
+          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20，2026/07/30，2026/09/02，2026/09/13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/9/2</t>
+          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/09/02</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23，2026/07/31，2026/9/2</t>
+          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23，2026/07/31，2026/09/02</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26</t>
+          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26，2026/09/04</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/05/05，2025/05/13，2025/05/24，2025/08/12，2025/08/30，2025/11/26，2026/08/21，2026/8/30</t>
+          <t>2025/03/10，2025/05/05，2025/05/13，2025/05/24，2025/08/12，2025/08/30，2025/11/26，2026/08/21，2026/08/30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02，2026/9/2</t>
+          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02，2026/09/02</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/9/2</t>
+          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/09/02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/16，2025/08/19，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09，2026/9/4</t>
+          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/16，2025/08/19，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09，2026/09/04，2026/09/06</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/03，2025/05/26，2025/06/01，2025/06/06，2025/09/08，2025/09/12，2026/04/09，2026/06/20，2026/07/22</t>
+          <t>2025/03/13，2025/04/03，2025/05/26，2025/06/01，2025/06/06，2025/09/08，2025/09/12，2026/04/09，2026/06/20，2026/07/22，2026/09/13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/30，2025/04/17，2025/04/21，2025/05/05，2025/05/13，2025/05/20，2025/06/06，2025/06/20，2025/06/27，2025/07/05，2025/07/31，2025/08/24，2025/08/29，2025/09/20，2025/09/30，2025/10/22，2025/11/26，2026/01/15，2026/02/14，2026/04/08，2026/05/20</t>
+          <t>2025/03/13，2025/03/30，2025/04/17，2025/04/21，2025/05/05，2025/05/13，2025/05/20，2025/06/06，2025/06/20，2025/06/27，2025/07/05，2025/07/31，2025/08/24，2025/08/29，2025/09/20，2025/09/30，2025/10/22，2025/11/26，2026/01/15，2026/02/14，2026/04/08，2026/05/20，2026/09/13</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/21，2025/05/15，2025/07/28，2025/09/10，2026/01/14，2026/06/28</t>
+          <t>2025/03/13，2025/04/21，2025/05/15，2025/07/28，2025/09/10，2026/01/14，2026/06/28，2026/09/13</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/17，2025/05/04，2025/05/13，2025/07/22，2025/09/05，2025/09/28，2026/06/03，2026/8/30</t>
+          <t>2025/03/13，2025/04/17，2025/05/04，2025/05/13，2025/07/22，2025/09/05，2025/09/28，2026/06/03，2026/08/30</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22，2026/8/28</t>
+          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22，2026/08/28</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/8/30，2026/9/4</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/08/30，2026/09/04</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/05/12，2025/05/22，2025/06/16，2025/06/30，2025/08/01，2025/08/16，2025/09/19，2025/10/05，2025/11/18，2025/12/23，2026/01/09，2026/02/27，2026/04/29，2026/07/05，2026/07/22</t>
+          <t>2025/03/13，2025/05/12，2025/05/22，2025/06/16，2025/06/30，2025/08/01，2025/08/16，2025/09/19，2025/10/05，2025/11/18，2025/12/23，2026/01/09，2026/02/27，2026/04/29，2026/07/05，2026/07/22，2026/09/06</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/19，2025/05/20，2025/07/26，2025/08/16，2025/12/11，2026/04/09，2026/04/18，2026/07/22</t>
+          <t>2025/03/14，2025/05/19，2025/05/20，2025/07/26，2025/08/16，2025/12/11，2026/04/09，2026/04/18，2026/07/22，2026/09/08</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/05/15，2025/06/07，2025/07/18，2025/09/12，2025/11/09，2025/11/22，2026/03/09，2026/04/14，2026/05/20</t>
+          <t>2025/03/14，2025/03/28，2025/05/15，2025/06/07，2025/07/18，2025/09/12，2025/11/09，2025/11/22，2026/03/09，2026/04/14，2026/05/20，2026/09/13</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22，2026/9/4</t>
+          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22，2026/09/04</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/8/30</t>
+          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/08/30</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/10/11，2025/11/14，2026/8/30</t>
+          <t>2025/03/14，2025/10/11，2025/11/14，2026/08/30</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31，2026/08/21，2026/8/28</t>
+          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31，2026/08/21，2026/08/28，2026/08/30，2026/09/11</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/8/30</t>
+          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/08/30，2026/09/11</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19，2026/9/4</t>
+          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19，2026/09/04</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31，2026/8/27</t>
+          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31，2026/08/27</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23，2026/08/02，2026/8/27</t>
+          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23，2026/08/02，2026/08/27，2026/09/06</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/05，2025/05/15，2025/08/12，2026/03/28</t>
+          <t>2025/03/15，2025/04/05，2025/05/15，2025/08/12，2026/03/28，2026/09/06</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/8/30</t>
+          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/08/30</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18，2026/08/25，2026/8/28</t>
+          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18，2026/08/25，2026/08/28，2026/09/06</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/9/4</t>
+          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/09/04，2026/09/08</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26，2026/08/02，2026/8/30</t>
+          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26，2026/08/02，2026/08/30</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/02，2025/09/12，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05，2026/8/30</t>
+          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/02，2025/09/12，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05，2026/08/30</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/8/30，2026/9/4</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/07/07，2025/08/12，2025/08/26，2025/09/13，2025/09/17，2025/10/10，2025/11/21，2025/12/11，2026/01/02，2026/01/15，2026/01/28，2026/02/19，2026/03/05，2026/04/09，2026/06/06，2026/06/20，2026/07/31，2026/07/31</t>
+          <t>2025/03/19，2025/07/07，2025/08/12，2025/08/26，2025/09/13，2025/09/17，2025/10/10，2025/11/21，2025/12/11，2026/01/02，2026/01/15，2026/01/28，2026/02/19，2026/03/05，2026/04/09，2026/06/06，2026/06/20，2026/07/31，2026/07/31，2026/09/11</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/05，2025/04/24，2025/05/12，2025/06/19，2025/07/11，2025/07/31，2025/09/03，2025/09/20，2025/10/17，2025/11/09，2025/11/21，2026/01/15，2026/8/27</t>
+          <t>2025/03/19，2025/04/05，2025/04/24，2025/05/12，2025/06/19，2025/07/11，2025/07/31，2025/09/03，2025/09/20，2025/10/17，2025/11/09，2025/11/21，2026/01/15，2026/08/27</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09，2026/9/4</t>
+          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09，2026/09/04</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/08，2025/04/18，2025/05/12，2025/05/23，2025/06/27，2025/07/24，2025/08/28，2025/10/11，2025/10/31，2025/11/24，2025/12/19，2026/02/02，2026/04/19，2026/07/25，2026/9/2</t>
+          <t>2025/03/19，2025/04/08，2025/04/18，2025/05/12，2025/05/23，2025/06/27，2025/07/24，2025/08/28，2025/10/11，2025/10/31，2025/11/24，2025/12/19，2026/02/02，2026/04/19，2026/07/25，2026/09/02</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25</t>
+          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25，2026/09/06</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/05/18，2025/06/13，2025/09/12，2025/10/01，2026/04/20，2026/06/10</t>
+          <t>2025/03/19，2025/04/07，2025/05/18，2025/06/13，2025/09/12，2025/10/01，2026/04/20，2026/06/10，2026/09/11</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/8/28，2026/8/28</t>
+          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/08/28，2026/08/28</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20，2026/8/28</t>
+          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20，2026/08/28</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/8/30</t>
+          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/08/30</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/8/28</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/13，2025/05/30，2025/06/06，2025/07/08，2025/08/07，2025/08/22，2025/09/30，2025/11/09，2025/11/13，2025/12/31，2026/04/16，2026/06/20</t>
+          <t>2025/03/20，2025/04/17，2025/05/13，2025/05/30，2025/06/06，2025/07/08，2025/08/07，2025/08/22，2025/09/30，2025/11/09，2025/11/13，2025/12/31，2026/04/16，2026/06/20，2026/09/08</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/8/27</t>
+          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08，2026/8/30</t>
+          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08，2026/08/30，2026/09/06</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/12，2025/12/07，2026/04/24，2026/8/30</t>
+          <t>2025/03/21，2025/05/12，2025/12/07，2026/04/24，2026/08/30</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/9/2</t>
+          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/09/02，2026/09/08</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7482,18 +7482,18 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>TWICE</t>
+          <t>Lenka</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/09/28，2026/8/27</t>
+          <t>2025/03/21，2025/09/28，2026/08/27</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/8/28</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/9/4</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/09/04</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/8/28</t>
+          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/07，2025/04/18，2025/05/08，2025/10/24，2025/12/12，2026/04/26</t>
+          <t>2025/03/21，2025/04/07，2025/04/18，2025/05/08，2025/10/24，2025/12/12，2026/04/26，2026/09/06</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08，2026/8/28，2026/8/28</t>
+          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08，2026/08/28，2026/08/28</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10，2026/9/4</t>
+          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10，2026/09/04</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/01，2025/05/12，2025/05/31，2025/07/11，2025/08/16，2025/09/19，2025/09/24，2025/11/18，2026/01/09，2026/02/14</t>
+          <t>2025/03/23，2025/04/01，2025/05/12，2025/05/31，2025/07/11，2025/08/16，2025/09/19，2025/09/24，2025/11/18，2026/01/09，2026/02/14，2026/09/08</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27，2026/9/4</t>
+          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27，2026/09/04，2026/09/13</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/17，2025/05/25，2025/12/02，2026/01/14，2026/06/06</t>
+          <t>2025/03/23，2025/04/17，2025/05/25，2025/12/02，2026/01/14，2026/06/06，2026/09/08</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05，2026/9/4</t>
+          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05，2026/09/04，2026/09/11</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/9/4</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/07/24，2025/07/29，2025/07/31，2025/09/04，2025/09/24，2025/10/03，2025/10/16，2025/11/18，2025/11/21，2026/03/05，2026/06/06</t>
+          <t>2025/03/25，2025/07/24，2025/07/29，2025/07/31，2025/09/04，2025/09/24，2025/10/03，2025/10/16，2025/11/18，2025/11/21，2026/03/05，2026/06/06，2026/09/11</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/24，2025/11/27，2026/04/14，2026/06/10，2026/8/30</t>
+          <t>2025/03/25，2025/09/24，2025/11/27，2026/04/14，2026/06/10，2026/08/30</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09，2026/9/4</t>
+          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09，2026/09/04</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15，2026/8/28</t>
+          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15，2026/08/28</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18</t>
+          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18，2026/09/08</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/15，2025/05/08，2025/06/10，2025/07/07，2025/08/04，2025/09/04，2025/10/01，2025/11/26，2026/01/10，2026/03/22，2026/06/20，2026/07/20</t>
+          <t>2025/03/27，2025/04/15，2025/05/08，2025/06/10，2025/07/07，2025/08/04，2025/09/04，2025/10/01，2025/11/26，2026/01/10，2026/03/22，2026/06/20，2026/07/20，2026/09/11</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/09，2025/05/29，2025/07/24，2025/09/04，2025/10/24，2025/11/19，2026/03/25，2026/04/09，2026/05/10，2026/06/10，2026/8/30</t>
+          <t>2025/03/27，2025/05/09，2025/05/29，2025/07/24，2025/09/04，2025/10/24，2025/11/19，2026/03/25，2026/04/09，2026/05/10，2026/06/10，2026/08/30</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12，2026/08/07</t>
+          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12，2026/08/07，2026/09/11</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/9/2</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/23，2025/06/13，2025/06/26，2025/07/11，2025/09/18，2025/11/03，2025/12/23，2025/12/26，2026/01/24，2026/06/03，2026/07/18，2026/8/30，2026/8/30</t>
+          <t>2025/03/28，2025/05/23，2025/06/13，2025/06/26，2025/07/11，2025/09/18，2025/11/03，2025/12/23，2025/12/26，2026/01/24，2026/06/03，2026/07/18，2026/08/30，2026/08/30</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/8/28</t>
+          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/08/28</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/9/2</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01，2026/8/28</t>
+          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01，2026/08/28</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/8/28，2026/8/30</t>
+          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/08/28，2026/08/30</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/9/4</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/09/04</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/8/27</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18，2026/8/30</t>
+          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18，2026/08/30</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16，2026/8/27</t>
+          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16，2026/08/27</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31，2026/8/28</t>
+          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31，2026/08/28</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09，2026/9/4</t>
+          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09，2026/09/04</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28，2026/8/28</t>
+          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28，2026/08/28</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2025/03/30，2026/8/30</t>
+          <t>2025/03/30，2026/08/30</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18，2026/9/4</t>
+          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18，2026/09/04</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20，2026/8/27</t>
+          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20，2026/08/27</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28，2026/08/18</t>
+          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28，2026/08/18，2026/09/08</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13，2026/08/21</t>
+          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13，2026/08/21，2026/09/12</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/05/10，2025/09/04，2025/09/10，2025/09/28，2025/11/26，2026/01/19，2026/05/10，2026/08/18</t>
+          <t>2025/04/01，2025/05/10，2025/09/04，2025/09/10，2025/09/28，2025/11/26，2026/01/19，2026/05/10，2026/08/18，2026/09/06</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16，2026/08/23，2026/8/28</t>
+          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16，2026/08/23，2026/08/28，2026/09/11</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16，2026/8/27，2026/8/27</t>
+          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16，2026/08/27，2026/09/11</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/21，2025/05/19，2025/06/02，2025/07/03，2025/09/19，2025/10/16</t>
+          <t>2025/04/02，2025/04/21，2025/05/19，2025/06/02，2025/07/03，2025/09/19，2025/10/16，2026/09/13</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/27，2025/07/24，2026/01/01，2026/06/14，2026/8/30</t>
+          <t>2025/04/02，2025/05/27，2025/07/24，2026/01/01，2026/06/14，2026/08/30，2026/09/08</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/9/2</t>
+          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/09/02</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/13，2025/05/10，2025/05/26，2025/06/02，2025/06/05，2025/06/17，2025/08/04，2025/09/10，2025/09/30，2025/10/16，2025/11/17，2025/12/06，2025/12/31，2026/04/26，2026/07/22，2026/8/30</t>
+          <t>2025/04/02，2025/04/13，2025/05/10，2025/05/26，2025/06/02，2025/06/05，2025/06/17，2025/08/04，2025/09/10，2025/09/30，2025/10/16，2025/11/17，2025/12/06，2025/12/31，2026/04/26，2026/07/22，2026/08/30</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/03，2025/04/08，2025/05/26，2025/07/18，2025/08/16，2025/09/30，2025/11/26，2026/01/23，2026/02/18，2026/03/12，2026/06/10，2026/9/4</t>
+          <t>2025/04/02，2025/04/03，2025/04/08，2025/05/26，2025/07/18，2025/08/16，2025/09/30，2025/11/26，2026/01/23，2026/02/18，2026/03/12，2026/06/10，2026/09/04</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/8/28</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/06/20，2025/09/19，2025/10/12，2026/03/09，2026/03/13，2026/03/17，2026/05/01，2026/06/18，2026/8/30</t>
+          <t>2025/04/03，2025/06/20，2025/09/19，2025/10/12，2026/03/09，2026/03/13，2026/03/17，2026/05/01，2026/06/18，2026/08/30</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/05/17，2025/05/29，2025/06/16，2025/07/10，2025/08/24，2025/10/16，2025/11/26，2026/04/26</t>
+          <t>2025/04/03，2025/05/17，2025/05/29，2025/06/16，2025/07/10，2025/08/24，2025/10/16，2025/11/26，2026/04/26，2026/09/11</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20，2026/8/30</t>
+          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20，2026/08/30</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/8/28</t>
+          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03，2026/9/4</t>
+          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03，2026/09/04</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/05/12，2025/05/18，2025/06/20，2025/07/05，2025/07/14，2025/12/23，2026/01/30，2026/04/09，2026/8/30</t>
+          <t>2025/04/04，2025/05/12，2025/05/18，2025/06/20，2025/07/05，2025/07/14，2025/12/23，2026/01/30，2026/04/09，2026/08/30</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/06/02，2025/06/29，2025/07/24，2025/07/26，2025/08/21，2025/11/09，2025/12/16，2026/9/2</t>
+          <t>2025/04/04，2025/06/02，2025/06/29，2025/07/24，2025/07/26，2025/08/21，2025/11/09，2025/12/16，2026/09/02</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2025/04/04，2026/01/29</t>
+          <t>2025/04/04，2026/01/29，2026/09/08</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/08/16，2026/8/30</t>
+          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/08/16，2026/08/30</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/8/28</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/10，2025/06/20，2025/12/23，2026/04/09</t>
+          <t>2025/04/06，2025/04/10，2025/06/20，2025/12/23，2026/04/09，2026/09/08</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -12398,7 +12398,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/05/23，2025/06/10，2025/10/03，2025/11/01</t>
+          <t>2025/04/06，2025/05/23，2025/06/10，2025/10/03，2025/11/01，2026/09/08</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09，2026/8/30，2026/9/4</t>
+          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09，2026/08/30，2026/09/04</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/8/30</t>
+          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/08/30，2026/09/11</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25</t>
+          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25，2026/09/06</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/05/08，2025/05/20，2025/05/30，2025/06/16，2025/08/29，2025/09/12，2025/10/09，2025/10/16，2025/11/18，2026/02/04，2026/02/14，2026/04/15，2026/06/13，2026/07/07，2026/07/28，2026/8/28</t>
+          <t>2025/04/07，2025/04/17，2025/05/08，2025/05/20，2025/05/30，2025/06/16，2025/08/29，2025/09/12，2025/10/09，2025/10/16，2025/11/18，2026/02/04，2026/02/14，2026/04/15，2026/06/13，2026/07/07，2026/07/28，2026/08/28，2026/08/28，2026/09/13</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/8/28</t>
+          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/08/28，2026/09/11</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/9/2</t>
+          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/09/02</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20，2026/8/28</t>
+          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20，2026/08/28</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/18，2025/06/09，2025/07/07，2025/08/26，2025/09/03，2025/09/13，2025/10/17，2025/10/30，2025/11/21，2025/12/17，2026/04/19，2026/8/27</t>
+          <t>2025/04/11，2025/05/18，2025/06/09，2025/07/07，2025/08/26，2025/09/03，2025/09/13，2025/10/17，2025/10/30，2025/11/21，2025/12/17，2026/04/19，2026/08/27</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25</t>
+          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25，2026/08/30</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2025/04/12，2025/07/14，2025/09/24，2025/09/28，2025/11/09，2026/04/24，2026/9/4</t>
+          <t>2025/04/12，2025/07/14，2025/09/24，2025/09/28，2025/11/09，2026/04/24，2026/09/04</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -13943,7 +13943,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2025/04/12，2026/8/30，2026/9/4</t>
+          <t>2025/04/12，2026/08/30，2026/09/04</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/8/28，2026/9/4</t>
+          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/08/28，2026/09/04</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/21，2025/04/22，2025/04/25，2025/04/26，2025/04/29，2025/05/08，2025/05/12，2025/05/22，2025/05/30，2025/06/06，2025/06/08，2025/06/28，2025/07/13，2025/08/12，2025/08/24，2025/09/07，2025/09/30，2025/10/05，2025/11/21，2025/12/17，2026/01/14，2026/01/23，2026/02/12，2026/03/31，2026/06/18，2026/07/17，2026/9/2</t>
+          <t>2025/04/13，2025/04/21，2025/04/22，2025/04/25，2025/04/26，2025/04/29，2025/05/08，2025/05/12，2025/05/22，2025/05/30，2025/06/06，2025/06/08，2025/06/28，2025/07/13，2025/08/12，2025/08/24，2025/09/07，2025/09/30，2025/10/05，2025/11/21，2025/12/17，2026/01/14，2026/01/23，2026/02/12，2026/03/31，2026/06/18，2026/07/17，2026/09/02，2026/09/08</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01，2026/8/30</t>
+          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01，2026/08/30</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/9/4</t>
+          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/09/04</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20，2026/8/27</t>
+          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20，2026/08/27</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16，2026/9/2</t>
+          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16，2026/09/02</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -14443,7 +14443,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17，2026/08/21</t>
+          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17，2026/08/21，2026/09/11</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/06/01，2025/08/18，2026/03/06，2026/03/17</t>
+          <t>2025/04/17，2025/06/01，2025/08/18，2026/03/06，2026/03/17，2026/09/13</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/31，2025/06/03，2025/06/14，2025/09/10，2026/03/28，2026/8/28</t>
+          <t>2025/04/17，2025/05/31，2025/06/03，2025/06/14，2025/09/10，2026/03/28，2026/08/28</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/06/17，2025/08/28，2026/8/30</t>
+          <t>2025/04/19，2025/06/17，2025/08/28，2026/08/30</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27</t>
+          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/9/2，2026/9/4</t>
+          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/09/02，2026/09/04</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -15699,7 +15699,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2025/04/22，2025/04/29，2025/05/03，2025/05/03，2025/06/03，2025/09/02，2025/10/10，2025/10/20，2025/10/31，2026/02/07，2026/03/13，2026/08/11</t>
+          <t>2025/04/22，2025/04/29，2025/05/03，2025/05/03，2025/06/03，2025/09/02，2025/10/10，2025/10/20，2025/10/31，2026/02/07，2026/03/13，2026/08/11，2026/09/06</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/09/22，2026/03/29，2026/06/10，2026/8/28</t>
+          <t>2025/04/24，2025/09/22，2026/03/29，2026/06/10，2026/08/28</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/05/15，2025/09/12，2025/09/30，2025/10/16，2025/11/13</t>
+          <t>2025/04/25，2025/05/15，2025/09/12，2025/09/30，2025/10/16，2025/11/13，2026/09/13</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/07/23，2025/09/19，2026/07/22</t>
+          <t>2025/04/25，2025/07/23，2025/09/19，2026/07/22，2026/09/13</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -16442,7 +16442,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/04，2025/05/26，2025/06/08，2025/08/28，2025/10/18，2025/11/18，2025/12/24，2026/01/29，2026/02/27，2026/04/09，2026/04/20</t>
+          <t>2025/04/27，2025/05/04，2025/05/26，2025/06/08，2025/08/28，2025/10/18，2025/11/18，2025/12/24，2026/01/29，2026/02/27，2026/04/09，2026/04/20，2026/09/06</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14，2026/08/02，2026/9/4</t>
+          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14，2026/08/02，2026/09/04</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27，2026/9/2</t>
+          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27，2026/09/02</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2025/04/29，2025/05/03，2026/04/20</t>
+          <t>2025/04/29，2025/05/03，2026/04/20，2026/09/11</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2025/05/01，2025/08/12，2025/08/26，2025/11/24，2026/06/20，2026/8/30</t>
+          <t>2025/05/01，2025/08/12，2025/08/26，2025/11/24，2026/06/20，2026/08/30</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -17231,7 +17231,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/07/18，2025/08/02，2025/10/16，2026/05/01，2026/8/27</t>
+          <t>2025/05/03，2025/07/18，2025/08/02，2025/10/16，2026/05/01，2026/08/27</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -17271,7 +17271,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25，2026/8/30</t>
+          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25，2026/08/30</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -17351,7 +17351,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2025/05/03，2026/8/27</t>
+          <t>2025/05/03，2026/08/27</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/8/28，2026/9/4</t>
+          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/08/28，2026/09/04，2026/09/11</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -17822,12 +17822,12 @@
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Adele</t>
+          <t>张靓颖</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/9/2</t>
+          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/09/02</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10，2026/8/28，2026/8/28</t>
+          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10，2026/08/28，2026/08/28</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/9/4</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/09/04</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16，2026/8/30</t>
+          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16，2026/08/30</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23，2026/08/11</t>
+          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23，2026/08/11，2026/09/06</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/06/17，2025/06/23，2025/07/06，2025/07/15，2025/09/10，2025/10/18，2025/11/13，2026/05/04，2026/07/09</t>
+          <t>2025/05/22，2025/06/17，2025/06/23，2025/07/06，2025/07/15，2025/09/10，2025/10/18，2025/11/13，2026/05/04，2026/07/09，2026/08/30</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10，2026/8/30</t>
+          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10，2026/08/30</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -18919,7 +18919,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/9/2</t>
+          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/09/02</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2025/05/23，2026/8/30</t>
+          <t>2025/05/23，2026/08/30</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/06/26，2025/07/21，2025/08/12，2025/09/10，2025/09/19，2025/11/01，2025/12/09，2025/12/13，2026/02/14，2026/04/24，2026/06/16</t>
+          <t>2025/05/23，2025/06/26，2025/07/21，2025/08/12，2025/09/10，2025/09/19，2025/11/01，2025/12/09，2025/12/13，2026/02/14，2026/04/24，2026/06/16，2026/09/13</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/08/16</t>
+          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/08/16，2026/09/12</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -19254,7 +19254,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>2025/05/26，2025/07/03，2025/09/15，2026/9/2</t>
+          <t>2025/05/26，2025/07/03，2025/09/15，2026/09/02</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -19683,7 +19683,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/8/30</t>
+          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/08/30</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2025/06/01，2026/01/23，2026/02/02，2026/02/23，2026/03/05，2026/03/17，2026/04/24，2026/05/16</t>
+          <t>2025/06/01，2026/01/23，2026/02/02，2026/02/23，2026/03/05，2026/03/17，2026/04/24，2026/05/16，2026/09/13</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -20607,7 +20607,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/06/07，2025/06/12，2025/06/28，2025/08/13，2025/09/11，2025/09/30，2025/11/27，2026/8/27</t>
+          <t>2025/06/02，2025/06/07，2025/06/12，2025/06/28，2025/08/13，2025/09/11，2025/09/30，2025/11/27，2026/08/27</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -20800,7 +20800,11 @@
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>中央人民广播电台少年广播合唱团</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>2025/06/06</t>
@@ -21287,7 +21291,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31，2026/08/21</t>
+          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31，2026/08/21，2026/09/11</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -21298,7 +21302,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -21487,7 +21491,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>2025/06/17，2025/09/24，2026/9/2</t>
+          <t>2025/06/17，2025/09/24，2026/09/02</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -21767,7 +21771,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/8/30</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21971,7 +21975,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11</t>
+          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11，2026/09/06</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -21982,7 +21986,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -22051,7 +22055,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/23，2026/07/09，2026/9/2</t>
+          <t>2025/06/23，2025/10/23，2026/07/09，2026/09/02</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -22091,7 +22095,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>2025/06/23，2026/8/30</t>
+          <t>2025/06/23，2026/08/30</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -22371,7 +22375,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08，2026/08/18</t>
+          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08，2026/08/18，2026/09/11</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -22382,7 +22386,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -22415,7 +22419,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17，2026/08/25</t>
+          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/09/06</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -22426,7 +22430,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -22667,7 +22671,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/09/19，2025/11/22，2026/07/22，2026/9/2</t>
+          <t>2025/06/29，2025/09/19，2025/11/22，2026/07/22，2026/09/02</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -22707,7 +22711,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16，2026/8/30，2026/9/4</t>
+          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/08/16，2026/08/30，2026/09/04，2026/09/12</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -22718,7 +22722,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -22747,7 +22751,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>2025/06/29，2026/08/11，2026/08/21，2026/8/30</t>
+          <t>2025/06/29，2026/08/11，2026/08/21，2026/08/30，2026/09/06</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -22758,7 +22762,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -22827,7 +22831,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2025/06/29，2026/8/30</t>
+          <t>2025/06/29，2026/08/30</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -22867,7 +22871,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>2025/06/29，2026/8/30</t>
+          <t>2025/06/29，2026/08/30</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -23183,7 +23187,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06，2026/9/2</t>
+          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06，2026/09/02</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -23419,7 +23423,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09，2026/8/28</t>
+          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09，2026/08/28，2026/09/06</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -23430,7 +23434,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -23699,7 +23703,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>2025/07/11，2025/07/15，2025/07/15，2025/08/04，2025/09/28，2025/10/05，2026/01/09，2026/03/07，2026/03/08，2026/06/14，2026/8/27</t>
+          <t>2025/07/11，2025/07/15，2025/07/15，2025/08/04，2025/09/28，2025/10/05，2026/01/09，2026/03/07，2026/03/08，2026/06/14，2026/08/27</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -23899,7 +23903,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/8/27</t>
+          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/08/27</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -23979,7 +23983,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28，2026/8/28</t>
+          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28，2026/08/28</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -24059,7 +24063,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23，2026/8/28</t>
+          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23，2026/08/28</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -24367,7 +24371,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>2025/07/21</t>
+          <t>2025/07/21，2026/09/08</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -24378,7 +24382,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -24531,7 +24535,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/26，2026/09/06</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -24542,7 +24546,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -24731,7 +24735,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22，2026/8/27</t>
+          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22，2026/08/27，2026/09/08</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -24742,7 +24746,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -25003,7 +25007,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31，2026/08/25</t>
+          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31，2026/08/25，2026/09/06</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -25014,7 +25018,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -25123,7 +25127,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13，2026/08/07，2026/9/4</t>
+          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13，2026/08/07，2026/09/04</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -26307,7 +26311,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/8/28，2026/8/30</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26423,7 +26427,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>2025/09/17，2025/10/11，2025/10/13，2025/10/20，2025/10/25，2025/11/21，2025/12/17，2026/02/23，2026/03/17，2026/03/25，2026/05/23，2026/8/27</t>
+          <t>2025/09/17，2025/10/11，2025/10/13，2025/10/20，2025/10/25，2025/11/21，2025/12/17，2026/02/23，2026/03/17，2026/03/25，2026/05/23，2026/08/27</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -26851,7 +26855,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>2025/09/20，2025/09/21，2025/09/22，2025/09/24，2025/09/27，2025/10/05，2025/10/12，2025/10/22，2025/11/01，2025/12/06，2025/12/12，2026/01/19，2026/04/08，2026/05/20，2026/06/06，2026/06/28，2026/07/22</t>
+          <t>2025/09/20，2025/09/21，2025/09/22，2025/09/24，2025/09/27，2025/10/05，2025/10/12，2025/10/22，2025/11/01，2025/12/06，2025/12/12，2026/01/19，2026/04/08，2026/05/20，2026/06/06，2026/06/28，2026/07/22，2026/09/13</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -26862,7 +26866,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -26891,7 +26895,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/9/4</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/09/04</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -27159,7 +27163,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22</t>
+          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22，2026/09/11</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -27170,7 +27174,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -27271,7 +27275,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19，2026/8/30</t>
+          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19，2026/08/30</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -27507,7 +27511,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>2025/09/28，2026/9/4</t>
+          <t>2025/09/28，2026/09/04</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -27587,7 +27591,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>2025/09/29，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/06，2026/01/15，2026/01/19，2026/03/07，2026/05/05</t>
+          <t>2025/09/29，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/06，2026/01/15，2026/01/19，2026/03/07，2026/05/05，2026/09/11</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -27598,7 +27602,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -28231,7 +28235,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>2025/10/13，2025/10/18，2026/03/15，2026/08/09，2026/9/2</t>
+          <t>2025/10/13，2025/10/18，2026/03/15，2026/08/09，2026/09/02</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -28591,7 +28595,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>2025/10/23，2026/08/16，2026/08/21，2026/9/4</t>
+          <t>2025/10/23，2026/08/16，2026/08/21，2026/09/04</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -29059,7 +29063,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16，2026/9/2</t>
+          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16，2026/09/02</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -29175,7 +29179,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>2025/10/31，2025/11/12</t>
+          <t>2025/10/31，2025/11/12，2026/09/06</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -29186,7 +29190,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -29483,7 +29487,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/9/2</t>
+          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/09/02</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -29679,7 +29683,11 @@
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
-      <c r="G730" t="inlineStr"/>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>西语</t>
+        </is>
+      </c>
       <c r="H730" t="inlineStr">
         <is>
           <t>2</t>
@@ -30059,7 +30067,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07，2026/9/2</t>
+          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07，2026/09/02</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -30099,7 +30107,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>2025/11/28，2026/9/2</t>
+          <t>2025/11/28，2026/09/02</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -30115,7 +30123,7 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>BV1Q6to6JEEx</t>
+          <t>BV1UatD6hEMa，BV1Q6to6JEEx</t>
         </is>
       </c>
       <c r="J741" t="inlineStr"/>
@@ -30371,7 +30379,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>2025/12/09，2026/02/02，2026/04/14</t>
+          <t>2025/12/09，2026/02/02，2026/04/14，2026/09/06</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -30382,7 +30390,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -30415,7 +30423,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/08/16</t>
+          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/08/16，2026/09/06</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -30426,7 +30434,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -30763,7 +30771,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/24，2025/12/26，2026/01/02，2026/01/09，2026/01/23，2026/01/29，2026/03/22，2026/04/29，2026/06/20，2026/08/11</t>
+          <t>2025/12/19，2025/12/24，2025/12/26，2026/01/02，2026/01/09，2026/01/23，2026/01/29，2026/03/22，2026/04/29，2026/06/20，2026/08/11，2026/09/13</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -30774,7 +30782,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -30843,7 +30851,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>2025/12/19，2026/9/4</t>
+          <t>2025/12/19，2026/09/04</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -30883,7 +30891,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/8/28</t>
+          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/08/28，2026/09/11</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -30894,7 +30902,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -30923,7 +30931,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/9/2</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/09/02</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30963,7 +30971,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/05，2026/01/19，2026/01/21，2026/01/22，2026/01/24，2026/02/07，2026/02/19，2026/02/24，2026/02/24，2026/02/25，2026/03/06，2026/03/25，2026/04/11，2026/04/20，2026/05/15，2026/06/19，2026/07/18，2026/08/21，2026/8/28</t>
+          <t>2025/12/26，2026/01/05，2026/01/19，2026/01/21，2026/01/22，2026/01/24，2026/02/07，2026/02/19，2026/02/24，2026/02/24，2026/02/25，2026/03/06，2026/03/25，2026/04/11，2026/04/20，2026/05/15，2026/06/19，2026/07/18，2026/08/21，2026/08/28</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
@@ -31047,7 +31055,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/8/28</t>
+          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/08/28</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -31283,7 +31291,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2026/01/19</t>
+          <t>2026/01/19，2026/09/06</t>
         </is>
       </c>
       <c r="F771" t="inlineStr"/>
@@ -31294,10 +31302,14 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I771" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>BV11cb46tE4x</t>
+        </is>
+      </c>
       <c r="J771" t="inlineStr"/>
     </row>
     <row r="772">
@@ -31431,7 +31443,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27</t>
+          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11</t>
         </is>
       </c>
       <c r="F775" t="inlineStr"/>
@@ -31442,7 +31454,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -31555,7 +31567,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>2026/01/25，2026/08/19</t>
+          <t>2026/01/25，2026/08/19，2026/09/05</t>
         </is>
       </c>
       <c r="F778" t="inlineStr"/>
@@ -31566,7 +31578,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -31639,7 +31651,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>2026/01/25，2026/01/30，2026/02/02，2026/02/08，2026/02/19，2026/02/23，2026/02/25，2026/03/12，2026/03/28，2026/04/12，2026/04/20，2026/06/26，2026/07/22，2026/9/4</t>
+          <t>2026/01/25，2026/01/30，2026/02/02，2026/02/08，2026/02/19，2026/02/23，2026/02/25，2026/03/12，2026/03/28，2026/04/12，2026/04/20，2026/06/26，2026/07/22，2026/09/04</t>
         </is>
       </c>
       <c r="F780" t="inlineStr"/>
@@ -31959,7 +31971,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02，2026/9/2</t>
+          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02，2026/09/02</t>
         </is>
       </c>
       <c r="F788" t="inlineStr"/>
@@ -32247,7 +32259,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>2026/02/19</t>
+          <t>2026/02/19，2026/08/30</t>
         </is>
       </c>
       <c r="F795" t="inlineStr"/>
@@ -32258,7 +32270,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -32367,7 +32379,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/8/27</t>
+          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/08/27</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
@@ -32491,7 +32503,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>2026/02/25，2026/02/28，2026/03/01，2026/04/20</t>
+          <t>2026/02/25，2026/02/28，2026/03/01，2026/04/20，2026/09/06</t>
         </is>
       </c>
       <c r="F801" t="inlineStr"/>
@@ -32502,7 +32514,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -33039,7 +33051,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11</t>
+          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -33050,7 +33062,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -33391,7 +33403,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21</t>
+          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21，2026/09/11</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -33402,7 +33414,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -33607,7 +33619,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/25，2026/04/01</t>
+          <t>2025/12/24，2025/12/25，2026/04/01，2026/09/13</t>
         </is>
       </c>
       <c r="F828" t="inlineStr"/>
@@ -33618,7 +33630,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -34247,7 +34259,11 @@
           <t>착하다는 말이 제일 싫어</t>
         </is>
       </c>
-      <c r="C844" t="inlineStr"/>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>最讨厌善良这句话</t>
+        </is>
+      </c>
       <c r="D844" t="inlineStr">
         <is>
           <t>YENA</t>
@@ -34255,7 +34271,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25，2026/9/2</t>
+          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25，2026/09/02</t>
         </is>
       </c>
       <c r="F844" t="inlineStr"/>
@@ -34295,7 +34311,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02</t>
+          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02，2026/09/06</t>
         </is>
       </c>
       <c r="F845" t="inlineStr"/>
@@ -34306,7 +34322,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -34595,7 +34611,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11，2026/08/25</t>
+          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11，2026/08/25，2026/09/11</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -34606,7 +34622,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -34675,7 +34691,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/08/02，2026/8/30</t>
+          <t>2026/05/01，2026/08/02，2026/08/30</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -34759,7 +34775,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/01，2026/09/13</t>
         </is>
       </c>
       <c r="F856" t="inlineStr"/>
@@ -34770,7 +34786,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -34891,7 +34907,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23</t>
+          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23，2026/09/11</t>
         </is>
       </c>
       <c r="F859" t="inlineStr"/>
@@ -34902,7 +34918,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -34935,7 +34951,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02，2026/9/4</t>
+          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02</t>
         </is>
       </c>
       <c r="F860" t="inlineStr"/>
@@ -34946,7 +34962,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -35135,7 +35151,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/9/4</t>
+          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/09/04</t>
         </is>
       </c>
       <c r="F865" t="inlineStr"/>
@@ -35627,7 +35643,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/8/28</t>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
@@ -35638,7 +35654,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -35751,7 +35767,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/8/28</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -35791,7 +35807,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/9/2</t>
+          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/09/02</t>
         </is>
       </c>
       <c r="F881" t="inlineStr"/>
@@ -35875,7 +35891,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>2026/07/27，2026/07/31</t>
+          <t>2026/07/27，2026/07/31，2026/09/13</t>
         </is>
       </c>
       <c r="F883" t="inlineStr"/>
@@ -35886,7 +35902,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -35955,7 +35971,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25</t>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
@@ -35966,7 +35982,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -36075,7 +36091,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25</t>
+          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11</t>
         </is>
       </c>
       <c r="F888" t="inlineStr"/>
@@ -36086,7 +36102,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -36115,7 +36131,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/08/11，2026/09/06</t>
         </is>
       </c>
       <c r="F889" t="inlineStr"/>
@@ -36126,7 +36142,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -36155,7 +36171,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/08/19，2026/08/23，2026/8/30</t>
+          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11</t>
         </is>
       </c>
       <c r="F890" t="inlineStr"/>
@@ -36166,7 +36182,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -36399,7 +36415,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/08/25</t>
+          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11</t>
         </is>
       </c>
       <c r="F896" t="inlineStr"/>
@@ -36410,7 +36426,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -36439,7 +36455,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/9/2</t>
+          <t>2026/08/23</t>
         </is>
       </c>
       <c r="F897" t="inlineStr"/>
@@ -36450,7 +36466,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -36548,18 +36564,18 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>All About That Bass</t>
+          <t>Love Me Like You Do</t>
         </is>
       </c>
       <c r="C900" t="inlineStr"/>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Meghan Trainor</t>
+          <t>Ellie Goulding</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>2026/8/30，2026/9/2</t>
+          <t>2026/08/30，2026/09/11</t>
         </is>
       </c>
       <c r="F900" t="inlineStr"/>
@@ -36575,7 +36591,7 @@
       </c>
       <c r="I900" t="inlineStr">
         <is>
-          <t>BV1y4th6AEz2</t>
+          <t>BV1W2tn6zEBJ，BV12wta6uEUK</t>
         </is>
       </c>
       <c r="J900" t="inlineStr"/>
@@ -36588,18 +36604,18 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Last Friday Night</t>
+          <t>Honeymoon Avenue</t>
         </is>
       </c>
       <c r="C901" t="inlineStr"/>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Katy Perry</t>
+          <t>Ariana Grande</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>2026/8/30</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="F901" t="inlineStr"/>
@@ -36615,7 +36631,7 @@
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>BV12Hth6iEup</t>
+          <t>BV1WhtW67ECn，BV1k8th6cEpk</t>
         </is>
       </c>
       <c r="J901" t="inlineStr"/>
@@ -36639,7 +36655,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>2026/8/30，2026/8/30</t>
+          <t>2026/08/30，2026/08/30</t>
         </is>
       </c>
       <c r="F902" t="inlineStr"/>
@@ -36655,7 +36671,7 @@
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>BV1w8th6wERB</t>
+          <t>BV1wvtW6yE7K，BV1w8th6wERB</t>
         </is>
       </c>
       <c r="J902" t="inlineStr"/>
@@ -36668,18 +36684,18 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Honeymoon Avenue</t>
+          <t>Last Friday Night (T.G.I.F.)</t>
         </is>
       </c>
       <c r="C903" t="inlineStr"/>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Ariana Grande</t>
+          <t>Katy Perry</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>2026/8/30</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="F903" t="inlineStr"/>
@@ -36695,7 +36711,7 @@
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>BV1k8th6cEpk</t>
+          <t>BV12Hth6iEup</t>
         </is>
       </c>
       <c r="J903" t="inlineStr"/>
@@ -36708,18 +36724,18 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Love Me Like You Do</t>
+          <t>All About That Bass</t>
         </is>
       </c>
       <c r="C904" t="inlineStr"/>
       <c r="D904" t="inlineStr">
         <is>
-          <t>Ellie Goulding</t>
+          <t>Meghan Trainor</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>2026/8/30</t>
+          <t>2026/08/30，2026/09/02</t>
         </is>
       </c>
       <c r="F904" t="inlineStr"/>
@@ -36730,12 +36746,12 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>BV12wta6uEUK</t>
+          <t>BV14Hth6qEwH，BV1y4th6AEz2</t>
         </is>
       </c>
       <c r="J904" t="inlineStr"/>
@@ -36751,7 +36767,11 @@
           <t>California King Bed</t>
         </is>
       </c>
-      <c r="C905" t="inlineStr"/>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>加州王床</t>
+        </is>
+      </c>
       <c r="D905" t="inlineStr">
         <is>
           <t>Rihanna</t>
@@ -36759,7 +36779,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>2026/9/2</t>
+          <t>2026/09/02</t>
         </is>
       </c>
       <c r="F905" t="inlineStr"/>
@@ -36775,7 +36795,7 @@
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>BV15eto6sEMB</t>
+          <t>BV1oetS6gEcN，BV15eto6sEMB</t>
         </is>
       </c>
       <c r="J905" t="inlineStr"/>
@@ -36788,37 +36808,153 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>willow</t>
+          <t>社畜少女</t>
         </is>
       </c>
       <c r="C906" t="inlineStr"/>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>2026/9/4</t>
+          <t>2026/09/11</t>
         </is>
       </c>
       <c r="F906" t="inlineStr"/>
       <c r="G906" t="inlineStr">
         <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>BV1cJY26QEG7</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>还是会寂寞</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr"/>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>陈绮贞</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>2026/09/06，2026/09/11</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr"/>
+      <c r="J907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>粛聖!! ロリ神レクイエム</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>肃静！萝莉神的镇魂曲</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>しぐれうい</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>2026/09/13</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>日语</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr"/>
+      <c r="J908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>willow</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr"/>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Taylor Swift</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr">
+        <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="H906" t="inlineStr">
+      <c r="H909" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I906" t="inlineStr">
+      <c r="I909" t="inlineStr">
         <is>
           <t>BV1Setr6MEBW</t>
         </is>
       </c>
-      <c r="J906" t="inlineStr"/>
+      <c r="J909" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J909"/>
+  <dimension ref="A1:J910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25</t>
+          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25，2026/9/14</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17</t>
+          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17，2026/9/14</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/9/14</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28</t>
+          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28，2026/9/14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26，2026/09/04</t>
+          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26，2026/09/04，2026/9/14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09</t>
+          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09，2026/9/14</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/06/06，2025/06/27，2025/08/01，2025/11/09，2025/11/14，2026/06/12</t>
+          <t>2025/03/14，2025/06/06，2025/06/27，2025/08/01，2025/11/09，2025/11/14，2026/06/12，2026/9/14</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18</t>
+          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27</t>
+          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/9/14</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28，2026/9/14</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21</t>
+          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21，2026/9/14</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27，2026/9/14</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/9/14</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13</t>
+          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/9/14</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/08/30，2026/09/11</t>
+          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/08/30，2026/09/11，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09</t>
+          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09，2026/9/14</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/23，2025/10/09，2026/01/22，2026/03/09</t>
+          <t>2025/04/25，2025/06/23，2025/10/09，2026/01/22，2026/03/09，2026/9/14</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09</t>
+          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09，2026/9/14</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2025/05/03，2026/08/27</t>
+          <t>2025/05/03，2026/08/27，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19</t>
+          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -18846,7 +18846,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -24655,7 +24655,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/08/08，2026/07/22</t>
+          <t>2025/07/26，2025/08/08，2026/07/22，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -24666,7 +24666,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -31931,7 +31931,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31942,7 +31942,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -32587,7 +32587,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16</t>
+          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16，2026/9/14，2026/9/14</t>
         </is>
       </c>
       <c r="F803" t="inlineStr"/>
@@ -32598,7 +32598,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -35767,7 +35767,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/9/14</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -35778,7 +35778,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -36091,7 +36091,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11</t>
+          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/9/14</t>
         </is>
       </c>
       <c r="F888" t="inlineStr"/>
@@ -36102,7 +36102,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -36873,7 +36873,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I907" t="inlineStr"/>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>BV13fY16KELD</t>
+        </is>
+      </c>
       <c r="J907" t="inlineStr"/>
     </row>
     <row r="908">
@@ -36913,7 +36917,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I908" t="inlineStr"/>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>BV1FwY16LEko</t>
+        </is>
+      </c>
       <c r="J908" t="inlineStr"/>
     </row>
     <row r="909">
@@ -36955,6 +36963,46 @@
         </is>
       </c>
       <c r="J909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Better Dig Two</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr"/>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>The Band Perry</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>BV1Pjen6QEeh</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J910"/>
+  <dimension ref="A1:J915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/01/23，2026/03/01，2026/03/22，2026/03/27，2026/06/28，2026/07/22</t>
+          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/01/23，2026/03/01，2026/03/22，2026/03/27，2026/06/28，2026/07/22，2026/09/23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06，2026/09/23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17，2026/09/06</t>
+          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17，2026/09/06，2026/09/23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04，2026/09/22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23</t>
+          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23，2026/09/17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28，2026/09/17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25，2026/9/14</t>
+          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25，2026/09/14，2026/09/22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/08/16</t>
+          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/08/16，2026/09/23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31，2026/08/25</t>
+          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31，2026/08/25，2026/09/26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25</t>
+          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25，2026/09/21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23，2026/08/30，2026/08/30</t>
+          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23，2026/08/30，2026/08/30，2026/09/23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17，2026/9/14</t>
+          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22，2026/08/11</t>
+          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22，2026/08/11，2026/09/21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19，2026/09/05</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19，2026/09/05，2026/09/19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/17，2025/05/18，2025/05/30，2025/06/06，2025/06/21，2025/06/27，2025/07/24，2025/08/24，2025/09/10，2025/09/30，2025/10/23，2025/11/10，2026/01/15，2026/02/14，2026/03/22，2026/05/20，2026/09/13</t>
+          <t>2025/03/06，2025/04/17，2025/05/18，2025/05/30，2025/06/06，2025/06/21，2025/06/27，2025/07/24，2025/08/24，2025/09/10，2025/09/30，2025/10/23，2025/11/10，2026/01/15，2026/02/14，2026/03/22，2026/05/20，2026/09/13，2026/09/23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/06，2025/04/13，2025/04/22，2025/05/08，2025/05/09，2025/05/30，2025/06/08，2025/08/04，2025/09/18，2025/10/12，2025/11/21，2026/01/24，2026/02/14，2026/02/25，2026/04/10，2026/04/25</t>
+          <t>2025/03/06，2025/04/06，2025/04/13，2025/04/22，2025/05/08，2025/05/09，2025/05/30，2025/06/08，2025/08/04，2025/09/18，2025/10/12，2025/11/21，2026/01/24，2026/02/14，2026/02/25，2026/04/10，2026/04/25，2026/09/23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/13，2025/05/01，2025/06/15，2025/07/24，2025/08/30，2025/09/05，2025/10/09，2025/11/03，2025/12/12，2026/02/04，2026/04/18，2026/05/20，2026/06/20，2026/07/30，2026/08/09</t>
+          <t>2025/03/06，2025/04/13，2025/05/01，2025/06/15，2025/07/24，2025/08/30，2025/09/05，2025/10/09，2025/11/03，2025/12/12，2026/02/04，2026/04/18，2026/05/20，2026/06/20，2026/07/30，2026/08/09，2026/09/22</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/04，2025/04/19，2025/06/02，2025/06/17，2025/06/23，2025/07/20，2025/09/24，2025/10/09，2026/02/17，2026/03/07，2026/05/24</t>
+          <t>2025/03/07，2025/04/04，2025/04/19，2025/06/02，2025/06/17，2025/06/23，2025/07/20，2025/09/24，2025/10/09，2026/02/17，2026/03/07，2026/05/24，2026/09/16</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/27，2025/04/07，2025/04/12，2025/04/22，2025/04/26，2025/05/05，2025/05/19，2025/06/03，2025/06/09，2025/07/18，2025/07/22，2025/09/10，2025/09/19，2025/10/16，2025/12/24，2026/06/20，2026/08/27</t>
+          <t>2025/03/07，2025/03/27，2025/04/07，2025/04/12，2025/04/22，2025/04/26，2025/05/05，2025/05/19，2025/06/03，2025/06/09，2025/07/18，2025/07/22，2025/09/10，2025/09/19，2025/10/16，2025/12/24，2026/06/20，2026/08/27，2026/09/21</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/9/14</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/09/14</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25，2026/08/25，2026/09/06</t>
+          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25，2026/08/25，2026/09/06，2026/09/19</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28，2026/09/06</t>
+          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28，2026/09/06，2026/09/22</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28，2026/9/14</t>
+          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28，2026/09/14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/06，2025/05/08，2025/05/24，2025/06/06，2025/07/05，2025/07/24，2025/08/04，2025/09/08，2025/09/19，2025/10/16，2025/10/28，2025/11/13，2025/12/16，2025/12/30，2026/02/19，2026/04/14，2026/06/12，2026/06/14</t>
+          <t>2025/03/09，2025/04/06，2025/05/08，2025/05/24，2025/06/06，2025/07/05，2025/07/24，2025/08/04，2025/09/08，2025/09/19，2025/10/16，2025/10/28，2025/11/13，2025/12/16，2025/12/30，2026/02/19，2026/04/14，2026/06/12，2026/06/14，2026/09/21</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21</t>
+          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21，2026/09/16，2026/09/22</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26，2026/09/04，2026/9/14</t>
+          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26，2026/09/04，2026/09/14，2026/09/23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09，2026/9/14</t>
+          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09，2026/09/14</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/05/10，2025/05/24，2025/06/20，2025/07/13，2025/08/23，2025/09/05，2025/09/18，2025/09/30，2025/11/27，2026/02/07</t>
+          <t>2025/03/13，2025/05/10，2025/05/24，2025/06/20，2025/07/13，2025/08/23，2025/09/05，2025/09/18，2025/09/30，2025/11/27，2026/02/07，2026/09/23</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22，2026/08/28</t>
+          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22，2026/08/28，2026/09/23</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/14，2025/04/14，2025/05/26，2025/06/02，2025/06/12，2025/06/23，2025/07/06，2025/07/10，2025/07/25，2025/08/23，2025/09/20，2025/11/09，2026/03/25，2026/04/26，2026/06/15，2026/08/25</t>
+          <t>2025/03/14，2025/03/14，2025/04/14，2025/05/26，2025/06/02，2025/06/12，2025/06/23，2025/07/06，2025/07/10，2025/07/25，2025/08/23，2025/09/20，2025/11/09，2026/03/25，2026/04/26，2026/06/15，2026/08/25，2026/09/21，2026/09/22</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16</t>
+          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16，2026/09/21</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/25，2025/06/26，2025/07/05，2025/09/05</t>
+          <t>2025/03/14，2025/03/25，2025/06/26，2025/07/05，2025/09/05，2026/09/21</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/19，2025/07/21，2025/10/20，2025/11/09，2026/01/14，2026/02/19，2026/04/19，2026/06/03</t>
+          <t>2025/03/14，2025/05/19，2025/07/21，2025/10/20，2025/11/09，2026/01/14，2026/02/19，2026/04/19，2026/06/03，2026/09/26</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/06/06，2025/06/27，2025/08/01，2025/11/09，2025/11/14，2026/06/12，2026/9/14</t>
+          <t>2025/03/14，2025/06/06，2025/06/27，2025/08/01，2025/11/09，2025/11/14，2026/06/12，2026/09/14，2026/09/22</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09，2026/07/31</t>
+          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09，2026/07/31，2026/09/16</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/12，2025/05/20，2025/05/30，2025/06/27，2025/08/13，2025/09/11，2025/10/28，2025/12/20，2026/01/16，2026/04/17，2026/08/08</t>
+          <t>2025/03/14，2025/04/12，2025/05/20，2025/05/30，2025/06/27，2025/08/13，2025/09/11，2025/10/28，2025/12/20，2026/01/16，2026/04/17，2026/08/08，2026/09/22</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/05，2025/05/15，2025/08/12，2026/03/28，2026/09/06</t>
+          <t>2025/03/15，2025/04/05，2025/05/15，2025/08/12，2026/03/28，2026/09/06，2026/09/22</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/9/14，2026/9/14</t>
+          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06，2026/09/23</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09，2026/08/02</t>
+          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09，2026/08/02，2026/09/17</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03</t>
+          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03，2026/09/26</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25，2026/09/06</t>
+          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25，2026/09/06，2026/09/21</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/08/28，2026/08/28</t>
+          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/08/28，2026/08/28，2026/09/26</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/04/17，2025/04/21，2025/04/29，2025/05/08，2025/05/30，2025/06/13，2025/06/26，2025/07/08，2025/07/18，2025/08/22，2025/09/05，2025/09/28，2025/10/25，2025/11/10，2025/11/27，2025/12/08，2025/12/24，2026/01/28，2026/04/22，2026/05/05，2026/06/14，2026/07/22，2026/07/31</t>
+          <t>2025/03/20，2025/04/04，2025/04/17，2025/04/21，2025/04/29，2025/05/08，2025/05/30，2025/06/13，2025/06/26，2025/07/08，2025/07/18，2025/08/22，2025/09/05，2025/09/28，2025/10/25，2025/11/10，2025/11/27，2025/12/08，2025/12/24，2026/01/28，2026/04/22，2026/05/05，2026/06/14，2026/07/22，2026/07/31，2026/09/22</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/22，2025/05/29，2025/06/03，2025/08/28，2025/09/11，2025/10/18，2025/10/30，2025/11/28，2025/12/28，2026/03/15，2026/05/19，2026/07/13</t>
+          <t>2025/03/20，2025/05/22，2025/05/29，2025/06/03，2025/08/28，2025/09/11，2025/10/18，2025/10/30，2025/11/28，2025/12/28，2026/03/15，2026/05/19，2026/07/13，2026/09/16</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06，2026/09/21</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28，2026/08/16</t>
+          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28，2026/08/16，2026/09/16</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11</t>
+          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11，2026/09/26</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/09/02，2026/09/08</t>
+          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/09/02，2026/09/08，2026/09/22</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/9/14</t>
+          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/09/14，2026/09/14，2026/09/22</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28，2026/9/14</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28，2026/09/14，2026/09/22</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28</t>
+          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28，2026/09/17</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/07，2025/04/18，2025/05/08，2025/10/24，2025/12/12，2026/04/26，2026/09/06</t>
+          <t>2025/03/21，2025/04/07，2025/04/18，2025/05/08，2025/10/24，2025/12/12，2026/04/26，2026/09/06，2026/09/23</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25</t>
+          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25，2026/09/14</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05，2026/09/04，2026/09/11</t>
+          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/11，2025/09/12，2025/10/31，2026/01/09，2026/07/05，2026/09/04，2026/09/11，2026/09/16</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/21，2025/04/26，2025/05/18，2025/08/24，2025/12/30</t>
+          <t>2025/03/24，2025/04/06，2025/04/21，2025/04/26，2025/05/18，2025/08/24，2025/12/30，2026/09/16</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04，2026/09/21</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/11，2025/04/20，2025/05/17，2025/05/22，2025/06/07，2025/06/21，2025/07/06，2025/07/28，2025/09/03，2025/09/14，2025/11/09，2026/01/01，2026/02/07，2026/03/25，2026/04/26，2026/06/23，2026/07/31，2026/07/31</t>
+          <t>2025/03/25，2025/04/11，2025/04/20，2025/05/17，2025/05/22，2025/06/07，2025/06/21，2025/07/06，2025/07/28，2025/09/03，2025/09/14，2025/11/09，2026/01/01，2026/02/07，2026/03/25，2026/04/26，2026/06/23，2026/07/31，2026/07/31，2026/09/14</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21，2026/9/14</t>
+          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21，2026/09/14</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/06，2025/05/01，2025/06/23，2025/07/09，2025/09/05，2025/09/15，2025/10/16，2025/11/19，2025/12/17，2026/04/09，2026/07/16</t>
+          <t>2025/03/25，2025/04/06，2025/05/01，2025/06/23，2025/07/09，2025/09/05，2025/09/15，2025/10/16，2025/11/19，2025/12/17，2026/04/09，2026/07/16，2026/09/21</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18，2026/09/08</t>
+          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18，2026/09/08，2026/09/16</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02，2026/09/17</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/08/28</t>
+          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/08/28，2026/09/16</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/08/28，2025/09/18，2025/11/21，2025/12/04，2026/03/21，2026/06/27</t>
+          <t>2025/03/28，2025/04/04，2025/08/28，2025/09/18，2025/11/21，2025/12/04，2026/03/21，2026/06/27，2026/09/16</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02，2026/09/16</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/17，2025/06/13，2025/07/05，2025/09/15，2025/10/23</t>
+          <t>2025/03/28，2025/05/17，2025/06/13，2025/07/05，2025/09/15，2025/10/23，2026/09/16</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/01，2025/04/12，2025/04/14，2025/04/17，2025/04/18，2025/04/20，2025/04/29，2025/05/08，2025/05/20，2025/05/25，2025/06/03，2025/06/08，2025/06/14，2025/06/20，2025/07/05，2025/07/08，2025/07/17，2025/07/28，2025/08/07，2025/08/19，2025/08/28，2025/09/03，2025/09/20，2025/10/03，2025/10/26，2025/12/08，2025/12/12，2026/01/28，2026/03/07，2026/03/28，2026/04/19，2026/05/15，2026/07/27</t>
+          <t>2025/03/29，2025/04/01，2025/04/12，2025/04/14，2025/04/17，2025/04/18，2025/04/20，2025/04/29，2025/05/08，2025/05/20，2025/05/25，2025/06/03，2025/06/08，2025/06/14，2025/06/20，2025/07/05，2025/07/08，2025/07/17，2025/07/28，2025/08/07，2025/08/19，2025/08/28，2025/09/03，2025/09/20，2025/10/03，2025/10/26，2025/12/08，2025/12/12，2026/01/28，2026/03/07，2026/03/28，2026/04/19，2026/05/15，2026/07/27，2026/09/17</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/05/29，2025/06/17，2025/07/24，2025/08/16，2025/09/21，2025/10/30，2026/02/09</t>
+          <t>2025/03/29，2025/05/29，2025/06/17，2025/07/24，2025/08/16，2025/09/21，2025/10/30，2026/02/09，2026/09/26</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -9978,7 +9978,7 @@
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>K/DA/Madison Beer/(G)I-DLE ((여자)아이들)/刘柏辛Lexie</t>
+          <t>K/DA/Madison Beer/(G)I-DLE/刘柏辛Lexie</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27，2026/9/14</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27，2026/09/14</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/08/22，2025/09/21，2025/10/20，2025/12/02，2026/02/09，2026/06/03</t>
+          <t>2025/03/29，2025/08/22，2025/09/21，2025/10/20，2025/12/02，2026/02/09，2026/06/03，2026/09/26</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17，2026/08/25</t>
+          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17，2026/08/25，2026/09/26</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16，2026/08/27</t>
+          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16，2026/08/27，2026/09/23，2026/09/26</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28，2026/08/28</t>
+          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28，2026/08/28，2026/09/14</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20，2026/08/02，2026/08/21</t>
+          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20，2026/08/02，2026/08/21，2026/09/23</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/04，2025/05/20，2025/06/23，2025/07/24，2025/09/12，2025/10/17，2025/12/09，2026/02/14，2026/03/25，2026/06/13，2026/07/28</t>
+          <t>2025/04/02，2025/05/04，2025/05/20，2025/06/23，2025/07/24，2025/09/12，2025/10/17，2025/12/09，2026/02/14，2026/03/25，2026/06/13，2026/07/28，2026/09/16</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28，2026/9/14，2026/9/14</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28，2026/09/14，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28</t>
+          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28，2026/09/22</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/27，2026/08/16</t>
+          <t>2025/04/03，2025/04/27，2026/08/16，2026/09/16</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03，2026/09/04</t>
+          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03，2026/09/04，2026/09/16</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -11929,7 +11929,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>BV1r8Yt6wEGn</t>
+        </is>
+      </c>
       <c r="J284" t="inlineStr"/>
     </row>
     <row r="285">
@@ -11951,7 +11955,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/11</t>
+          <t>2025/04/04，2025/07/11，2026/09/16</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -11962,7 +11966,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -12307,7 +12311,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/9/14</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12318,7 +12322,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -12347,7 +12351,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/9/14</t>
+          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/09/14，2026/09/16</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -12358,7 +12362,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -12751,7 +12755,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/08/30，2026/09/11，2026/9/14，2026/9/14</t>
+          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09，2026/08/23，2026/08/30，2026/09/11，2026/09/14，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -12762,7 +12766,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -12831,7 +12835,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25，2026/09/06</t>
+          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25，2026/09/06，2026/09/22</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -12842,7 +12846,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12911,7 +12915,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/08/28，2026/09/11</t>
+          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/08/28，2026/09/11，2026/09/16</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -12922,7 +12926,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -12951,7 +12955,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/09/02</t>
+          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/09/02，2026/09/14</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -12962,7 +12966,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -13391,7 +13395,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25，2026/08/30</t>
+          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25，2026/08/30，2026/09/14</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -13402,7 +13406,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -13743,7 +13747,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/18，2025/09/08，2025/12/05，2026/01/28，2026/04/19</t>
+          <t>2025/04/11，2025/05/18，2025/09/08，2025/12/05，2026/01/28，2026/04/19，2026/09/21</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -13754,7 +13758,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -13823,7 +13827,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/02，2025/06/12，2025/09/27，2025/11/09，2025/12/19，2026/01/01，2026/02/17，2026/07/09，2026/07/27，2026/08/21</t>
+          <t>2025/04/11，2025/06/02，2025/06/12，2025/09/27，2025/11/09，2025/12/19，2026/01/01，2026/02/17，2026/07/09，2026/07/27，2026/08/21，2026/09/21</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -13834,7 +13838,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -13943,7 +13947,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2025/04/12，2026/08/30，2026/09/04</t>
+          <t>2025/04/12，2026/08/30，2026/09/04，2026/09/21</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -13954,7 +13958,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -14159,7 +14163,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/09/04</t>
+          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/09/04，2026/09/16</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -14170,7 +14174,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -14243,7 +14247,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/10/31，2026/08/11</t>
+          <t>2025/04/14，2025/10/31，2026/08/11，2026/09/23</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -14254,7 +14258,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -14443,7 +14447,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17，2026/08/21，2026/09/11</t>
+          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17，2026/08/21，2026/09/11，2026/09/26</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -14454,7 +14458,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -14483,7 +14487,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09，2026/9/14</t>
+          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -14494,7 +14498,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -14523,7 +14527,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/04/20，2025/05/18，2025/05/20，2025/05/25，2025/06/28，2025/06/30，2025/08/24，2025/09/26，2026/01/09，2026/04/17</t>
+          <t>2025/04/15，2025/04/18，2025/04/20，2025/05/18，2025/05/20，2025/05/25，2025/06/28，2025/06/30，2025/08/24，2025/09/26，2026/01/09，2026/04/17，2026/09/17</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
@@ -14534,7 +14538,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -14603,7 +14607,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/13，2025/06/13，2025/07/07，2025/09/30</t>
+          <t>2025/04/17，2025/05/13，2025/06/13，2025/07/07，2025/09/30，2026/09/16</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -14614,7 +14618,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -14683,7 +14687,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/18，2025/07/03，2025/10/17，2025/10/30，2026/01/09</t>
+          <t>2025/04/17，2025/04/18，2025/07/03，2025/10/17，2025/10/30，2026/01/09，2026/09/23</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -14694,7 +14698,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -14851,7 +14855,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06，2026/09/22</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14862,7 +14866,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -15411,7 +15415,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11</t>
+          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11，2026/09/22</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -15422,7 +15426,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15451,7 +15455,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/12/23</t>
+          <t>2025/04/20，2025/12/23，2026/09/21</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -15462,7 +15466,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -16471,7 +16475,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/23，2025/10/09，2026/01/22，2026/03/09，2026/9/14</t>
+          <t>2025/04/25，2025/06/23，2025/10/09，2026/01/22，2026/03/09，2026/09/14</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -16551,7 +16555,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09，2026/9/14</t>
+          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09，2026/09/14</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -16795,7 +16799,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/05/06，2025/07/27，2025/09/17，2025/10/16，2025/11/09，2026/02/12，2026/07/10，2026/07/15</t>
+          <t>2025/04/28，2025/05/06，2025/07/27，2025/09/17，2025/10/16，2025/11/09，2026/02/12，2026/07/10，2026/07/15，2026/09/16</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -16806,7 +16810,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -17191,7 +17195,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09，2026/08/16</t>
+          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09，2026/08/16，2026/09/16</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -17202,7 +17206,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -17351,7 +17355,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2025/05/03，2026/08/27，2026/9/14，2026/9/14</t>
+          <t>2025/05/03，2026/08/27，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -17827,7 +17831,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/09/02</t>
+          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/09/02，2026/09/22</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -17838,7 +17842,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -18187,7 +18191,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03，2026/08/07，2026/08/23</t>
+          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03，2026/08/07，2026/08/23，2026/09/16</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -18198,7 +18202,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -18711,7 +18715,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/06/17，2025/06/23，2025/07/06，2025/07/15，2025/09/10，2025/10/18，2025/11/13，2026/05/04，2026/07/09，2026/08/30</t>
+          <t>2025/05/22，2025/06/17，2025/06/23，2025/07/06，2025/07/15，2025/09/10，2025/10/18，2025/11/13，2026/05/04，2026/07/09，2026/08/30，2026/09/22</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -18722,7 +18726,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -18835,7 +18839,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19，2026/9/14，2026/9/14</t>
+          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19，2026/09/14，2026/09/14，2026/09/22</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -18846,7 +18850,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -18959,7 +18963,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/12，2025/10/03，2025/10/11，2026/01/15，2026/04/29，2026/06/18</t>
+          <t>2025/05/22，2025/09/12，2025/10/03，2025/10/11，2026/01/15，2026/04/29，2026/06/18，2026/09/26</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -18970,7 +18974,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -19443,7 +19447,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16，2026/08/23</t>
+          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16，2026/08/23，2026/09/22，2026/09/23</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -19454,7 +19458,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -19883,7 +19887,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>2025/05/31，2025/12/09</t>
+          <t>2025/05/31，2025/12/09，2026/09/26</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -19894,7 +19898,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -20927,7 +20931,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>2025/06/08，2025/06/13，2025/06/16，2025/06/28，2025/07/18，2025/07/29，2025/08/18，2025/09/03，2025/09/11，2025/09/30，2025/10/05，2025/10/30，2025/11/17，2025/12/24，2026/02/02，2026/03/25</t>
+          <t>2025/06/08，2025/06/13，2025/06/16，2025/06/28，2025/07/18，2025/07/29，2025/08/18，2025/09/03，2025/09/11，2025/09/30，2025/10/05，2025/10/30，2025/11/17，2025/12/24，2026/02/02，2026/03/25，2026/09/21</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -20938,7 +20942,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -21127,7 +21131,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>2025/06/12，2025/07/13，2025/07/18，2025/09/28，2025/10/20，2026/01/19，2026/04/17，2026/06/15</t>
+          <t>2025/06/12，2025/07/13，2025/07/18，2025/09/28，2025/10/20，2026/01/19，2026/04/17，2026/06/15，2026/09/21</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -21138,7 +21142,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -21931,7 +21935,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/23，2025/09/29，2026/01/09，2026/02/10</t>
+          <t>2025/06/20，2025/06/23，2025/09/29，2026/01/09，2026/02/10，2026/09/21</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -21942,7 +21946,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -22135,7 +22139,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>2025/06/23</t>
+          <t>2025/06/23，2026/09/21</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -22146,7 +22150,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -22511,7 +22515,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>2025/06/27，2025/07/21，2025/08/18，2025/08/21，2025/09/17，2025/09/22，2025/10/16，2025/11/26，2026/01/19，2026/05/20</t>
+          <t>2025/06/27，2025/07/21，2025/08/18，2025/08/21，2025/09/17，2025/09/22，2025/10/16，2025/11/26，2026/01/19，2026/05/20，2026/09/22</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -22522,7 +22526,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -23823,7 +23827,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>2025/07/11</t>
+          <t>2025/07/11，2026/09/23</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -23834,7 +23838,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -23863,7 +23867,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>2025/07/13，2025/08/26，2025/12/17</t>
+          <t>2025/07/13，2025/08/26，2025/12/17，2026/09/16</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -23874,7 +23878,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -24103,7 +24107,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11</t>
+          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11，2026/09/19</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -24114,7 +24118,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -24331,7 +24335,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>2025/07/21，2025/09/08</t>
+          <t>2025/07/21，2025/09/08，2026/09/21</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -24342,7 +24346,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -24615,7 +24619,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>2025/07/26，2026/07/17</t>
+          <t>2025/07/26，2026/07/17，2026/09/26</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -24626,7 +24630,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -24655,7 +24659,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/08/08，2026/07/22，2026/9/14，2026/9/14</t>
+          <t>2025/07/26，2025/08/08，2026/07/22，2026/09/14，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -24666,7 +24670,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -24775,7 +24779,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>2025/07/31，2025/09/12</t>
+          <t>2025/07/31，2025/09/12，2026/09/21</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -24786,7 +24790,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -25687,7 +25691,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>2025/09/10，2025/09/22，2025/09/24，2025/10/23，2025/12/06，2026/01/24，2026/02/05，2026/02/23，2026/05/05，2026/05/23，2026/07/09</t>
+          <t>2025/09/10，2025/09/22，2025/09/24，2025/10/23，2025/12/06，2026/01/24，2026/02/05，2026/02/23，2026/05/05，2026/05/23，2026/07/09，2026/09/21</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -25698,7 +25702,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -26071,7 +26075,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>2025/09/12，2025/10/17</t>
+          <t>2025/09/12，2025/10/17，2026/09/16</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -26082,7 +26086,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -26311,7 +26315,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30，2026/09/16</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26322,7 +26326,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -26895,7 +26899,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/09/04</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/09/04，2026/09/17</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26906,7 +26910,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -27087,7 +27091,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>2025/09/22，2025/10/09，2025/12/05，2026/08/16</t>
+          <t>2025/09/22，2025/10/09，2025/12/05，2026/08/16，2026/09/16</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -27098,7 +27102,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -27671,7 +27675,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>2025/09/30，2025/10/01，2025/10/11，2025/10/17，2025/10/26，2026/08/16</t>
+          <t>2025/09/30，2025/10/01，2025/10/11，2025/10/17，2025/10/26，2026/08/16，2026/09/16</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -27682,7 +27686,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -27831,7 +27835,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2025/10/01，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/20，2025/11/03，2025/11/27</t>
+          <t>2025/10/01，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/20，2025/11/03，2025/11/27，2026/09/16</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -27842,7 +27846,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -27943,7 +27947,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2025/10/05</t>
+          <t>2025/10/05，2026/09/26</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -27954,7 +27958,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -28279,7 +28283,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>2025/10/17，2025/10/18，2025/10/23，2025/12/30，2026/01/12，2026/03/29</t>
+          <t>2025/10/17，2025/10/18，2025/10/23，2025/12/30，2026/01/12，2026/03/29，2026/09/16</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -28290,7 +28294,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -28319,7 +28323,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>2025/10/17，2025/10/18，2025/10/23，2025/10/28，2025/12/05，2025/12/12，2025/12/30</t>
+          <t>2025/10/17，2025/10/18，2025/10/23，2025/10/28，2025/12/05，2025/12/12，2025/12/30，2026/09/16</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -28330,7 +28334,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -28519,7 +28523,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>2025/10/19，2025/10/20，2025/11/18，2025/12/08，2025/12/16，2026/01/10，2026/06/17</t>
+          <t>2025/10/19，2025/10/20，2025/11/18，2025/12/08，2025/12/16，2026/01/10，2026/06/17，2026/09/21</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -28530,7 +28534,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -28979,7 +28983,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09，2026/08/11</t>
+          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09，2026/08/11，2026/09/21</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -28990,7 +28994,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -29487,7 +29491,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/09/02</t>
+          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/09/02，2026/09/22</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -29498,7 +29502,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -29643,7 +29647,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/14，2026/09/16</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -29654,10 +29658,14 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I729" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>BV1zueg62Eh7</t>
+        </is>
+      </c>
       <c r="J729" t="inlineStr"/>
     </row>
     <row r="730">
@@ -30067,7 +30075,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07，2026/09/02</t>
+          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07，2026/09/02，2026/09/22</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -30078,7 +30086,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -30811,7 +30819,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>2025/12/19，2026/02/08，2026/05/01，2026/05/25</t>
+          <t>2025/12/19，2026/02/08，2026/05/01，2026/05/25，2026/09/23</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -30822,7 +30830,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -30891,7 +30899,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/08/28，2026/09/11</t>
+          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/08/28，2026/09/11，2026/09/26</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -30902,7 +30910,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -30931,7 +30939,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/09/02</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/09/02，2026/09/17</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30942,7 +30950,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -31055,7 +31063,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/08/28</t>
+          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/08/28，2026/09/16</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -31066,7 +31074,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -31242,7 +31250,7 @@
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr">
         <is>
-          <t>三理Mit3uri</t>
+          <t>龙奔</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -31443,7 +31451,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11</t>
+          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11，2026/09/21</t>
         </is>
       </c>
       <c r="F775" t="inlineStr"/>
@@ -31454,7 +31462,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -31483,7 +31491,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07，2026/08/23</t>
+          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07，2026/08/23，2026/09/21</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
@@ -31494,7 +31502,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -31931,7 +31939,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/9/14，2026/9/14</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/09/14，2026/09/14，2026/09/26</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31942,7 +31950,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -32015,7 +32023,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>2026/02/09，2026/02/27，2026/03/09，2026/04/14，2026/05/25，2026/07/25</t>
+          <t>2026/02/09，2026/02/27，2026/03/09，2026/04/14，2026/05/25，2026/07/25，2026/09/22</t>
         </is>
       </c>
       <c r="F789" t="inlineStr"/>
@@ -32026,7 +32034,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -32219,7 +32227,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>2026/02/19</t>
+          <t>2026/02/19，2026/09/21</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
@@ -32230,7 +32238,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -32379,7 +32387,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/08/27</t>
+          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/08/27，2026/09/26</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
@@ -32390,7 +32398,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -32587,7 +32595,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16，2026/9/14，2026/9/14</t>
+          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F803" t="inlineStr"/>
@@ -32963,7 +32971,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/25，2026/03/28，2026/04/11，2026/04/20，2026/05/26，2026/07/05，2026/07/22</t>
+          <t>2026/03/13，2026/03/25，2026/03/28，2026/04/11，2026/04/20，2026/05/26，2026/07/05，2026/07/22，2026/09/23</t>
         </is>
       </c>
       <c r="F812" t="inlineStr"/>
@@ -32974,7 +32982,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -33323,7 +33331,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/06/17</t>
+          <t>2026/03/17，2026/06/17，2026/09/21</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
@@ -33334,7 +33342,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -34907,7 +34915,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23，2026/09/11</t>
+          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23，2026/09/11，2026/09/23</t>
         </is>
       </c>
       <c r="F859" t="inlineStr"/>
@@ -34918,7 +34926,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -34951,7 +34959,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02</t>
+          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02，2026/09/22</t>
         </is>
       </c>
       <c r="F860" t="inlineStr"/>
@@ -34962,7 +34970,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -35275,7 +35283,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>2026/06/16，2026/06/17，2026/06/25</t>
+          <t>2026/06/16，2026/06/17，2026/06/25，2026/09/21</t>
         </is>
       </c>
       <c r="F868" t="inlineStr"/>
@@ -35286,7 +35294,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -35603,7 +35611,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>2026/07/05，2026/07/07，2026/07/17</t>
+          <t>2026/07/05，2026/07/07，2026/07/17，2026/09/23</t>
         </is>
       </c>
       <c r="F876" t="inlineStr"/>
@@ -35614,7 +35622,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -35767,7 +35775,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/9/14</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/09/14</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -35971,7 +35979,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08</t>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
@@ -35982,7 +35990,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -36091,7 +36099,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/9/14</t>
+          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/09/14，2026/09/21</t>
         </is>
       </c>
       <c r="F888" t="inlineStr"/>
@@ -36102,7 +36110,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -36415,7 +36423,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11</t>
+          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21</t>
         </is>
       </c>
       <c r="F896" t="inlineStr"/>
@@ -36426,7 +36434,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -36495,7 +36503,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>2026/08/23</t>
+          <t>2026/08/23，2026/09/21，2026/09/26</t>
         </is>
       </c>
       <c r="F898" t="inlineStr"/>
@@ -36506,7 +36514,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -36859,7 +36867,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>2026/09/06，2026/09/11</t>
+          <t>2026/09/06，2026/09/11，2026/09/16</t>
         </is>
       </c>
       <c r="F907" t="inlineStr"/>
@@ -36870,7 +36878,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -36903,7 +36911,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>2026/09/13</t>
+          <t>2026/09/13，2026/09/21</t>
         </is>
       </c>
       <c r="F908" t="inlineStr"/>
@@ -36914,7 +36922,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -36943,7 +36951,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>2026/09/04</t>
+          <t>2026/09/04，2026/09/16，2026/09/22</t>
         </is>
       </c>
       <c r="F909" t="inlineStr"/>
@@ -36954,7 +36962,7 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -36975,7 +36983,11 @@
           <t>Better Dig Two</t>
         </is>
       </c>
-      <c r="C910" t="inlineStr"/>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>最好挖两座坟</t>
+        </is>
+      </c>
       <c r="D910" t="inlineStr">
         <is>
           <t>The Band Perry</t>
@@ -37003,6 +37015,202 @@
         </is>
       </c>
       <c r="J910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Let Her Go</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr"/>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Passenger</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>BV1MBeA6CEhH</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Say Something</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr"/>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>A Great Big World</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>BV1d7eg6gEGu</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>U&amp;I</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr"/>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>放課後ティータイム</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>2026/09/21</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>日语</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>BV1mzht6MEds</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>天天</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr"/>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>陶喆</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>2026/09/21</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>BV1kThz6fEeg</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>荷塘月色</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr"/>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>凤凰传奇</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>2026/09/26</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr"/>
+      <c r="J915" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,56 +425,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J915"/>
+  <dimension ref="A1:J932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>歌名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>歌名翻译</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>原唱</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>语言</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>歌切</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
@@ -571,7 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19</t>
+          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/10/03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -582,7 +594,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -619,7 +631,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/25，2025/03/28，2025/04/17，2025/05/03，2025/05/09，2025/05/16，2025/05/30，2025/06/14，2025/06/19，2025/07/05，2025/07/18，2025/08/21，2025/08/25，2025/09/05，2025/09/22，2025/09/26，2026/01/19，2026/01/21，2026/03/04，2026/04/16，2026/06/06，2026/06/18，2026/06/23，2026/08/25</t>
+          <t>2025/03/02，2025/03/25，2025/03/28，2025/04/17，2025/05/03，2025/05/09，2025/05/16，2025/05/30，2025/06/14，2025/06/19，2025/07/05，2025/07/18，2025/08/21，2025/08/25，2025/09/05，2025/09/22，2025/09/26，2026/01/19，2026/01/21，2026/03/04，2026/04/16，2026/06/06，2026/06/18，2026/06/23，2026/08/25，2026/10/03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -630,7 +642,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -991,7 +1003,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06，2026/09/23</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06，2026/09/23，2026/09/27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1002,7 +1014,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1071,7 +1083,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/03，2025/04/17，2025/05/22，2025/06/03，2025/07/24，2025/08/12，2025/09/03，2025/10/10，2025/11/09，2025/11/10，2026/03/13，2026/06/03，2026/09/08</t>
+          <t>2025/03/04，2025/04/03，2025/04/17，2025/05/22，2025/06/03，2025/07/24，2025/08/12，2025/09/03，2025/10/10，2025/11/09，2025/11/10，2026/03/13，2026/06/03，2026/09/08，2026/10/03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1082,7 +1094,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1271,7 +1283,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28，2026/09/17</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28，2026/09/17，2026/10/01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1282,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1471,7 +1483,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/07，2025/05/29，2025/06/06，2025/06/19，2025/06/26，2025/07/10，2025/07/11，2025/07/14，2025/08/02，2025/09/03，2025/09/26，2025/10/03，2025/11/09，2025/11/24，2025/11/26，2026/01/05，2026/01/30，2026/03/04，2026/06/17，2026/08/05</t>
+          <t>2025/03/04，2025/04/07，2025/05/29，2025/06/06，2025/06/19，2025/06/26，2025/07/10，2025/07/11，2025/07/14，2025/08/02，2025/09/03，2025/09/26，2025/10/03，2025/11/09，2025/11/24，2025/11/26，2026/01/05，2026/01/30，2026/03/04，2026/06/17，2026/08/05，2026/09/27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1551,7 +1563,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/08/28，2026/09/06</t>
+          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/08/28，2026/09/06，2026/09/27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1562,7 +1574,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1671,7 +1683,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25，2026/09/21</t>
+          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25，2026/09/21，2026/09/27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1682,7 +1694,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1711,7 +1723,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01，2026/09/02</t>
+          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01，2026/09/02，2026/09/27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1722,7 +1734,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2071,7 +2083,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26，2026/09/02</t>
+          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26，2026/09/02，2026/10/02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2082,7 +2094,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2291,7 +2303,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/28，2025/04/19，2025/04/24，2025/05/03，2025/05/15，2025/05/16，2025/05/22，2025/05/30，2025/06/14，2025/06/19，2025/06/26，2025/07/18，2025/08/04，2025/09/10，2025/09/18，2025/10/03，2026/02/07，2026/02/09，2026/02/27，2026/04/18，2026/06/06，2026/06/16，2026/06/17，2026/06/23</t>
+          <t>2025/03/06，2025/03/28，2025/04/19，2025/04/24，2025/05/03，2025/05/15，2025/05/16，2025/05/22，2025/05/30，2025/06/14，2025/06/19，2025/06/26，2025/07/18，2025/08/04，2025/09/10，2025/09/18，2025/10/03，2026/02/07，2026/02/09，2026/02/27，2026/04/18，2026/06/06，2026/06/16，2026/06/17，2026/06/23，2026/10/03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2306,7 +2318,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2583,7 +2595,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/25，2026/06/10</t>
+          <t>2025/03/07，2025/05/25，2026/06/10，2026/09/27</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -2594,7 +2606,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2703,7 +2715,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/02，2025/05/09，2025/05/29，2025/05/31，2025/10/01，2025/10/31</t>
+          <t>2025/03/07，2025/04/02，2025/05/09，2025/05/29，2025/05/31，2025/10/01，2025/10/31，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2714,7 +2726,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3327,7 +3339,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25，2026/09/08</t>
+          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25，2026/09/08，2026/10/02</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3338,7 +3350,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3371,7 +3383,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/01，2025/04/12，2025/04/28，2025/04/29，2025/05/09，2025/08/13，2025/08/24，2025/10/07，2025/11/12，2026/03/04，2026/07/26</t>
+          <t>2025/03/09，2025/04/01，2025/04/12，2025/04/28，2025/04/29，2025/05/09，2025/08/13，2025/08/24，2025/10/07，2025/11/12，2026/03/04，2026/07/26，2026/09/27</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -3382,7 +3394,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3739,7 +3751,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/04，2025/05/03，2025/06/15，2025/07/28，2025/09/04，2025/10/22，2026/03/04</t>
+          <t>2025/03/12，2025/04/04，2025/05/03，2025/06/15，2025/07/28，2025/09/04，2025/10/22，2026/03/04，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -3750,7 +3762,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3995,7 +4007,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/11，2025/04/26，2025/04/29，2025/05/18，2025/06/02，2025/06/27，2025/07/05，2025/07/15，2025/08/02，2025/09/10，2026/07/16</t>
+          <t>2025/03/13，2025/04/11，2025/04/26，2025/04/29，2025/05/18，2025/06/02，2025/06/27，2025/07/05，2025/07/15，2025/08/02，2025/09/10，2026/07/16，2026/09/27</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -4006,7 +4018,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4835,7 +4847,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/10/11，2025/11/14，2026/08/30</t>
+          <t>2025/03/14，2025/10/11，2025/11/14，2026/08/30，2026/09/27</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -4846,7 +4858,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5687,7 +5699,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/09/14，2026/09/14</t>
+          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/09/14，2026/09/14，2026/10/03</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5698,7 +5710,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5727,7 +5739,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06，2026/09/23</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06，2026/09/23，2026/09/27</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5738,7 +5750,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5767,7 +5779,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/09/04，2026/09/08</t>
+          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/09/04，2026/09/08，2026/10/03</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5778,7 +5790,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5807,7 +5819,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/27，2025/04/25，2025/05/01，2025/05/15，2025/06/10，2025/07/03，2025/09/11，2025/12/11，2026/01/09，2026/08/11</t>
+          <t>2025/03/17，2025/03/27，2025/04/25，2025/05/01，2025/05/15，2025/06/10，2025/07/03，2025/09/11，2025/12/11，2026/01/09，2026/08/11，2026/09/27</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -5818,7 +5830,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5847,7 +5859,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/07，2025/04/17，2025/04/28，2025/05/20，2025/06/03，2025/07/11，2025/08/04，2025/09/11，2025/09/24，2025/10/07，2025/11/26，2025/12/24，2026/02/07，2026/07/16</t>
+          <t>2025/03/17，2025/04/07，2025/04/17，2025/04/28，2025/05/20，2025/06/03，2025/07/11，2025/08/04，2025/09/11，2025/09/24，2025/10/07，2025/11/26，2025/12/24，2026/02/07，2026/07/16，2026/09/27</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -5858,7 +5870,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6087,7 +6099,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04，2026/10/01</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6098,7 +6110,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6167,7 +6179,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03，2026/09/26</t>
+          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03，2026/09/26，2026/10/01</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6178,7 +6190,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6895,7 +6907,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/13，2025/05/30，2025/06/06，2025/07/08，2025/08/07，2025/08/22，2025/09/30，2025/11/09，2025/11/13，2025/12/31，2026/04/16，2026/06/20，2026/09/08</t>
+          <t>2025/03/20，2025/04/17，2025/05/13，2025/05/30，2025/06/06，2025/07/08，2025/08/07，2025/08/22，2025/09/30，2025/11/09，2025/11/13，2025/12/31，2026/04/16，2026/06/20，2026/09/08，2026/10/03</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -6906,7 +6918,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -6935,7 +6947,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/06/26，2026/04/14，2026/06/10，2026/08/02</t>
+          <t>2025/03/20，2025/06/26，2026/04/14，2026/06/10，2026/08/02，2026/10/03</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -6946,7 +6958,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7135,7 +7147,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2025/03/21，2026/06/12，2026/08/02</t>
+          <t>2025/03/21，2026/06/12，2026/08/02，2026/09/29</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -7146,7 +7158,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7211,7 +7223,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23，2026/08/25</t>
+          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23，2026/08/25，2026/09/27</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -7222,7 +7234,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7331,7 +7343,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/09/02，2026/09/08，2026/09/22</t>
+          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27，2026/09/02，2026/09/08，2026/09/22，2026/10/03</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -7342,7 +7354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7371,7 +7383,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/09/14，2026/09/14，2026/09/22</t>
+          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/09/14，2026/09/14，2026/09/22，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -7382,7 +7394,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7735,7 +7747,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28，2026/09/17</t>
+          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28，2026/09/17，2026/10/01</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -7746,7 +7758,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7815,7 +7827,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25，2026/08/07</t>
+          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25，2026/08/07，2026/09/29</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -7826,7 +7838,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -7935,7 +7947,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/06/24，2026/05/20</t>
+          <t>2025/03/22，2025/06/24，2026/05/20，2026/09/27</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -7946,7 +7958,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -8295,7 +8307,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04，2026/09/21</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04，2026/09/21，2026/09/27</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8306,7 +8318,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8335,7 +8347,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/06/23，2026/01/09，2026/04/09</t>
+          <t>2025/03/24，2025/06/23，2026/01/09，2026/04/09，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -8346,7 +8358,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -8775,7 +8787,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09，2026/09/04</t>
+          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09，2026/09/04，2026/10/03</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -8786,7 +8798,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9263,7 +9275,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02，2026/09/17</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02，2026/09/17，2026/09/29</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9274,7 +9286,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9659,7 +9671,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02，2026/09/16</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02，2026/09/16，2026/09/27</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9670,7 +9682,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9983,7 +9995,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/09/04</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/09/04，2026/10/03</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -9994,7 +10006,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10271,7 +10283,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18，2026/08/30</t>
+          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19，2026/08/18，2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -10282,7 +10294,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -10311,7 +10323,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/24，2025/05/15，2025/05/29，2025/09/21，2025/09/27，2025/10/24，2026/01/05，2026/02/09，2026/03/15，2026/05/01</t>
+          <t>2025/03/30，2025/04/24，2025/05/15，2025/05/29，2025/09/21，2025/09/27，2025/10/24，2026/01/05，2026/02/09，2026/03/15，2026/05/01，2026/09/27</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -10322,7 +10334,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -10551,7 +10563,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18，2026/09/04</t>
+          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07，2026/08/18，2026/09/04，2026/10/03</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -10562,7 +10574,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -10631,7 +10643,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20，2026/08/27</t>
+          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20，2026/08/27，2026/10/03</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -10642,7 +10654,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -10671,7 +10683,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/05/15，2025/06/09，2025/09/03，2025/09/24，2026/01/05</t>
+          <t>2025/04/01，2025/05/15，2025/06/09，2025/09/03，2025/09/24，2026/01/05，2026/10/03</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -10682,7 +10694,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -10751,7 +10763,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28，2026/08/18，2026/09/08</t>
+          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28，2026/08/18，2026/09/08，2026/10/03</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -10762,7 +10774,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -11271,7 +11283,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/09/02</t>
+          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/09/02，2026/10/02</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -11282,7 +11294,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -11391,7 +11403,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/19，2025/05/09，2025/05/20，2025/06/26，2025/07/15，2025/09/30，2025/12/05，2026/05/20</t>
+          <t>2025/04/02，2025/04/19，2025/05/09，2025/05/20，2025/06/26，2025/07/15，2025/09/30，2025/12/05，2026/05/20，2026/09/27</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -11402,7 +11414,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -11675,7 +11687,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28，2026/09/22</t>
+          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28，2026/09/22，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11686,7 +11698,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -12351,7 +12363,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/09/14，2026/09/16</t>
+          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/09/14，2026/09/16，2026/10/01</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -12362,7 +12374,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -12431,7 +12443,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/17，2025/05/04，2025/05/24，2025/05/30，2025/09/19，2025/10/22，2025/11/13，2026/06/28</t>
+          <t>2025/04/06，2025/04/17，2025/05/04，2025/05/24，2025/05/30，2025/09/19，2025/10/22，2025/11/13，2026/06/28，2026/09/29</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -12442,7 +12454,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -12795,7 +12807,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25，2026/08/02，2026/08/21</t>
+          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25，2026/08/02，2026/08/21，2026/10/03</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -12806,7 +12818,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -13235,7 +13247,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20，2026/08/28</t>
+          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20，2026/08/28，2026/10/02</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -13246,7 +13258,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14247,7 +14259,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/10/31，2026/08/11，2026/09/23</t>
+          <t>2025/04/14，2025/10/31，2026/08/11，2026/09/23，2026/09/27</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -14258,7 +14270,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -14327,7 +14339,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20，2026/08/27</t>
+          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20，2026/08/27，2026/09/27</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -14338,7 +14350,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -15215,7 +15227,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/05/19，2025/07/06，2025/10/18，2025/11/13，2025/11/24，2025/12/16</t>
+          <t>2025/04/19，2025/05/19，2025/07/06，2025/10/18，2025/11/13，2025/11/24，2025/12/16，2026/09/29</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -15226,7 +15238,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -15375,7 +15387,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/02，2026/01/26，2026/06/28，2026/08/07</t>
+          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/02，2026/01/26，2026/06/28，2026/08/07，2026/10/02</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -15386,7 +15398,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -16595,7 +16607,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/04，2025/05/26，2025/06/08，2025/08/28，2025/10/18，2025/11/18，2025/12/24，2026/01/29，2026/02/27，2026/04/09，2026/04/20，2026/09/06</t>
+          <t>2025/04/27，2025/05/04，2025/05/26，2025/06/08，2025/08/28，2025/10/18，2025/11/18，2025/12/24，2026/01/29，2026/02/27，2026/04/09，2026/04/20，2026/09/06，2026/09/27</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -16606,7 +16618,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -16879,7 +16891,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27，2026/09/02</t>
+          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27，2026/09/02，2026/10/03</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -16890,7 +16902,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -16995,7 +17007,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2025/04/29，2025/05/03，2026/04/20，2026/09/11</t>
+          <t>2025/04/29，2025/05/03，2026/04/20，2026/09/11，2026/09/29</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -17006,7 +17018,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -17035,7 +17047,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>2025/05/01，2025/05/12</t>
+          <t>2025/05/01，2025/05/12，2026/09/27</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -17046,7 +17058,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -17275,7 +17287,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25，2026/08/30</t>
+          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25，2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -17286,7 +17298,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -17435,7 +17447,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/10/31，2026/04/14</t>
+          <t>2025/05/03，2025/10/31，2026/04/14，2026/10/01</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -17446,7 +17458,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -17475,7 +17487,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/10/31，2025/12/16</t>
+          <t>2025/05/03，2025/10/31，2025/12/16，2026/10/03</t>
         </is>
       </c>
       <c r="F423" t="inlineStr"/>
@@ -17486,7 +17498,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -17911,7 +17923,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2025/05/12，2025/05/31，2025/06/05，2025/06/15，2025/06/21，2025/06/27，2025/07/23，2025/08/24，2025/09/22，2025/12/19，2026/03/04，2026/06/03，2026/07/26</t>
+          <t>2025/05/12，2025/05/31，2025/06/05，2025/06/15，2025/06/21，2025/06/27，2025/07/23，2025/08/24，2025/09/22，2025/12/19，2026/03/04，2026/06/03，2026/07/26，2026/10/02</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -17922,7 +17934,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -18071,7 +18083,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2025/05/15，2025/09/03，2025/09/13，2026/04/20</t>
+          <t>2025/05/15，2025/09/03，2025/09/13，2026/04/20，2026/10/03</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -18082,7 +18094,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -18431,7 +18443,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/09/04</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/09/04，2026/09/27</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18442,7 +18454,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -18511,7 +18523,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16，2026/08/30</t>
+          <t>2025/05/19，2025/12/16，2025/12/24，2026/08/16，2026/08/30，2026/09/29</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -18522,7 +18534,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -18923,7 +18935,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/09/02</t>
+          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/09/02，2026/10/01</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -18934,7 +18946,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -19247,7 +19259,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/08/16，2026/09/12</t>
+          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/08/16，2026/09/12，2026/10/01</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -19258,7 +19270,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -19647,7 +19659,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/07/13，2025/10/31，2026/03/05，2026/08/08</t>
+          <t>2025/05/30，2025/07/13，2025/10/31，2026/03/05，2026/08/08，2026/10/03</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -19658,7 +19670,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -19687,7 +19699,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/08/30</t>
+          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -19698,7 +19710,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -19767,7 +19779,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28，2026/08/03，2026/08/23</t>
+          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28，2026/08/03，2026/08/23，2026/09/27</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -19778,7 +19790,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -19807,7 +19819,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2025/05/31，2025/06/02，2025/06/23，2025/09/15，2025/09/27，2025/10/17，2026/08/16</t>
+          <t>2025/05/31，2025/06/02，2025/06/23，2025/09/15，2025/09/27，2025/10/17，2026/08/16，2026/09/29</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -19818,7 +19830,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -20611,7 +20623,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/06/07，2025/06/12，2025/06/28，2025/08/13，2025/09/11，2025/09/30，2025/11/27，2026/08/27</t>
+          <t>2025/06/02，2025/06/07，2025/06/12，2025/06/28，2025/08/13，2025/09/11，2025/09/30，2025/11/27，2026/08/27，2026/09/27</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -20622,7 +20634,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -20891,7 +20903,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>2025/06/07，2025/11/24，2026/08/18</t>
+          <t>2025/06/07，2025/11/24，2026/08/18，2026/09/29</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -20902,7 +20914,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -21335,7 +21347,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>2025/06/16</t>
+          <t>2025/06/16，2026/09/29</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -21346,7 +21358,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -21775,7 +21787,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30，2026/10/01</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21786,7 +21798,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21979,7 +21991,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11，2026/09/06</t>
+          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11，2026/09/06，2026/10/02</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -21990,7 +22002,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -22179,7 +22191,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/19，2026/01/19，2026/08/16</t>
+          <t>2025/06/23，2025/10/19，2026/01/19，2026/08/16，2026/10/02</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -22190,7 +22202,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -22790,12 +22802,12 @@
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Selena Gomez/The Scene</t>
+          <t>Selena Gomez &amp; The Scene</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/10/31</t>
+          <t>2025/06/29，2025/10/31，2026/10/03</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -22806,7 +22818,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -22835,7 +22847,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2025/06/29，2026/08/30</t>
+          <t>2025/06/29，2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -22846,7 +22858,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -23035,7 +23047,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/06/30，2026/10/03</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -23046,7 +23058,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
@@ -23071,7 +23083,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>2025/06/30，2025/09/29</t>
+          <t>2025/06/30，2025/09/29，2026/09/29</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -23082,7 +23094,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -23231,7 +23243,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>2025/07/05，2025/10/23，2026/01/19</t>
+          <t>2025/07/05，2025/10/23，2026/01/19，2026/10/03</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -23242,7 +23254,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I566" t="inlineStr"/>
@@ -23267,7 +23279,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>2025/07/06，2025/07/18，2025/12/31，2026/04/09</t>
+          <t>2025/07/06，2025/07/18，2025/12/31，2026/04/09，2026/10/03</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -23278,7 +23290,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -23907,7 +23919,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/08/27</t>
+          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/08/27，2026/09/27</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -23918,7 +23930,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -24067,7 +24079,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23，2026/08/28</t>
+          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23，2026/08/28，2026/10/03</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -24078,7 +24090,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -24107,7 +24119,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11，2026/09/19</t>
+          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11，2026/09/19，2026/09/27</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -24118,7 +24130,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -24455,7 +24467,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/11，2025/09/17，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26</t>
+          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/11，2025/09/17，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26，2026/09/27</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -24466,7 +24478,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -24579,7 +24591,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/09/24，2025/10/28，2025/11/12，2025/12/16，2026/01/14，2026/01/30，2026/06/10，2026/07/26，2026/08/21</t>
+          <t>2025/07/26，2025/09/24，2025/10/28，2025/11/12，2025/12/16，2026/01/14，2026/01/30，2026/06/10，2026/07/26，2026/08/21，2026/09/27</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -24590,7 +24602,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -25455,7 +25467,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>2025/09/03，2026/04/20</t>
+          <t>2025/09/03，2026/04/20，2026/09/29</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -25466,7 +25478,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -26627,7 +26639,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>2025/09/15</t>
+          <t>2025/09/15，2026/10/02</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -26638,7 +26650,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
@@ -27279,7 +27291,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19，2026/08/30</t>
+          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31，2026/08/19，2026/08/30，2026/09/27</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -27290,7 +27302,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -27439,7 +27451,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>2025/09/27</t>
+          <t>2025/09/27，2026/09/29</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -27450,10 +27462,14 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I673" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>BV1SVaW6YEGG</t>
+        </is>
+      </c>
       <c r="J673" t="inlineStr"/>
     </row>
     <row r="674">
@@ -28599,7 +28615,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>2025/10/23，2026/08/16，2026/08/21，2026/09/04</t>
+          <t>2025/10/23，2026/08/16，2026/08/21，2026/09/04，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -28610,7 +28626,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -28639,7 +28655,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>2025/10/23，2025/10/25，2025/12/12，2026/01/19，2026/03/28，2026/08/21</t>
+          <t>2025/10/23，2025/10/25，2025/12/12，2026/01/19，2026/03/28，2026/08/21，2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -28650,7 +28666,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -28871,7 +28887,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/10/23，2026/10/03</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -28882,7 +28898,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I709" t="inlineStr"/>
@@ -30471,7 +30487,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>2025/12/11，2025/12/12，2025/12/17，2026/01/02，2026/01/05，2026/01/11，2026/01/17，2026/01/29，2026/02/09，2026/03/28，2026/04/29，2026/07/05，2026/07/26</t>
+          <t>2025/12/11，2025/12/12，2025/12/17，2026/01/02，2026/01/05，2026/01/11，2026/01/17，2026/01/29，2026/02/09，2026/03/28，2026/04/29，2026/07/05，2026/07/26，2026/09/27</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -30482,7 +30498,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -31451,7 +31467,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11，2026/09/21</t>
+          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11，2026/09/21，2026/10/02</t>
         </is>
       </c>
       <c r="F775" t="inlineStr"/>
@@ -31462,7 +31478,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -32107,7 +32123,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19，2026/08/25</t>
+          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19，2026/08/25，2026/10/03</t>
         </is>
       </c>
       <c r="F791" t="inlineStr"/>
@@ -32118,7 +32134,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -33059,7 +33075,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11</t>
+          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11，2026/10/01</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -33070,7 +33086,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -33795,7 +33811,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/09，2026/10/03</t>
         </is>
       </c>
       <c r="F832" t="inlineStr"/>
@@ -33806,7 +33822,7 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -33875,7 +33891,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/09，2026/09/27</t>
         </is>
       </c>
       <c r="F834" t="inlineStr"/>
@@ -33886,7 +33902,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -35447,7 +35463,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>2026/06/20，2026/06/30</t>
+          <t>2026/06/20，2026/06/30，2026/09/27</t>
         </is>
       </c>
       <c r="F872" t="inlineStr"/>
@@ -35458,7 +35474,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -35527,7 +35543,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>2026/06/25，2026/08/01，2026/08/11</t>
+          <t>2026/06/25，2026/08/01，2026/08/11，2026/09/27</t>
         </is>
       </c>
       <c r="F874" t="inlineStr"/>
@@ -35538,7 +35554,7 @@
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -35651,7 +35667,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11</t>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11，2026/10/01</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
@@ -35662,7 +35678,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -35979,7 +35995,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22</t>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22，2026/09/27</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
@@ -35990,7 +36006,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -36139,7 +36155,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/09/06</t>
+          <t>2026/08/11，2026/09/06，2026/09/27，2026/10/01</t>
         </is>
       </c>
       <c r="F889" t="inlineStr"/>
@@ -36150,7 +36166,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -36179,7 +36195,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11</t>
+          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11，2026/09/27</t>
         </is>
       </c>
       <c r="F890" t="inlineStr"/>
@@ -36190,7 +36206,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -36219,7 +36235,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/18，2026/09/27</t>
         </is>
       </c>
       <c r="F891" t="inlineStr"/>
@@ -36230,7 +36246,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -36423,7 +36439,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21</t>
+          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21，2026/09/27</t>
         </is>
       </c>
       <c r="F896" t="inlineStr"/>
@@ -36434,7 +36450,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -36503,7 +36519,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/09/21，2026/09/26</t>
+          <t>2026/08/23，2026/09/21，2026/09/26，2026/09/29</t>
         </is>
       </c>
       <c r="F898" t="inlineStr"/>
@@ -36514,7 +36530,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -36583,7 +36599,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/09/11</t>
+          <t>2026/08/30，2026/09/11，2026/10/02，2026/10/03</t>
         </is>
       </c>
       <c r="F900" t="inlineStr"/>
@@ -36594,7 +36610,7 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -36663,7 +36679,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/08/30</t>
+          <t>2026/08/30，2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F902" t="inlineStr"/>
@@ -36674,7 +36690,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -36703,7 +36719,7 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F903" t="inlineStr"/>
@@ -36714,7 +36730,7 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -37075,7 +37091,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/16，2026/09/29</t>
         </is>
       </c>
       <c r="F912" t="inlineStr"/>
@@ -37086,7 +37102,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -37209,8 +37225,692 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I915" t="inlineStr"/>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>BV1S7ax6BEWj</t>
+        </is>
+      </c>
       <c r="J915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>二十二</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr"/>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>陶喆</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>2026/09/27</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>BV1RWa36MEU2</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>American Boy</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr"/>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Estelle/Kanye West</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>2026/09/27</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>BV1BLa36CEdd</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>What Do You Mean?</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr"/>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Justin Bieber</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>2026/09/29，2026/10/03</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>BV1RAaW6gECq</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Say So</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr"/>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Doja Cat/Nicki Minaj</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>BV1mnaW6ZEKs</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>STAY</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr"/>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>The Kid LAROI/Justin Bieber</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>BV1fRap61EJi</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Galway Girl</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr"/>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Ed Sheeran</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>BV1mnaW6ZENW</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Stitches</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr"/>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Shawn Mendes</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>BV19KaW6MEw2</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Attention</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr"/>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Charlie Puth</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>2026/09/29，2026/10/03</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>BV1aQaW6qEXq</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>当你穿过我的身体</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr"/>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>汉堡黄</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>2026/09/29，2026/10/02</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>BV1MhaX6yEgC</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr"/>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Ellie Goulding</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>2026/10/02，2026/10/03</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>BV1SFHB6VETv</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr"/>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Ellie Goulding</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>2026/10/02，2026/10/03</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>BV1TAHB63EY6</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Beauty And A Beat</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr"/>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Justin Bieber/Nicki Minaj</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>BV1uZHq6yEpC</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Ass Back Home</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr"/>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Gym Class Heroes/Neon Hitch</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>BV1uZHq6yEor</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Maps</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Maroon 5</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>BV1uZHq6yEDC</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Just Dance</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr"/>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Lady Gaga/Colby O'Donis/RedOne</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>BV1TAHB63Epz</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>We Found Love</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr"/>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Rihanna/Calvin Harris</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>BV1TAHB63Ehs</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Hit The Lights</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr"/>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Selena Gomez &amp; The Scene</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>BV1TAHB63EGB</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J932"/>
+  <dimension ref="A1:J937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/02，2025/09/07，2025/09/17，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11，2026/09/12</t>
+          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/02，2025/09/07，2025/09/17，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11，2026/09/12，2026/10/09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/08/28，2026/09/04，2026/09/13</t>
+          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08，2026/08/28，2026/09/04，2026/09/13，2026/10/15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09，2026/09/02</t>
+          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09，2026/09/02，2026/10/10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/04/29，2026/06/25，2026/09/12</t>
+          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/04/29，2026/06/25，2026/09/12，2026/10/15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09，2026/07/31，2026/08/25</t>
+          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09，2026/07/31，2026/08/25，2026/10/16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/17，2025/06/02，2025/07/07，2025/07/14，2025/08/07，2025/09/04，2025/09/29，2025/11/07，2025/12/05，2026/05/21</t>
+          <t>2025/03/03，2025/04/17，2025/06/02，2025/07/07，2025/07/14，2025/08/07，2025/09/04，2025/09/29，2025/11/07，2025/12/05，2026/05/21，2026/10/06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31，2026/09/11，2026/09/13</t>
+          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31，2026/09/11，2026/09/13，2026/10/15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18，2026/09/06</t>
+          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18，2026/09/06，2026/10/06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06，2026/09/23，2026/09/27</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17，2026/08/28，2026/09/04，2026/09/06，2026/09/23，2026/09/27，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17，2026/09/06，2026/09/23</t>
+          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17，2026/09/06，2026/09/23，2026/10/06，2026/10/16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04，2026/09/22</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04，2026/09/22，2026/10/16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23，2026/09/17</t>
+          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23，2026/09/17，2026/10/16</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28，2026/09/17，2026/10/01</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26，2026/08/28，2026/09/17，2026/10/01，2026/10/13，2026/10/16</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25，2026/09/14，2026/09/22</t>
+          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09，2026/08/25，2026/09/14，2026/09/22，2026/10/16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/08/28，2026/08/28</t>
+          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/08/28，2026/08/28，2026/10/15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/05/09，2025/06/13，2025/06/19，2025/06/27，2025/07/10，2025/09/10，2025/09/19，2025/11/14，2025/12/31，2026/02/23，2026/04/16，2026/07/22</t>
+          <t>2025/03/04，2025/04/14，2025/05/09，2025/06/13，2025/06/19，2025/06/27，2025/07/10，2025/09/10，2025/09/19，2025/11/14，2025/12/31，2026/02/23，2026/04/16，2026/07/22，2026/10/15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1438,7 +1438,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>单依纯</t>
+          <t>周兴哲</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31，2026/08/25，2026/09/26</t>
+          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31，2026/08/25，2026/09/26，2026/10/16</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/08/28，2026/09/06，2026/09/27</t>
+          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31，2026/08/28，2026/09/06，2026/09/27，2026/10/10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/13，2025/05/06，2025/05/15，2025/05/25，2025/06/06，2025/06/23，2025/07/15，2025/07/26，2025/09/15，2025/09/24，2025/10/03，2025/11/26，2025/12/26，2026/01/10，2026/03/22，2026/06/17</t>
+          <t>2025/03/04，2025/04/13，2025/05/06，2025/05/15，2025/05/25，2025/06/06，2025/06/23，2025/07/15，2025/07/26，2025/09/15，2025/09/24，2025/10/03，2025/11/26，2025/12/26，2026/01/10，2026/03/22，2026/06/17，2026/10/10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21，2026/09/04，2026/09/06</t>
+          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/02，2025/09/12，2025/09/17，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27，2026/08/21，2026/09/04，2026/09/06，2026/10/09，2026/10/10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25，2026/09/21，2026/09/27</t>
+          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11，2026/08/25，2026/09/21，2026/09/27，2026/10/09</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/03，2025/04/14，2025/05/05，2025/05/15，2025/05/29，2025/06/20，2025/06/27，2025/08/07，2025/08/24，2025/09/17，2025/10/16，2025/11/10，2025/12/09，2025/12/17，2026/01/21，2026/02/12，2026/02/25，2026/07/27，2026/09/08</t>
+          <t>2025/03/06，2025/04/03，2025/04/14，2025/05/05，2025/05/15，2025/05/29，2025/06/20，2025/06/27，2025/08/07，2025/08/24，2025/09/17，2025/10/16，2025/11/10，2025/12/09，2025/12/17，2026/01/21，2026/02/12，2026/02/25，2026/07/27，2026/09/08，2026/10/15</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/06，2025/04/13，2025/04/22，2025/05/08，2025/05/09，2025/05/30，2025/06/08，2025/08/04，2025/09/18，2025/10/12，2025/11/21，2026/01/24，2026/02/14，2026/02/25，2026/04/10，2026/04/25，2026/09/23</t>
+          <t>2025/03/06，2025/04/06，2025/04/13，2025/04/22，2025/05/08，2025/05/09，2025/05/30，2025/06/08，2025/08/04，2025/09/18，2025/10/12，2025/11/21，2026/01/24，2026/02/14，2026/02/25，2026/04/10，2026/04/25，2026/09/23，2026/10/09</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/04，2025/04/19，2025/06/02，2025/06/17，2025/06/23，2025/07/20，2025/09/24，2025/10/09，2026/02/17，2026/03/07，2026/05/24，2026/09/16</t>
+          <t>2025/03/07，2025/04/04，2025/04/19，2025/06/02，2025/06/17，2025/06/23，2025/07/20，2025/09/24，2025/10/09，2026/02/17，2026/03/07，2026/05/24，2026/09/16，2026/10/11</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/25，2026/06/10，2026/09/27</t>
+          <t>2025/03/07，2025/05/25，2026/06/10，2026/09/27，2026/10/16</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/09/14</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07，2026/09/11</t>
+          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07，2026/09/11，2026/10/10</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27，2026/08/18</t>
+          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27，2026/08/18，2026/10/16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/08/28，2026/09/02，2026/09/11</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/08/28，2026/09/02，2026/09/11，2026/10/09</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18，2026/08/21，2026/08/28</t>
+          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18，2026/08/21，2026/08/28，2026/10/15</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04，2026/08/30</t>
+          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04，2026/08/30，2026/10/15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28，2026/09/14</t>
+          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27，2026/08/28，2026/09/14，2026/10/10，2026/10/10</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/09/02</t>
+          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/09/02，2026/10/16</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21，2026/09/16，2026/09/22</t>
+          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21，2026/09/16，2026/09/22，2026/10/13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02，2026/09/02</t>
+          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02，2026/09/02，2026/10/07</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/09/02</t>
+          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/09/02，2026/10/16</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/03，2025/05/26，2025/06/01，2025/06/06，2025/09/08，2025/09/12，2026/04/09，2026/06/20，2026/07/22，2026/09/13</t>
+          <t>2025/03/13，2025/04/03，2025/05/26，2025/06/01，2025/06/06，2025/09/08，2025/09/12，2026/04/09，2026/06/20，2026/07/22，2026/09/13，2026/10/15</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/30，2025/04/17，2025/04/21，2025/05/05，2025/05/13，2025/05/20，2025/06/06，2025/06/20，2025/06/27，2025/07/05，2025/07/31，2025/08/24，2025/08/29，2025/09/20，2025/09/30，2025/10/22，2025/11/26，2026/01/15，2026/02/14，2026/04/08，2026/05/20，2026/09/13</t>
+          <t>2025/03/13，2025/03/30，2025/04/17，2025/04/21，2025/05/05，2025/05/13，2025/05/20，2025/06/06，2025/06/20，2025/06/27，2025/07/05，2025/07/31，2025/08/24，2025/08/29，2025/09/20，2025/09/30，2025/10/22，2025/11/26，2026/01/15，2026/02/14，2026/04/08，2026/05/20，2026/09/13，2026/10/15</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/08/30，2026/09/04</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/08/30，2026/09/04，2026/10/10，2026/10/10</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/19，2025/05/20，2025/07/26，2025/08/16，2025/12/11，2026/04/09，2026/04/18，2026/07/22，2026/09/08</t>
+          <t>2025/03/14，2025/05/19，2025/05/20，2025/07/26，2025/08/16，2025/12/11，2026/04/09，2026/04/18，2026/07/22，2026/09/08，2026/10/09</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16，2026/09/21</t>
+          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16，2026/09/21，2026/10/10</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/08/30</t>
+          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/08/30，2026/10/10</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09，2026/07/31，2026/09/16</t>
+          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09，2026/07/31，2026/09/16，2026/10/14</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19，2026/09/04</t>
+          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19，2026/09/04，2026/10/10</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31，2026/08/27</t>
+          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31，2026/08/27，2026/10/16</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/08/30</t>
+          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/08/30，2026/10/16</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18，2026/08/25，2026/08/28，2026/09/06</t>
+          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18，2026/08/25，2026/08/28，2026/09/06，2026/10/10，2026/10/13，2026/10/16</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/05/12，2025/06/23，2025/09/04，2025/12/23，2026/05/05，2026/07/16，2026/08/25</t>
+          <t>2025/03/15，2025/05/12，2025/06/23，2025/09/04，2025/12/23，2026/05/05，2026/07/16，2026/08/25，2026/10/14</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/09/14，2026/09/14，2026/10/03</t>
+          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23，2026/08/18，2026/09/14，2026/09/14，2026/10/03，2026/10/10</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06，2026/09/23，2026/09/27</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11，2026/08/25，2026/09/06，2026/09/23，2026/09/27，2026/10/09，2026/10/16</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09，2026/08/02，2026/09/17</t>
+          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09，2026/08/02，2026/09/17，2026/10/16</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04，2026/10/01</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04，2026/10/01，2026/10/10</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03，2026/09/26，2026/10/01</t>
+          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03，2026/09/26，2026/10/01，2026/10/09</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09，2026/09/04</t>
+          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09，2026/09/04，2026/10/15</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25，2026/09/06，2026/09/21</t>
+          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17，2026/08/25，2026/09/06，2026/09/21，2026/10/16</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/08/28，2026/08/28，2026/09/26</t>
+          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11，2026/08/28，2026/08/28，2026/09/26，2026/10/10</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20，2026/08/28</t>
+          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20，2026/08/28，2026/10/15</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/08/30</t>
+          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/08/30，2026/10/10</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02，2026/08/02，2026/08/09</t>
+          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02，2026/08/02，2026/08/09，2026/10/16</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/22，2025/05/29，2025/06/03，2025/08/28，2025/09/11，2025/10/18，2025/10/30，2025/11/28，2025/12/28，2026/03/15，2026/05/19，2026/07/13，2026/09/16</t>
+          <t>2025/03/20，2025/05/22，2025/05/29，2025/06/03，2025/08/28，2025/09/11，2025/10/18，2025/10/30，2025/11/28，2025/12/28，2026/03/15，2026/05/19，2026/07/13，2026/09/16，2026/10/10</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06，2026/09/21</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06，2026/09/21，2026/10/06，2026/10/10</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/11，2025/04/22，2025/05/08，2025/06/12，2025/08/22，2025/08/29，2025/09/05，2025/11/19，2025/12/31，2026/02/14，2026/04/24</t>
+          <t>2025/03/20，2025/04/11，2025/04/22，2025/05/08，2025/06/12，2025/08/22，2025/08/29，2025/09/05，2025/11/19，2025/12/31，2026/02/14，2026/04/24，2026/10/13</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11，2026/09/26</t>
+          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11，2026/09/26，2026/10/09，2026/10/16</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7218,7 +7218,7 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>单依纯</t>
+          <t>陈韵若/陈每文</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/24，2025/06/05，2025/07/26，2025/09/21，2025/10/16，2025/10/30，2025/11/09，2026/01/09，2026/04/24，2026/05/23，2026/06/20，2026/07/19</t>
+          <t>2025/03/21，2025/04/24，2025/06/05，2025/07/26，2025/09/21，2025/10/16，2025/10/30，2025/11/09，2026/01/09，2026/04/24，2026/05/23，2026/06/20，2026/07/19，2026/10/16</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/09/14，2026/09/14，2026/09/22，2026/09/29，2026/10/03</t>
+          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27，2026/09/14，2026/09/14，2026/09/22，2026/09/29，2026/10/03，2026/10/16</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/03/29，2025/04/25，2025/05/30，2025/06/22，2025/07/18，2025/09/03，2025/09/13，2026/04/16，2026/08/23</t>
+          <t>2025/03/21，2025/03/29，2025/04/25，2025/05/30，2025/06/22，2025/07/18，2025/09/03，2025/09/13，2026/04/16，2026/08/23，2026/10/15</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28，2026/09/14，2026/09/22</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11，2026/08/28，2026/09/14，2026/09/22，2026/10/13</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/09/04</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/09/04，2026/10/07，2026/10/10，2026/10/10</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/04，2025/04/18，2025/04/25，2025/05/01，2025/05/25，2025/06/02，2025/06/06，2025/12/26，2026/01/21，2026/03/12</t>
+          <t>2025/03/21，2025/04/04，2025/04/18，2025/04/25，2025/05/01，2025/05/25，2025/06/02，2025/06/06，2025/12/26，2026/01/21，2026/03/12，2026/10/13</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28，2026/09/17，2026/10/01</t>
+          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27，2026/08/28，2026/09/17，2026/10/01，2026/10/13</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25，2026/08/07，2026/09/29</t>
+          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25，2026/08/07，2026/09/29，2026/10/13</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25，2026/09/14</t>
+          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08，2026/08/28，2026/08/28</t>
+          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08，2026/08/28，2026/08/28，2026/10/10，2026/10/10</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10，2026/09/04</t>
+          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10，2026/09/04，2026/10/10</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27，2026/09/04，2026/09/13</t>
+          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27，2026/09/04，2026/09/13，2026/10/15</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/02，2025/05/18，2025/06/19，2025/07/07，2025/09/04，2025/09/12，2026/01/19，2026/04/09</t>
+          <t>2025/03/24，2025/04/02，2025/05/18，2025/06/19，2025/07/07，2025/09/04，2025/09/12，2026/01/19，2026/04/09，2026/10/10</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/21，2025/04/21，2025/05/31，2025/12/19</t>
+          <t>2025/03/24，2025/04/21，2025/04/21，2025/05/31，2025/12/19，2026/10/15，2026/10/16</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04，2026/09/21，2026/09/27</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31，2026/09/04，2026/09/21，2026/09/27，2026/10/10，2026/10/13，2026/10/16，2026/10/16</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21，2026/09/14</t>
+          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23，2026/08/21，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/18，2025/06/02，2026/02/19，2026/05/23</t>
+          <t>2025/03/25，2025/04/18，2025/06/02，2026/02/19，2026/05/23，2026/10/13</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15，2026/08/28</t>
+          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15，2026/08/28，2026/10/16，2026/10/16</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18，2026/09/08，2026/09/16</t>
+          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28，2026/08/18，2026/09/08，2026/09/16，2026/10/05</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12，2026/08/07，2026/09/11</t>
+          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12，2026/08/07，2026/09/11，2026/10/15</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/29，2025/06/09，2025/07/24，2025/08/01，2025/08/03，2025/08/16，2025/09/08，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/01，2026/03/12，2026/04/01，2026/05/01，2026/06/10</t>
+          <t>2025/03/28，2025/04/29，2025/06/09，2025/07/24，2025/08/01，2025/08/03，2025/08/16，2025/09/08，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/01，2026/03/12，2026/04/01，2026/05/01，2026/06/10，2026/10/13，2026/10/16</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/03，2025/05/26，2025/11/09，2026/05/06，2026/06/10，2026/08/02</t>
+          <t>2025/03/28，2025/05/03，2025/05/26，2025/11/09，2026/05/06，2026/06/10，2026/08/02，2026/10/16</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02，2026/09/16，2026/09/27</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/08/16，2026/09/02，2026/09/16，2026/09/27，2026/10/13</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/01，2025/04/12，2025/04/14，2025/04/17，2025/04/18，2025/04/20，2025/04/29，2025/05/08，2025/05/20，2025/05/25，2025/06/03，2025/06/08，2025/06/14，2025/06/20，2025/07/05，2025/07/08，2025/07/17，2025/07/28，2025/08/07，2025/08/19，2025/08/28，2025/09/03，2025/09/20，2025/10/03，2025/10/26，2025/12/08，2025/12/12，2026/01/28，2026/03/07，2026/03/28，2026/04/19，2026/05/15，2026/07/27，2026/09/17</t>
+          <t>2025/03/29，2025/04/01，2025/04/12，2025/04/14，2025/04/17，2025/04/18，2025/04/20，2025/04/29，2025/05/08，2025/05/20，2025/05/25，2025/06/03，2025/06/08，2025/06/14，2025/06/20，2025/07/05，2025/07/08，2025/07/17，2025/07/28，2025/08/07，2025/08/19，2025/08/28，2025/09/03，2025/09/20，2025/10/03，2025/10/26，2025/12/08，2025/12/12，2026/01/28，2026/03/07，2026/03/28，2026/04/19，2026/05/15，2026/07/27，2026/09/17，2026/10/05</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/08/28，2026/08/30</t>
+          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02，2026/08/28，2026/08/30，2026/10/06</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31，2026/08/28</t>
+          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31，2026/08/28，2026/10/15</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/21，2025/05/19，2025/06/02，2025/07/03，2025/09/19，2025/10/16，2026/09/13</t>
+          <t>2025/04/02，2025/04/21，2025/05/19，2025/06/02，2025/07/03，2025/09/19，2025/10/16，2026/09/13，2026/10/14</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/04，2025/05/20，2025/06/23，2025/07/24，2025/09/12，2025/10/17，2025/12/09，2026/02/14，2026/03/25，2026/06/13，2026/07/28，2026/09/16</t>
+          <t>2025/04/02，2025/05/04，2025/05/20，2025/06/23，2025/07/24，2025/09/12，2025/10/17，2025/12/09，2026/02/14，2026/03/25，2026/06/13，2026/07/28，2026/09/16，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28，2026/09/14，2026/09/14，2026/09/14</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08，2026/08/28，2026/09/14，2026/09/14，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28，2026/09/22，2026/09/29，2026/10/03</t>
+          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22，2026/08/25，2026/08/28，2026/09/22，2026/09/29，2026/10/03，2026/10/16</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/11，2026/09/16</t>
+          <t>2025/04/04，2025/07/11，2026/09/16，2026/10/13</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/06/26，2026/03/13</t>
+          <t>2025/04/04，2025/06/26，2026/03/13，2026/10/13</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/09/14，2026/09/14</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/09/14，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/10，2025/06/20，2025/12/23，2026/04/09，2026/09/08</t>
+          <t>2025/04/06，2025/04/10，2025/06/20，2025/12/23，2026/04/09，2026/09/08，2026/10/10</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/08/21，2025/09/30</t>
+          <t>2025/04/06，2025/08/21，2025/09/30，2026/10/16</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/19，2025/10/11，2025/12/06</t>
+          <t>2025/04/07，2025/05/19，2025/10/11，2025/12/06，2026/10/16</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25，2026/09/06，2026/09/22</t>
+          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08，2026/08/19，2026/08/25，2026/09/06，2026/09/22，2026/10/06</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/08/28，2026/09/11，2026/09/16</t>
+          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02，2026/08/28，2026/09/11，2026/09/16，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/09/02，2026/09/14</t>
+          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27，2026/09/02，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2025/04/10，2025/05/19，2025/06/27，2025/08/21，2025/08/29，2025/09/17，2025/10/17，2025/10/30，2026/03/01，2026/03/29</t>
+          <t>2025/04/10，2025/05/19，2025/06/27，2025/08/21，2025/08/29，2025/09/17，2025/10/17，2025/10/30，2026/03/01，2026/03/29，2026/10/07</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25，2026/08/30，2026/09/14</t>
+          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18，2026/08/25，2026/08/30，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/11，2025/09/12，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15，2026/08/02</t>
+          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/11，2025/09/12，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15，2026/08/02，2026/10/10</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/18，2025/04/25，2025/04/29，2025/05/30，2025/06/09，2025/06/13，2025/06/26，2025/07/05，2025/07/14，2025/08/21，2025/09/10，2025/10/09，2025/11/21，2026/01/22</t>
+          <t>2025/04/11，2025/04/18，2025/04/25，2025/04/29，2025/05/30，2025/06/09，2025/06/13，2025/06/26，2025/07/05，2025/07/14，2025/08/21，2025/09/10，2025/10/09，2025/11/21，2026/01/22，2026/10/13</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/09/02</t>
+          <t>2025/04/11，2025/09/02，2026/10/06</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/08/28，2026/09/04</t>
+          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/08/28，2026/09/04，2026/10/10</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/09/04，2026/09/16</t>
+          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23，2026/09/04，2026/09/16，2026/10/13</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16，2026/09/02</t>
+          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16，2026/09/02，2026/10/10</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09，2026/09/14，2026/09/14</t>
+          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09，2026/09/14，2026/09/14，2026/10/16</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/04/20，2025/05/18，2025/05/20，2025/05/25，2025/06/28，2025/06/30，2025/08/24，2025/09/26，2026/01/09，2026/04/17，2026/09/17</t>
+          <t>2025/04/15，2025/04/18，2025/04/20，2025/05/18，2025/05/20，2025/05/25，2025/06/28，2025/06/30，2025/08/24，2025/09/26，2026/01/09，2026/04/17，2026/09/17，2026/10/13</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06，2026/09/22</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06，2026/09/22，2026/10/16</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/10/01，2026/01/23</t>
+          <t>2025/04/18，2025/10/01，2026/01/23，2026/10/06</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25，2026/08/11，2026/08/25</t>
+          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25，2026/08/11，2026/08/25，2026/10/13</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/04/25，2025/05/22，2025/07/03，2025/07/11，2025/07/26，2025/09/08，2025/10/03，2025/12/02，2026/01/25，2026/06/06</t>
+          <t>2025/04/19，2025/04/25，2025/05/22，2025/07/03，2025/07/11，2025/07/26，2025/09/08，2025/10/03，2025/12/02，2026/01/25，2026/06/06，2026/10/13</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11，2026/09/22</t>
+          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11，2026/09/22，2026/10/15</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/09/15，2025/10/11，2026/01/05，2026/06/03，2026/07/26</t>
+          <t>2025/04/21，2025/09/15，2025/10/11，2026/01/05，2026/06/03，2026/07/26，2026/10/07</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/23，2025/12/05，2026/02/14，2026/04/09，2026/04/24</t>
+          <t>2025/04/25，2025/06/23，2025/12/05，2026/02/14，2026/04/09，2026/04/24，2026/10/13</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31，2026/08/25</t>
+          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31，2026/08/25，2026/10/10</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09，2026/09/14</t>
+          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09，2026/09/14，2026/10/06</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/29，2025/06/17，2025/07/11，2025/08/03，2025/09/22，2026/04/09，2026/06/23</t>
+          <t>2025/04/27，2025/05/29，2025/06/17，2025/07/11，2025/08/03，2025/09/22，2026/04/09，2026/06/23，2026/10/13</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/20，2025/06/08，2025/08/18，2025/09/11，2025/11/03，2026/07/09</t>
+          <t>2025/04/27，2025/05/20，2025/06/08，2025/08/18，2025/09/11，2025/11/03，2026/07/09，2026/10/15</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -16782,7 +16782,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/08/28，2026/09/04，2026/09/11</t>
+          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/08/28，2026/09/04，2026/09/11，2026/10/13</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/09/02，2026/09/22</t>
+          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07，2026/09/02，2026/09/22，2026/10/13</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>2025/05/12，2025/05/22，2025/05/25，2025/07/20，2025/09/12，2026/01/15，2026/01/24，2026/01/30，2026/04/08，2026/05/04，2026/05/23</t>
+          <t>2025/05/12，2025/05/22，2025/05/25，2025/07/20，2025/09/12，2026/01/15，2026/01/24，2026/01/30，2026/04/08，2026/05/04，2026/05/23，2026/10/06，2026/10/16</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>2025/05/17，2025/06/05，2025/07/07，2025/12/16</t>
+          <t>2025/05/17，2025/06/05，2025/07/07，2025/12/16，2026/10/06</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10，2026/08/28，2026/08/28</t>
+          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10，2026/08/28，2026/08/28，2026/10/16</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/11/28，2026/04/01</t>
+          <t>2025/05/18，2025/11/28，2026/04/01，2026/10/16</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/09/04，2026/09/27</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11，2026/08/25，2026/09/04，2026/09/27，2026/10/16</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23，2026/08/11，2026/09/06</t>
+          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23，2026/08/11，2026/09/06，2026/10/13</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19，2026/09/14，2026/09/14，2026/09/22</t>
+          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19，2026/09/14，2026/09/14，2026/09/22，2026/10/10，2026/10/10</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/06/17，2025/07/21，2025/08/16，2025/10/16，2025/12/02，2026/04/22，2026/06/23，2026/07/05</t>
+          <t>2025/05/22，2025/06/17，2025/07/21，2025/08/16，2025/10/16，2025/12/02，2026/04/22，2026/06/23，2026/07/05，2026/10/06</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/05/29，2025/09/02，2025/09/17，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07，2026/08/25</t>
+          <t>2025/05/23，2025/05/29，2025/09/02，2025/09/17，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07，2026/08/25，2026/10/10</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2025/05/25，2025/06/26，2025/09/13</t>
+          <t>2025/05/25，2025/06/26，2025/09/13，2026/10/16</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16，2026/08/23，2026/09/22，2026/09/23</t>
+          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16，2026/08/23，2026/09/22，2026/09/23，2026/10/09</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>2025/05/29，2025/09/19，2025/11/26</t>
+          <t>2025/05/29，2025/09/19，2025/11/26，2026/10/06</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -19510,7 +19510,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2025/06/01，2026/01/23，2026/02/02，2026/02/23，2026/03/05，2026/03/17，2026/04/24，2026/05/16，2026/09/13</t>
+          <t>2025/06/01，2026/01/23，2026/02/02，2026/02/23，2026/03/05，2026/03/17，2026/04/24，2026/05/16，2026/09/13，2026/10/15</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -20434,7 +20434,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>2025/06/12，2025/06/27，2025/07/07，2026/01/01，2026/01/15</t>
+          <t>2025/06/12，2025/06/27，2025/07/07，2026/01/01，2026/01/15，2026/10/16</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31，2026/08/21，2026/09/11</t>
+          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31，2026/08/21，2026/09/11，2026/10/05，2026/10/16</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30，2026/10/01</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30，2026/10/01，2026/10/10</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/23，2025/09/29，2026/01/09，2026/02/10，2026/09/21</t>
+          <t>2025/06/20，2025/06/23，2025/09/29，2026/01/09，2026/02/10，2026/09/21，2026/10/13</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/09/06</t>
+          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/09/06，2026/10/06</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -22475,7 +22475,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>2025/06/27，2025/09/08，2025/10/13，2025/10/16，2026/01/24，2026/02/09，2026/03/06，2026/03/22，2026/04/11，2026/04/30，2026/05/26，2026/06/18，2026/08/03</t>
+          <t>2025/06/27，2025/09/08，2025/10/13，2025/10/16，2026/01/24，2026/02/09，2026/03/06，2026/03/22，2026/04/11，2026/04/30，2026/05/26，2026/06/18，2026/08/03，2026/10/09</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -23061,7 +23061,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I561" t="inlineStr"/>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>BV1MdHv6MExg</t>
+        </is>
+      </c>
       <c r="J561" t="inlineStr"/>
     </row>
     <row r="562">
@@ -23203,7 +23207,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06，2026/09/02</t>
+          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06，2026/09/02，2026/10/14</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -23214,7 +23218,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -23257,7 +23261,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>BV14AHB63EkZ</t>
+        </is>
+      </c>
       <c r="J566" t="inlineStr"/>
     </row>
     <row r="567">
@@ -23879,7 +23887,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>2025/07/13，2025/08/26，2025/12/17，2026/09/16</t>
+          <t>2025/07/13，2025/08/26，2025/12/17，2026/09/16，2026/10/11</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -23890,7 +23898,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -23919,7 +23927,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/08/27，2026/09/27</t>
+          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26，2026/08/27，2026/09/27，2026/10/10</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -23930,7 +23938,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -24039,7 +24047,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/07/15，2026/10/06</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -24050,7 +24058,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -24119,7 +24127,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11，2026/09/19，2026/09/27</t>
+          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11，2026/09/19，2026/09/27，2026/10/16</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -24130,7 +24138,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -24467,7 +24475,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/11，2025/09/17，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26，2026/09/27</t>
+          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/11，2025/09/17，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26，2026/09/27，2026/10/15</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -24478,7 +24486,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -24671,7 +24679,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/08/08，2026/07/22，2026/09/14，2026/09/14，2026/09/14</t>
+          <t>2025/07/26，2025/08/08，2026/07/22，2026/09/14，2026/09/14，2026/09/14，2026/10/10</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -24682,7 +24690,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -24751,7 +24759,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22，2026/08/27，2026/09/08</t>
+          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22，2026/08/27，2026/09/08，2026/10/15</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -24762,7 +24770,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -25023,7 +25031,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31，2026/08/25，2026/09/06</t>
+          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31，2026/08/25，2026/09/06，2026/10/09，2026/10/13</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -25034,7 +25042,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -25183,7 +25191,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>2025/08/21，2026/01/16，2026/02/02，2026/03/17，2026/04/08，2026/06/14，2026/08/02</t>
+          <t>2025/08/21，2026/01/16，2026/02/02，2026/03/17，2026/04/08，2026/06/14，2026/08/02，2026/10/10</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -25194,7 +25202,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -26327,7 +26335,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30，2026/09/16</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30，2026/09/16，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26338,7 +26346,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -26599,7 +26607,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>2025/09/15，2026/03/13，2026/08/02</t>
+          <t>2025/09/15，2026/03/13，2026/08/02，2026/10/06</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -26610,7 +26618,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -26653,7 +26661,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I652" t="inlineStr"/>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>BV19GH86wERi</t>
+        </is>
+      </c>
       <c r="J652" t="inlineStr"/>
     </row>
     <row r="653">
@@ -26911,7 +26923,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/09/04，2026/09/17</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31，2026/08/23，2026/09/04，2026/09/17，2026/10/09</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26922,7 +26934,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -27179,7 +27191,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22，2026/09/11</t>
+          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22，2026/09/11，2026/10/13，2026/10/16</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -27190,7 +27202,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -27371,7 +27383,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>2025/09/26，2025/11/18，2026/01/09，2026/02/25，2026/03/29</t>
+          <t>2025/09/26，2025/11/18，2026/01/09，2026/02/25，2026/03/29，2026/10/06</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -27382,7 +27394,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -27611,7 +27623,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>2025/09/29，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/06，2026/01/15，2026/01/19，2026/03/07，2026/05/05，2026/09/11</t>
+          <t>2025/09/29，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/06，2026/01/15，2026/01/19，2026/03/07，2026/05/05，2026/09/11，2026/10/15</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -27622,7 +27634,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -28043,7 +28055,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>2025/10/09，2025/11/17</t>
+          <t>2025/10/09，2025/11/17，2026/10/06</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -28054,7 +28066,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -28299,7 +28311,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>2025/10/17，2025/10/18，2025/10/23，2025/12/30，2026/01/12，2026/03/29，2026/09/16</t>
+          <t>2025/10/17，2025/10/18，2025/10/23，2025/12/30，2026/01/12，2026/03/29，2026/09/16，2026/10/13</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -28310,7 +28322,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -28901,7 +28913,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I709" t="inlineStr"/>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>BV1TAHB63Eyt</t>
+        </is>
+      </c>
       <c r="J709" t="inlineStr"/>
     </row>
     <row r="710">
@@ -29043,7 +29059,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>2025/10/25，2025/12/02，2026/02/23</t>
+          <t>2025/10/25，2025/12/02，2026/02/23，2026/10/06，2026/10/13</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -29054,7 +29070,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -29083,7 +29099,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16，2026/09/02</t>
+          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/08/16，2026/09/02，2026/10/16</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -29094,7 +29110,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -30131,7 +30147,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>2025/11/28，2026/09/02</t>
+          <t>2025/11/28，2026/09/02，2026/10/06</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -30142,7 +30158,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -30403,7 +30419,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>2025/12/09，2026/02/02，2026/04/14，2026/09/06</t>
+          <t>2025/12/09，2026/02/02，2026/04/14，2026/09/06，2026/10/06</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -30414,7 +30430,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -30447,7 +30463,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/08/16，2026/09/06</t>
+          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/08/16，2026/09/06，2026/10/16</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -30458,7 +30474,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -30955,7 +30971,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/09/02，2026/09/17</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08，2026/08/19，2026/09/02，2026/09/17，2026/10/13</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30966,7 +30982,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -31079,7 +31095,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/08/28，2026/09/16</t>
+          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01，2026/08/28，2026/09/16，2026/10/13</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -31090,7 +31106,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -31467,7 +31483,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11，2026/09/21，2026/10/02</t>
+          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27，2026/09/11，2026/09/21，2026/10/02，2026/10/16</t>
         </is>
       </c>
       <c r="F775" t="inlineStr"/>
@@ -31478,7 +31494,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -31507,7 +31523,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07，2026/08/23，2026/09/21</t>
+          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07，2026/08/23，2026/09/21，2026/10/13</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
@@ -31518,7 +31534,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -31795,7 +31811,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27，2026/07/31，2026/07/31，2026/08/11</t>
+          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27，2026/07/31，2026/07/31，2026/08/11，2026/10/15</t>
         </is>
       </c>
       <c r="F783" t="inlineStr"/>
@@ -31806,7 +31822,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -31835,7 +31851,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>2026/02/07，2026/04/19</t>
+          <t>2026/02/07，2026/04/19，2026/10/10</t>
         </is>
       </c>
       <c r="F784" t="inlineStr"/>
@@ -31846,7 +31862,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -31955,7 +31971,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/09/14，2026/09/14，2026/09/26</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/09/14，2026/09/14，2026/09/26，2026/10/15</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31966,7 +31982,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -32447,7 +32463,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>2026/02/23</t>
+          <t>2026/02/23，2026/10/10</t>
         </is>
       </c>
       <c r="F799" t="inlineStr"/>
@@ -32458,7 +32474,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -33075,7 +33091,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11，2026/10/01</t>
+          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11，2026/10/01，2026/10/10</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -33086,7 +33102,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -33271,7 +33287,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/03/17，2026/10/06</t>
         </is>
       </c>
       <c r="F819" t="inlineStr"/>
@@ -33282,10 +33298,14 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I819" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>BV12BpM6ZEes</t>
+        </is>
+      </c>
       <c r="J819" t="inlineStr"/>
     </row>
     <row r="820">
@@ -33427,7 +33447,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21，2026/09/11</t>
+          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21，2026/09/11，2026/10/06，2026/10/10</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -33438,7 +33458,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -34131,7 +34151,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>2026/04/14，2026/06/14</t>
+          <t>2026/04/14，2026/06/14，2026/10/06</t>
         </is>
       </c>
       <c r="F840" t="inlineStr"/>
@@ -34142,7 +34162,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -34335,7 +34355,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02，2026/09/06</t>
+          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02，2026/09/06，2026/10/13，2026/10/16，2026/10/16</t>
         </is>
       </c>
       <c r="F845" t="inlineStr"/>
@@ -34346,7 +34366,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -34715,7 +34735,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/08/02，2026/08/30</t>
+          <t>2026/05/01，2026/08/02，2026/08/30，2026/10/13</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -34726,7 +34746,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -35055,7 +35075,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/06，2026/10/06</t>
         </is>
       </c>
       <c r="F862" t="inlineStr"/>
@@ -35066,7 +35086,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -35095,7 +35115,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>2026/06/10</t>
+          <t>2026/06/10，2026/10/06</t>
         </is>
       </c>
       <c r="F863" t="inlineStr"/>
@@ -35106,7 +35126,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -35175,7 +35195,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/09/04</t>
+          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/09/04，2026/10/10</t>
         </is>
       </c>
       <c r="F865" t="inlineStr"/>
@@ -35186,7 +35206,7 @@
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
@@ -35627,7 +35647,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>2026/07/05，2026/07/07，2026/07/17，2026/09/23</t>
+          <t>2026/07/05，2026/07/07，2026/07/17，2026/09/23，2026/10/13</t>
         </is>
       </c>
       <c r="F876" t="inlineStr"/>
@@ -35638,7 +35658,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -35667,7 +35687,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11，2026/10/01</t>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11，2026/10/01，2026/10/07，2026/10/10，2026/10/15</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
@@ -35678,7 +35698,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -35791,7 +35811,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/09/14</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/09/14，2026/10/10，2026/10/15</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -35802,7 +35822,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -35831,7 +35851,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/09/02</t>
+          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/09/02，2026/10/09</t>
         </is>
       </c>
       <c r="F881" t="inlineStr"/>
@@ -35842,7 +35862,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -35995,7 +36015,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22，2026/09/27</t>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22，2026/09/27，2026/10/10</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
@@ -36006,7 +36026,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -36115,7 +36135,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/09/14，2026/09/21</t>
+          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/09/14，2026/09/21，2026/10/05，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F888" t="inlineStr"/>
@@ -36126,7 +36146,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -36155,7 +36175,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/09/06，2026/09/27，2026/10/01</t>
+          <t>2026/08/11，2026/09/06，2026/09/27，2026/10/01，2026/10/16</t>
         </is>
       </c>
       <c r="F889" t="inlineStr"/>
@@ -36166,7 +36186,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -36195,7 +36215,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11，2026/09/27</t>
+          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11，2026/09/27，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F890" t="inlineStr"/>
@@ -36206,7 +36226,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -36235,7 +36255,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/09/27</t>
+          <t>2026/08/18，2026/09/27，2026/10/16</t>
         </is>
       </c>
       <c r="F891" t="inlineStr"/>
@@ -36246,7 +36266,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -36439,7 +36459,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21，2026/09/27</t>
+          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21，2026/09/27，2026/10/09，2026/10/13</t>
         </is>
       </c>
       <c r="F896" t="inlineStr"/>
@@ -36450,7 +36470,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -36519,7 +36539,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/09/21，2026/09/26，2026/09/29</t>
+          <t>2026/08/23，2026/09/21，2026/09/26，2026/09/29，2026/10/09</t>
         </is>
       </c>
       <c r="F898" t="inlineStr"/>
@@ -36530,7 +36550,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -36639,7 +36659,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/30，2026/10/13</t>
         </is>
       </c>
       <c r="F901" t="inlineStr"/>
@@ -36650,7 +36670,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -36759,7 +36779,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/09/02</t>
+          <t>2026/08/30，2026/09/02，2026/10/16</t>
         </is>
       </c>
       <c r="F904" t="inlineStr"/>
@@ -36770,7 +36790,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -36843,7 +36863,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>2026/09/11</t>
+          <t>2026/09/11，2026/10/06，2026/10/09</t>
         </is>
       </c>
       <c r="F906" t="inlineStr"/>
@@ -36854,7 +36874,7 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -36883,7 +36903,7 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>2026/09/06，2026/09/11，2026/09/16</t>
+          <t>2026/09/06，2026/09/11，2026/09/16，2026/10/11，2026/10/14</t>
         </is>
       </c>
       <c r="F907" t="inlineStr"/>
@@ -36894,7 +36914,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -37091,7 +37111,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>2026/09/16，2026/09/29</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="F912" t="inlineStr"/>
@@ -37102,7 +37122,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -37171,7 +37191,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>2026/09/21</t>
+          <t>2026/09/21，2026/10/13</t>
         </is>
       </c>
       <c r="F914" t="inlineStr"/>
@@ -37182,7 +37202,7 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
@@ -37571,7 +37591,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>2026/09/29，2026/10/02</t>
+          <t>2026/09/29，2026/10/02，2026/10/05，2026/10/14</t>
         </is>
       </c>
       <c r="F924" t="inlineStr"/>
@@ -37582,7 +37602,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -37627,7 +37647,7 @@
       </c>
       <c r="I925" t="inlineStr">
         <is>
-          <t>BV1SFHB6VETv</t>
+          <t>BV118H86SE3N，BV1SFHB6VETv</t>
         </is>
       </c>
       <c r="J925" t="inlineStr"/>
@@ -37667,7 +37687,7 @@
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>BV1TAHB63EY6</t>
+          <t>BV1vDH86KEfx，BV1TAHB63EY6</t>
         </is>
       </c>
       <c r="J926" t="inlineStr"/>
@@ -37911,6 +37931,210 @@
         </is>
       </c>
       <c r="J932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Love wins all</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>爱胜过一切</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>IU</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>韩语</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>BV1SjHt6DEsu</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>娱乐人生</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr"/>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>陈蕾</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>粤语</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>BV1GkpN6bEaa</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>让她降落</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr"/>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>何璐</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>BV1GkpN6bE8n</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>你若成风</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr"/>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>许嵩/莫诗旎</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>BV1HwpK61Ega</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>0+0</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr"/>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>한로로</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>2026/10/09，2026/10/10，2026/10/14</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>韩语</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>BV1kWp86mE6M</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J937"/>
+  <dimension ref="A1:J943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>歌名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>歌名翻译</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>原唱</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>语言</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>次数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>歌切</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
@@ -499,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/01/23，2026/03/01，2026/03/22，2026/03/27，2026/06/28，2026/07/22，2026/09/23</t>
+          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/01/23，2026/03/01，2026/03/22，2026/03/27，2026/06/28，2026/07/22，2026/09/23，2026/10/25，2026/10/25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -510,7 +498,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -583,7 +571,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/10/03</t>
+          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/10/03，2026/10/23，2026/10/25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -594,7 +582,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -759,7 +747,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08，2026/09/02</t>
+          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08，2026/09/02，2026/10/24，2026/10/25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -770,7 +758,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -799,7 +787,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/04/29，2026/06/25，2026/09/12，2026/10/15</t>
+          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/01/29，2026/04/29，2026/06/25，2026/09/12，2026/10/15，2026/10/25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -810,12 +798,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BV1yd9xBEEC8，BV1pbEuzFEaX</t>
+          <t>BV1yd9xBEEC8，BV1pbEuzFEaX，BV1Xx6cBRE14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -919,7 +907,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31，2026/09/11，2026/09/13，2026/10/15</t>
+          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31，2026/09/11，2026/09/13，2026/10/15，2026/10/18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -930,7 +918,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -963,7 +951,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18，2026/09/06，2026/10/06</t>
+          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27，2026/08/18，2026/09/06，2026/10/06，2026/10/24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -974,7 +962,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1123,7 +1111,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04，2026/09/22，2026/10/16</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28，2026/08/30，2026/09/04，2026/09/22，2026/10/16，2026/10/24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1134,7 +1122,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1203,7 +1191,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/29，2025/05/20，2025/07/13，2025/07/25，2025/07/31，2025/10/09，2025/12/02，2026/01/09，2026/03/21，2026/07/19，2026/09/13</t>
+          <t>2025/03/04，2025/04/29，2025/05/20，2025/07/13，2025/07/25，2025/07/31，2025/10/09，2025/12/02，2026/01/09，2026/03/21，2026/07/19，2026/09/13，2026/10/19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1214,7 +1202,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1243,7 +1231,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23，2026/09/17，2026/10/16</t>
+          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23，2026/09/17，2026/10/16，2026/10/19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1254,7 +1242,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1363,7 +1351,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/08/28，2026/08/28，2026/10/15</t>
+          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15，2026/08/21，2026/08/28，2026/08/28，2026/10/15，2026/10/24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1374,7 +1362,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1443,7 +1431,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/08/16，2026/09/23</t>
+          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/08/16，2026/09/23，2026/10/19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1454,7 +1442,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1883,7 +1871,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/21，2025/04/05，2025/04/14，2025/04/24，2025/05/20，2025/06/05，2025/06/17，2025/06/23，2025/06/26，2025/08/12，2025/08/21，2025/09/14，2025/09/24，2025/10/16，2025/10/24，2025/12/17，2026/02/14，2026/03/08，2026/04/25，2026/05/21，2026/07/18，2026/07/28</t>
+          <t>2025/03/04，2025/03/21，2025/04/05，2025/04/14，2025/04/24，2025/05/20，2025/06/05，2025/06/17，2025/06/23，2025/06/26，2025/08/12，2025/08/21，2025/09/14，2025/09/24，2025/10/16，2025/10/24，2025/12/17，2026/02/14，2026/03/08，2026/04/25，2026/05/21，2026/07/18，2026/07/28，2026/10/19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1894,7 +1882,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1923,7 +1911,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17，2026/09/14，2026/09/14</t>
+          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17，2026/09/14，2026/09/14，2026/10/24</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1934,7 +1922,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2043,7 +2031,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17，2026/09/02</t>
+          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17，2026/09/02，2026/10/24</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2054,7 +2042,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2123,7 +2111,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22，2026/08/11，2026/09/21</t>
+          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22，2026/08/11，2026/09/21，2026/10/24</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2134,7 +2122,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2255,7 +2243,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19，2026/09/05，2026/09/19</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05，2026/08/19，2026/09/05，2026/09/19，2026/10/23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2266,7 +2254,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2675,7 +2663,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/09/14，2026/10/10</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20，2026/08/30，2026/09/14，2026/10/10，2026/10/22</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2686,7 +2674,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2795,7 +2783,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07，2026/09/11，2026/10/10</t>
+          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07，2026/09/11，2026/10/10，2026/10/24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2806,7 +2794,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2883,7 +2871,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27，2026/08/18，2026/10/16</t>
+          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27，2026/08/18，2026/10/16，2026/10/24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2894,7 +2882,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2923,7 +2911,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/04，2025/04/12，2025/04/18，2025/04/24，2025/06/17，2025/06/19，2025/07/11，2025/07/18，2025/08/28，2025/09/05，2025/09/08，2025/09/27，2025/10/03，2025/12/11，2025/12/30，2026/01/21，2026/01/25，2026/02/10，2026/02/23，2026/03/06，2026/03/22，2026/04/24，2026/08/19</t>
+          <t>2025/03/07，2025/04/04，2025/04/12，2025/04/18，2025/04/24，2025/06/17，2025/06/19，2025/07/11，2025/07/18，2025/08/28，2025/09/05，2025/09/08，2025/09/27，2025/10/03，2025/12/11，2025/12/30，2026/01/21，2026/01/25，2026/02/10，2026/02/23，2026/03/06，2026/03/22，2026/04/24，2026/08/19，2026/10/19</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -2934,7 +2922,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2963,7 +2951,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/08/28，2026/09/02，2026/09/11，2026/10/09</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09，2026/08/28，2026/09/02，2026/09/11，2026/10/09，2026/10/22</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2974,7 +2962,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3007,7 +2995,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28，2026/09/06，2026/09/22</t>
+          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28，2026/09/06，2026/09/22，2026/10/18</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3018,7 +3006,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3211,7 +3199,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10，2026/08/28，2026/09/08</t>
+          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10，2026/08/28，2026/09/08，2026/10/25</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3222,7 +3210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3339,7 +3327,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25，2026/09/08，2026/10/02</t>
+          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07，2026/08/25，2026/09/08，2026/10/02，2026/10/19，2026/10/24</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3350,7 +3338,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3463,7 +3451,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/09/02，2026/10/16</t>
+          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16，2026/09/02，2026/10/16，2026/10/17</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -3474,7 +3462,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3503,7 +3491,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21，2026/09/16，2026/09/22，2026/10/13</t>
+          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08，2026/08/21，2026/09/16，2026/09/22，2026/10/13，2026/10/23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3514,7 +3502,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3671,7 +3659,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/05/03，2025/06/19，2026/01/19，2026/06/23，2026/08/21</t>
+          <t>2025/03/12，2025/05/03，2025/06/19，2026/01/19，2026/06/23，2026/08/21，2026/10/17</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -3682,7 +3670,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3791,7 +3779,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09，2026/09/14</t>
+          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09，2026/09/14，2026/10/18</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -3802,7 +3790,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3875,7 +3863,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19，2026/08/05，2026/08/05，2026/08/19</t>
+          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19，2026/08/05，2026/08/05，2026/08/19，2026/10/23</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -3886,7 +3874,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3923,7 +3911,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/09/02，2026/10/16</t>
+          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11，2026/09/02，2026/10/16，2026/10/24</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3934,7 +3922,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4087,7 +4075,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/12，2025/05/19，2025/05/25，2025/07/05，2025/08/12，2025/09/03，2025/09/10，2025/11/14，2025/12/31，2026/02/18，2026/06/06</t>
+          <t>2025/03/13，2025/04/12，2025/05/19，2025/05/25，2025/07/05，2025/08/12，2025/09/03，2025/09/10，2025/11/14，2025/12/31，2026/02/18，2026/06/06，2026/10/24</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -4098,7 +4086,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4407,7 +4395,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/08/30，2026/09/04，2026/10/10，2026/10/10</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19，2026/08/25，2026/08/30，2026/09/04，2026/10/10，2026/10/10，2026/10/25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4418,7 +4406,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4527,7 +4515,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/15，2025/06/06，2025/07/31，2025/09/12，2026/04/09</t>
+          <t>2025/03/14，2025/05/15，2025/06/06，2025/07/31，2025/09/12，2026/04/09，2026/10/22</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -4538,7 +4526,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4687,7 +4675,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22，2026/09/04</t>
+          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22，2026/09/04，2026/10/18</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4698,7 +4686,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4727,7 +4715,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16，2026/09/21，2026/10/10</t>
+          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16，2026/09/21，2026/10/10，2026/10/19</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -4738,7 +4726,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4767,7 +4755,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/08/30，2026/10/10</t>
+          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26，2026/08/25，2026/08/30，2026/10/10，2026/10/18</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4778,7 +4766,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5099,7 +5087,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31，2026/08/21，2026/08/28，2026/08/30，2026/09/11</t>
+          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31，2026/08/21，2026/08/28，2026/08/30，2026/09/11，2026/10/22</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -5110,7 +5098,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5139,7 +5127,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/08/30，2026/09/11</t>
+          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17，2026/08/25，2026/08/30，2026/09/11，2026/10/17</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5150,7 +5138,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5539,7 +5527,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/08/30，2026/10/16</t>
+          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28，2026/08/30，2026/10/16，2026/10/24</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -5550,7 +5538,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5779,7 +5767,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/09/04，2026/09/08，2026/10/03</t>
+          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22，2026/09/04，2026/09/08，2026/10/03，2026/10/18</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5790,7 +5778,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6099,7 +6087,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04，2026/10/01，2026/10/10</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08，2026/08/23，2026/08/30，2026/09/04，2026/10/01，2026/10/10，2026/10/17，2026/10/25</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6110,7 +6098,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6139,7 +6127,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08，2026/08/16</t>
+          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08，2026/08/16，2026/10/25</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -6150,7 +6138,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6379,7 +6367,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/04/11，2025/05/19，2025/05/23，2025/06/12，2025/06/23，2025/07/20，2025/08/19，2025/09/21，2025/10/07，2025/10/20，2025/10/28，2025/11/09，2025/11/24，2025/12/16，2025/12/24，2025/12/26，2026/05/23，2026/07/30</t>
+          <t>2025/03/19，2025/03/28，2025/04/11，2025/05/19，2025/05/23，2025/06/12，2025/06/23，2025/07/20，2025/08/19，2025/09/21，2025/10/07，2025/10/20，2025/10/28，2025/11/09，2025/11/24，2025/12/16，2025/12/24，2025/12/26，2026/05/23，2026/07/30，2026/10/19</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -6390,7 +6378,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6663,7 +6651,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/08/30，2026/10/10</t>
+          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18，2026/08/25，2026/08/30，2026/10/10，2026/10/22</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -6674,7 +6662,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6703,7 +6691,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02，2026/08/02，2026/08/09，2026/10/16</t>
+          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02，2026/08/02，2026/08/09，2026/10/16，2026/10/24</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -6714,7 +6702,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6823,7 +6811,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06，2026/09/21，2026/10/06，2026/10/10</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/16，2025/08/26，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31，2026/08/25，2026/08/28，2026/09/06，2026/09/21，2026/10/06，2026/10/10，2026/10/25</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6834,7 +6822,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7027,7 +7015,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11，2026/09/26，2026/10/09，2026/10/16</t>
+          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12，2026/08/27，2026/09/11，2026/09/26，2026/10/09，2026/10/16，2026/10/25</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -7038,7 +7026,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7067,7 +7055,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08，2026/08/30，2026/09/06</t>
+          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08，2026/08/30，2026/09/06，2026/10/17</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -7078,7 +7066,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7223,7 +7211,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23，2026/08/25，2026/09/27</t>
+          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23，2026/08/25，2026/09/27，2026/10/25</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -7234,7 +7222,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7623,7 +7611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/09/04，2026/10/07，2026/10/10，2026/10/10</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02，2026/08/21，2026/09/04，2026/10/07，2026/10/10，2026/10/10，2026/10/24</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7634,7 +7622,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7867,7 +7855,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25，2026/09/14，2026/10/10</t>
+          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09，2026/08/25，2026/09/14，2026/10/10，2026/10/21</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -7878,7 +7866,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8107,7 +8095,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/17，2025/05/25，2025/12/02，2026/01/14，2026/06/06，2026/09/08</t>
+          <t>2025/03/23，2025/04/17，2025/05/25，2025/12/02，2026/01/14，2026/06/06，2026/09/08，2026/10/24</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -8118,7 +8106,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8707,7 +8695,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/20，2025/06/01，2025/07/15，2025/09/27，2025/10/03，2026/03/09，2026/06/26</t>
+          <t>2025/03/25，2025/05/20，2025/06/01，2025/07/15，2025/09/27，2025/10/03，2026/03/09，2026/06/26，2026/10/18</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -8718,7 +8706,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -8747,7 +8735,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/18，2025/04/24，2025/06/23，2025/09/29，2025/12/17，2026/04/08，2026/05/21</t>
+          <t>2025/03/25，2025/04/18，2025/04/24，2025/06/23，2025/09/29，2025/12/17，2026/04/08，2026/05/21，2026/10/19</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -8758,7 +8746,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -8995,7 +8983,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/06/08，2025/07/13，2025/07/21，2025/07/24，2025/07/28，2025/08/01，2025/08/16，2025/09/26，2025/10/28，2025/11/10，2025/11/17，2025/12/23，2026/04/17，2026/05/25，2026/06/26</t>
+          <t>2025/03/27，2025/06/08，2025/07/13，2025/07/21，2025/07/24，2025/07/28，2025/08/01，2025/08/16，2025/09/26，2025/10/28，2025/11/10，2025/11/17，2025/12/23，2026/04/17，2026/05/25，2026/06/26，2026/10/24</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -9006,7 +8994,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9235,7 +9223,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/22，2025/05/20，2025/06/27，2025/09/12，2025/11/09，2025/11/14，2025/12/09，2026/01/31</t>
+          <t>2025/03/28，2025/04/22，2025/05/20，2025/06/27，2025/09/12，2025/11/09，2025/11/14，2025/12/09，2026/01/31，2026/10/17</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -9246,7 +9234,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -9275,7 +9263,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02，2026/09/17，2026/09/29</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08，2026/09/02，2026/09/17，2026/09/29，2026/10/19</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9286,7 +9274,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9475,7 +9463,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/08/28，2026/09/16</t>
+          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31，2026/08/28，2026/09/16，2026/10/17，2026/10/19</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -9486,7 +9474,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9751,7 +9739,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01，2026/08/28</t>
+          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01，2026/08/28，2026/10/21</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -9762,7 +9750,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9995,7 +9983,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/09/04，2026/10/03</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05，2026/08/19，2026/09/04，2026/10/03，2026/10/23</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -10006,7 +9994,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10035,7 +10023,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27，2026/09/14</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28，2026/08/27，2026/09/14，2026/10/25</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10046,7 +10034,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10243,7 +10231,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17，2026/08/25，2026/09/26</t>
+          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17，2026/08/25，2026/09/26，2026/10/17</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -10254,7 +10242,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -10443,7 +10431,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09，2026/09/04</t>
+          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09，2026/09/04，2026/10/21</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -10454,7 +10442,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -10603,7 +10591,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/06/19，2025/07/05</t>
+          <t>2025/03/30，2025/06/19，2025/07/05，2026/10/21</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -10614,7 +10602,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -10803,7 +10791,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13，2026/08/21，2026/09/12</t>
+          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13，2026/08/21，2026/09/12，2026/10/20</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -10814,7 +10802,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -10923,7 +10911,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16，2026/08/23，2026/08/28，2026/09/11</t>
+          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16，2026/08/23，2026/08/28，2026/09/11，2026/10/22</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -10934,7 +10922,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -10963,7 +10951,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16，2026/08/27，2026/09/11</t>
+          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16，2026/08/27，2026/09/11，2026/10/19</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -10974,7 +10962,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -11283,7 +11271,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/09/02，2026/10/02</t>
+          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27，2026/09/02，2026/10/02，2026/10/18</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -11294,7 +11282,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -11647,7 +11635,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20，2026/08/30</t>
+          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20，2026/08/30，2026/10/21</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -11658,7 +11646,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -12047,7 +12035,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/04/11，2025/05/18，2025/09/12，2025/10/12，2026/01/16</t>
+          <t>2025/04/04，2025/04/11，2025/05/18，2025/09/12，2025/10/12，2026/01/16，2026/10/25</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -12058,7 +12046,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -12323,7 +12311,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/09/14，2026/09/14，2026/10/10</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20，2026/08/28，2026/09/14，2026/09/14，2026/10/10，2026/10/25</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12334,7 +12322,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -12363,7 +12351,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/09/14，2026/09/16，2026/10/01</t>
+          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13，2026/09/14，2026/09/16，2026/10/01，2026/10/25</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -12374,7 +12362,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13047,7 +13035,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/05/12，2025/08/22，2025/10/01，2025/10/17，2026/02/23，2026/03/06，2026/04/22，2026/06/10，2026/08/05</t>
+          <t>2025/04/08，2025/05/12，2025/08/22，2025/10/01，2025/10/17，2026/02/23，2026/03/06，2026/04/22，2026/06/10，2026/08/05，2026/10/24</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -13058,7 +13046,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -13087,7 +13075,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06，2026/08/07，2026/08/23</t>
+          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06，2026/08/07，2026/08/23，2026/10/22</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -13098,7 +13086,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -13167,7 +13155,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2025/04/10，2025/04/24，2025/05/13，2025/06/13，2025/09/03，2025/09/19，2025/10/13，2025/11/21，2026/03/04，2026/03/24</t>
+          <t>2025/04/10，2025/04/24，2025/05/13，2025/06/13，2025/09/03，2025/09/19，2025/10/13，2025/11/21，2026/03/04，2026/03/24，2026/10/21</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -13178,7 +13166,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -13207,7 +13195,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2025/04/10，2025/05/19，2025/06/27，2025/08/21，2025/08/29，2025/09/17，2025/10/17，2025/10/30，2026/03/01，2026/03/29，2026/10/07</t>
+          <t>2025/04/10，2025/05/19，2025/06/27，2025/08/21，2025/08/29，2025/09/17，2025/10/17，2025/10/30，2026/03/01，2026/03/29，2026/10/07，2026/10/18</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -13218,7 +13206,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -13679,7 +13667,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/18，2025/04/25，2025/04/29，2025/05/30，2025/06/09，2025/06/13，2025/06/26，2025/07/05，2025/07/14，2025/08/21，2025/09/10，2025/10/09，2025/11/21，2026/01/22，2026/10/13</t>
+          <t>2025/04/11，2025/04/18，2025/04/25，2025/04/29，2025/05/30，2025/06/09，2025/06/13，2025/06/26，2025/07/05，2025/07/14，2025/08/21，2025/09/10，2025/10/09，2025/11/21，2026/01/22，2026/10/13，2026/10/21</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -13690,7 +13678,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -13799,7 +13787,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/08/04，2025/09/12，2025/09/12，2026/04/09</t>
+          <t>2025/04/11，2025/08/04，2025/09/12，2025/09/12，2026/04/09，2026/10/21</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -13810,7 +13798,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -13999,7 +13987,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/08/28，2026/09/04，2026/10/10</t>
+          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27，2026/08/23，2026/08/28，2026/09/04，2026/10/10，2026/10/22，2026/10/25</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -14010,7 +13998,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -14091,7 +14079,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/15，2025/04/27，2025/05/22，2025/05/29，2025/06/03，2025/06/13，2025/06/28，2025/08/22，2025/09/19，2025/10/12，2025/12/05，2025/12/09，2026/01/15，2026/01/24，2026/03/19，2026/05/01，2026/05/21，2026/06/15，2026/07/16</t>
+          <t>2025/04/13，2025/04/15，2025/04/27，2025/05/22，2025/05/29，2025/06/03，2025/06/13，2025/06/28，2025/08/22，2025/09/19，2025/10/12，2025/12/05，2025/12/09，2026/01/15，2026/01/24，2026/03/19，2026/05/01，2026/05/21，2026/06/15，2026/07/16，2026/10/24</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -14102,7 +14090,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -14135,7 +14123,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01，2026/08/30</t>
+          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01，2026/08/30，2026/10/17</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -14146,7 +14134,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -14659,7 +14647,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/21，2025/05/08，2025/06/10，2025/06/28，2025/07/08，2025/08/22，2025/09/11，2025/10/25，2026/03/13，2026/04/18，2026/07/22</t>
+          <t>2025/04/17，2025/04/21，2025/05/08，2025/06/10，2025/06/28，2025/07/08，2025/08/22，2025/09/11，2025/10/25，2026/03/13，2026/04/18，2026/07/22，2026/10/24</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -14670,7 +14658,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -14787,7 +14775,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/01，2025/05/26，2025/07/03，2025/07/27，2025/09/18，2025/10/17，2025/11/21，2026/01/12，2026/01/24，2026/02/19，2026/02/23，2026/03/24，2026/05/04，2026/07/07，2026/08/25</t>
+          <t>2025/04/17，2025/05/01，2025/05/26，2025/07/03，2025/07/27，2025/09/18，2025/10/17，2025/11/21，2026/01/12，2026/01/24，2026/02/19，2026/02/23，2026/03/24，2026/05/04，2026/07/07，2026/08/25，2026/10/10</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -14798,7 +14786,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -14867,7 +14855,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06，2026/09/22，2026/10/16</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31，2026/09/06，2026/09/22，2026/10/16，2026/10/24</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14878,7 +14866,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -15183,7 +15171,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/05/18，2025/06/19，2025/07/15，2025/08/01，2025/09/17，2025/10/28，2025/11/13，2025/11/14，2026/02/10，2026/02/27，2026/08/02</t>
+          <t>2025/04/18，2025/05/18，2025/06/19，2025/07/15，2025/08/01，2025/09/17，2025/10/28，2025/11/13，2025/11/14，2026/02/10，2026/02/27，2026/08/02，2026/10/24</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -15194,7 +15182,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -15347,7 +15335,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/04/25，2025/05/22，2025/07/03，2025/07/11，2025/07/26，2025/09/08，2025/10/03，2025/12/02，2026/01/25，2026/06/06，2026/10/13</t>
+          <t>2025/04/19，2025/04/25，2025/05/22，2025/07/03，2025/07/11，2025/07/26，2025/09/08，2025/10/03，2025/12/02，2026/01/25，2026/06/06，2026/10/13，2026/10/24</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -15358,7 +15346,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -15427,7 +15415,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11，2026/09/22，2026/10/15</t>
+          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27，2026/09/11，2026/09/22，2026/10/15，2026/10/25</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -15438,7 +15426,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15595,7 +15583,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/09/15，2025/10/11，2026/01/05，2026/06/03，2026/07/26，2026/10/07</t>
+          <t>2025/04/21，2025/09/15，2025/10/11，2026/01/05，2026/06/03，2026/07/26，2026/10/07，2026/10/19</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -15606,7 +15594,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -15635,7 +15623,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/09/02，2026/09/04</t>
+          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06，2026/09/02，2026/09/04，2026/10/19</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -15646,7 +15634,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -16215,7 +16203,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/23，2025/12/05，2026/02/14，2026/04/09，2026/04/24，2026/10/13</t>
+          <t>2025/04/25，2025/06/23，2025/12/05，2026/02/14，2026/04/09，2026/04/24，2026/10/13，2026/10/19</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -16226,7 +16214,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -16295,7 +16283,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2025/04/25</t>
+          <t>2025/04/25，2026/10/21</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -16306,10 +16294,14 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>BV17zn66hEVw</t>
+        </is>
+      </c>
       <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
@@ -16367,7 +16359,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31，2026/08/25，2026/10/10</t>
+          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31，2026/08/25，2026/10/10，2026/10/25</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -16378,7 +16370,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -17567,7 +17559,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/08/28，2026/09/04，2026/09/11，2026/10/13</t>
+          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23，2026/08/28，2026/09/04，2026/09/11，2026/10/13，2026/10/21，2026/10/25</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -17578,7 +17570,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -17923,7 +17915,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2025/05/12，2025/05/31，2025/06/05，2025/06/15，2025/06/21，2025/06/27，2025/07/23，2025/08/24，2025/09/22，2025/12/19，2026/03/04，2026/06/03，2026/07/26，2026/10/02</t>
+          <t>2025/05/12，2025/05/31，2025/06/05，2025/06/15，2025/06/21，2025/06/27，2025/07/23，2025/08/24，2025/09/22，2025/12/19，2026/03/04，2026/06/03，2026/07/26，2026/10/02，2026/10/25</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -17934,7 +17926,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -18123,7 +18115,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>2025/05/15，2025/06/13，2025/06/23，2025/07/18，2025/08/02，2025/09/04，2025/09/15，2025/10/03，2025/10/28，2025/11/09，2025/11/14，2025/12/05，2026/02/02，2026/05/04</t>
+          <t>2025/05/15，2025/06/13，2025/06/23，2025/07/18，2025/08/02，2025/09/04，2025/09/15，2025/10/03，2025/10/28，2025/11/09，2025/11/14，2025/12/05，2026/02/02，2026/05/04，2026/10/19</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -18134,7 +18126,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -18403,7 +18395,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/11/28，2026/04/01，2026/10/16</t>
+          <t>2025/05/18，2025/11/28，2026/04/01，2026/10/16，2026/10/25</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -18414,7 +18406,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -18767,7 +18759,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10，2026/08/30</t>
+          <t>2025/05/22，2025/09/02，2025/09/12，2025/12/05，2026/04/09，2026/05/10，2026/08/30，2026/10/21</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -18778,7 +18770,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -18935,7 +18927,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/09/02，2026/10/01</t>
+          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31，2026/09/02，2026/10/01，2026/10/24</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -18946,7 +18938,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -19059,7 +19051,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/05/29，2025/09/02，2025/09/17，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07，2026/08/25，2026/10/10</t>
+          <t>2025/05/23，2025/05/29，2025/09/02，2025/09/17，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07，2026/08/25，2026/10/10，2026/10/25</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -19070,7 +19062,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -19699,7 +19691,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/08/30，2026/10/03</t>
+          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20，2026/08/30</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -19710,7 +19702,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -20071,7 +20063,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>2025/06/01，2025/06/16，2025/07/21</t>
+          <t>2025/06/01，2025/06/16，2025/07/21，2026/10/21</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -20082,7 +20074,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -20111,7 +20103,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>2025/06/01，2025/09/04，2026/03/01</t>
+          <t>2025/06/01，2025/09/04，2026/03/01，2026/10/21</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -20122,7 +20114,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -20663,7 +20655,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/10/20，2025/11/01，2026/03/05，2026/04/14，2026/08/23</t>
+          <t>2025/06/02，2025/10/20，2025/11/01，2026/03/05，2026/04/14，2026/08/23，2026/10/19</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -20674,7 +20666,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -21787,7 +21779,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30，2026/10/01，2026/10/10</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11，2026/08/30，2026/10/01，2026/10/10，2026/10/18</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21798,7 +21790,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21827,7 +21819,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/06/27，2025/08/24</t>
+          <t>2025/06/19，2025/06/27，2025/08/24，2026/10/21</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -21838,7 +21830,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -21991,7 +21983,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11，2026/09/06，2026/10/02</t>
+          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11，2026/09/06，2026/10/02，2026/10/24</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -22002,7 +21994,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -22381,7 +22373,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Midnight Reflection</t>
+          <t>午夜反射</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -22391,7 +22383,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08，2026/08/18，2026/09/11</t>
+          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08，2026/08/18，2026/09/11，2026/10/24</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -22402,7 +22394,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -23447,7 +23439,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09，2026/08/28，2026/09/06</t>
+          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09，2026/08/28，2026/09/06，2026/10/25</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -23458,7 +23450,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -24007,7 +23999,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28，2026/08/28</t>
+          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28，2026/08/28，2026/10/24</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -24018,7 +24010,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -24203,7 +24195,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/24，2025/07/28，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/26，2025/08/29，2025/09/19，2025/09/29，2025/10/11，2025/10/22，2025/10/28，2025/11/10，2025/11/28，2025/12/16，2026/02/19，2026/03/06，2026/03/28，2026/04/19，2026/06/14，2026/07/22</t>
+          <t>2025/07/17，2025/07/24，2025/07/28，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/26，2025/08/29，2025/09/19，2025/09/29，2025/10/11，2025/10/22，2025/10/28，2025/11/10，2025/11/28，2025/12/16，2026/02/19，2026/03/06，2026/03/28，2026/04/19，2026/06/14，2026/07/22，2026/10/24</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -24214,7 +24206,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -24559,7 +24551,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>2025/07/26，2026/09/06</t>
+          <t>2025/07/26，2026/09/06，2026/10/21</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -24570,7 +24562,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -25551,7 +25543,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>2025/09/04，2026/03/13</t>
+          <t>2025/09/04，2026/03/13，2026/10/21</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -25562,7 +25554,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -25671,7 +25663,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>2025/09/10，2026/01/28</t>
+          <t>2025/09/10，2026/01/28，2026/10/21</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -25682,7 +25674,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -26095,7 +26087,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>2025/09/12，2025/10/17，2026/09/16</t>
+          <t>2025/09/12，2025/10/17，2026/09/16，2026/10/19</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -26106,7 +26098,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -26135,7 +26127,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>2025/09/12</t>
+          <t>2025/09/12，2026/10/21</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -26146,7 +26138,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -26335,7 +26327,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30，2026/09/16，2026/10/10，2026/10/16</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28，2026/08/28，2026/08/30，2026/09/16，2026/10/10，2026/10/16，2026/10/25，2026/10/25</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26346,7 +26338,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -27003,7 +26995,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>2025/09/22，2026/08/19</t>
+          <t>2025/09/22，2026/08/19，2026/10/23</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -27014,7 +27006,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -27191,7 +27183,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22，2026/09/11，2026/10/13，2026/10/16</t>
+          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22，2026/09/11，2026/10/13，2026/10/16，2026/10/24，2026/10/25</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -27202,7 +27194,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -27583,7 +27575,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>2025/09/29，2025/09/30，2025/10/05，2025/10/07，2025/10/11，2025/10/16，2025/10/19，2025/10/22，2025/10/25，2025/11/19，2025/12/02，2025/12/11，2026/01/09，2026/01/14，2026/02/07，2026/03/22，2026/04/27，2026/05/25，2026/06/20，2026/07/09，2026/07/26，2026/08/11</t>
+          <t>2025/09/29，2025/09/30，2025/10/05，2025/10/07，2025/10/11，2025/10/16，2025/10/19，2025/10/22，2025/10/25，2025/11/19，2025/12/02，2025/12/11，2026/01/09，2026/01/14，2026/02/07，2026/03/22，2026/04/27，2026/05/25，2026/06/20，2026/07/09，2026/07/26，2026/08/11，2026/10/18</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -27594,7 +27586,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -28939,7 +28931,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>2025/10/23，2025/10/28，2026/04/02，2026/06/13</t>
+          <t>2025/10/23，2025/10/28，2026/04/02，2026/06/13，2026/10/20</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -28950,7 +28942,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -29015,7 +29007,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09，2026/08/11，2026/09/21</t>
+          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09，2026/08/11，2026/09/21，2026/10/24</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -29026,7 +29018,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -29523,7 +29515,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/09/02，2026/09/22</t>
+          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25，2026/09/02，2026/09/22，2026/10/25</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -29534,7 +29526,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -29827,7 +29819,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2025/11/19，2025/12/26，2026/03/06，2026/08/11</t>
+          <t>2025/11/19，2025/12/26，2026/03/06，2026/08/11，2026/10/25</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -29838,7 +29830,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -30931,7 +30923,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/08/28，2026/09/11，2026/09/26</t>
+          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07，2026/08/23，2026/08/28，2026/09/11，2026/09/26，2026/10/22，2026/10/25</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -30942,7 +30934,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -31607,7 +31599,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>2026/01/25，2026/08/19，2026/09/05</t>
+          <t>2026/01/25，2026/08/19，2026/09/05，2026/10/23</t>
         </is>
       </c>
       <c r="F778" t="inlineStr"/>
@@ -31618,7 +31610,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -31724,24 +31716,24 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>爱要坦荡荡(R&amp;B版)</t>
+          <t>Long Live</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
       <c r="D781" t="inlineStr">
         <is>
-          <t>顾叮当</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2026/01/30</t>
         </is>
       </c>
       <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -31749,11 +31741,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I781" t="inlineStr">
-        <is>
-          <t>BV1Xx6cBRE14</t>
-        </is>
-      </c>
+      <c r="I781" t="inlineStr"/>
       <c r="J781" t="inlineStr"/>
     </row>
     <row r="782">
@@ -31764,32 +31752,36 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Long Live</t>
+          <t>身不由己</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>大都会乐团</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27，2026/07/31，2026/07/31，2026/08/11，2026/10/15</t>
         </is>
       </c>
       <c r="F782" t="inlineStr"/>
       <c r="G782" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I782" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>BV1fxFMzqEDd</t>
+        </is>
+      </c>
       <c r="J782" t="inlineStr"/>
     </row>
     <row r="783">
@@ -31800,18 +31792,18 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>身不由己</t>
+          <t>乐鸣东方</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
       <c r="D783" t="inlineStr">
         <is>
-          <t>大都会乐团</t>
+          <t>洛天依</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27，2026/07/31，2026/07/31，2026/08/11，2026/10/15</t>
+          <t>2026/02/07，2026/04/19，2026/10/10</t>
         </is>
       </c>
       <c r="F783" t="inlineStr"/>
@@ -31822,12 +31814,12 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>BV1fxFMzqEDd</t>
+          <t>BV1A7dfBGEKE</t>
         </is>
       </c>
       <c r="J783" t="inlineStr"/>
@@ -31840,18 +31832,18 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>乐鸣东方</t>
+          <t>爱的飞行日记</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
       <c r="D784" t="inlineStr">
         <is>
-          <t>洛天依</t>
+          <t>周杰伦</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>2026/02/07，2026/04/19，2026/10/10</t>
+          <t>2026/02/07</t>
         </is>
       </c>
       <c r="F784" t="inlineStr"/>
@@ -31862,12 +31854,12 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>BV1A7dfBGEKE</t>
+          <t>BV1wGF4zFEBM</t>
         </is>
       </c>
       <c r="J784" t="inlineStr"/>
@@ -31880,18 +31872,18 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>爱的飞行日记</t>
+          <t>相亲相爱</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr">
         <is>
-          <t>周杰伦</t>
+          <t>陈慧琳/张惠妹/孙楠/古淖文</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>2026/02/07</t>
+          <t>2026/02/08</t>
         </is>
       </c>
       <c r="F785" t="inlineStr"/>
@@ -31907,7 +31899,7 @@
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>BV1wGF4zFEBM</t>
+          <t>BV1U9cTzpEjm</t>
         </is>
       </c>
       <c r="J785" t="inlineStr"/>
@@ -31920,18 +31912,18 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>相亲相爱</t>
+          <t>混入人类计划</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
       <c r="D786" t="inlineStr">
         <is>
-          <t>陈慧琳/张惠妹/孙楠/古淖文</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>2026/02/08</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/09/14，2026/09/14，2026/09/26，2026/10/15，2026/10/25</t>
         </is>
       </c>
       <c r="F786" t="inlineStr"/>
@@ -31942,12 +31934,12 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>BV1U9cTzpEjm</t>
+          <t>BV17kJs6JEcm，BV1JncczQEuJ，BV1c6fGBDEG1</t>
         </is>
       </c>
       <c r="J786" t="inlineStr"/>
@@ -31960,37 +31952,41 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>混入人类计划</t>
+          <t>纸飞机</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
       <c r="D787" t="inlineStr">
         <is>
-          <t>ChiliChill</t>
+          <t>鸣潮先约电台/飞行雪绒</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08，2026/08/23，2026/09/14，2026/09/14，2026/09/26，2026/10/15</t>
+          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02，2026/09/02，2026/10/21</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>BV17kJs6JEcm，BV1JncczQEuJ，BV1c6fGBDEG1</t>
-        </is>
-      </c>
-      <c r="J787" t="inlineStr"/>
+          <t>BV1HW9jBJEUE，BV1W4cuzSE8Y，BV12Ef6BBE5C</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -32000,41 +31996,37 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>纸飞机</t>
+          <t>刻在我心底的名字</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
       <c r="D788" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/飞行雪绒</t>
+          <t>卢广仲</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02，2026/09/02</t>
+          <t>2026/02/09，2026/02/27，2026/03/09，2026/04/14，2026/05/25，2026/07/25，2026/09/22</t>
         </is>
       </c>
       <c r="F788" t="inlineStr"/>
       <c r="G788" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>BV1HW9jBJEUE，BV1W4cuzSE8Y，BV12Ef6BBE5C</t>
-        </is>
-      </c>
-      <c r="J788" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1EkcszREeP，BV11dAQz2ESx</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -32044,18 +32036,18 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>刻在我心底的名字</t>
+          <t>词不达意</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
-          <t>卢广仲</t>
+          <t>林忆莲</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>2026/02/09，2026/02/27，2026/03/09，2026/04/14，2026/05/25，2026/07/25，2026/09/22</t>
+          <t>2026/02/12</t>
         </is>
       </c>
       <c r="F789" t="inlineStr"/>
@@ -32066,12 +32058,12 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>BV1EkcszREeP，BV11dAQz2ESx</t>
+          <t>BV1BNcBz4ECH</t>
         </is>
       </c>
       <c r="J789" t="inlineStr"/>
@@ -32084,37 +32076,45 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>词不达意</t>
-        </is>
-      </c>
-      <c r="C790" t="inlineStr"/>
+          <t>RUNNING FOR YOUR LIFE</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>无所遁藏</t>
+        </is>
+      </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>林忆莲</t>
+          <t>鸣潮先约电台/Casey Lee Williams</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>2026/02/12</t>
+          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19，2026/08/25，2026/10/03</t>
         </is>
       </c>
       <c r="F790" t="inlineStr"/>
       <c r="G790" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>BV1BNcBz4ECH</t>
-        </is>
-      </c>
-      <c r="J790" t="inlineStr"/>
+          <t>BV1QuGC6uEn3，BV14GZEBgErZ</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -32124,45 +32124,37 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>RUNNING FOR YOUR LIFE</t>
-        </is>
-      </c>
-      <c r="C791" t="inlineStr">
-        <is>
-          <t>无所遁藏</t>
-        </is>
-      </c>
+          <t>发财发福中国年</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr"/>
       <c r="D791" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/Casey Lee Williams</t>
+          <t>中国娃娃</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19，2026/08/25，2026/10/03</t>
+          <t>2026/02/17，2026/02/19</t>
         </is>
       </c>
       <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>BV1QuGC6uEn3，BV14GZEBgErZ</t>
-        </is>
-      </c>
-      <c r="J791" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1EYZ1B6ECT</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -32172,18 +32164,18 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>发财发福中国年</t>
+          <t>恭喜发财</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="inlineStr">
         <is>
-          <t>中国娃娃</t>
+          <t>刘德华</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>2026/02/17，2026/02/19</t>
+          <t>2026/02/17</t>
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
@@ -32194,14 +32186,10 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I792" t="inlineStr">
-        <is>
-          <t>BV1EYZ1B6ECT</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr"/>
       <c r="J792" t="inlineStr"/>
     </row>
     <row r="793">
@@ -32212,32 +32200,36 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>恭喜发财</t>
+          <t>迎春花</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr">
         <is>
-          <t>刘德华</t>
+          <t>卓依婷</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>2026/02/17</t>
+          <t>2026/02/19，2026/09/21</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>粤语</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I793" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>BV1gnZBBiEmr</t>
+        </is>
+      </c>
       <c r="J793" t="inlineStr"/>
     </row>
     <row r="794">
@@ -32248,24 +32240,24 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>迎春花</t>
+          <t>天堂</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr">
         <is>
-          <t>卓依婷</t>
+          <t>腾格尔</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>2026/02/19，2026/09/21</t>
+          <t>2026/02/19，2026/08/30</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
       <c r="G794" t="inlineStr">
         <is>
-          <t>粤语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
@@ -32275,7 +32267,7 @@
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>BV1gnZBBiEmr</t>
+          <t>BV166ZBBQEWz</t>
         </is>
       </c>
       <c r="J794" t="inlineStr"/>
@@ -32288,18 +32280,18 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>天堂</t>
+          <t>退后</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr">
         <is>
-          <t>腾格尔</t>
+          <t>周杰伦</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>2026/02/19，2026/08/30</t>
+          <t>2026/02/20</t>
         </is>
       </c>
       <c r="F795" t="inlineStr"/>
@@ -32310,12 +32302,12 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
         <is>
-          <t>BV166ZBBQEWz</t>
+          <t>BV1zkfGBEELD</t>
         </is>
       </c>
       <c r="J795" t="inlineStr"/>
@@ -32328,13 +32320,13 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>退后</t>
+          <t>最近还好吗</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
       <c r="D796" t="inlineStr">
         <is>
-          <t>周杰伦</t>
+          <t>S.H.E</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -32355,7 +32347,7 @@
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>BV1zkfGBEELD</t>
+          <t>BV14Tf3BWEef</t>
         </is>
       </c>
       <c r="J796" t="inlineStr"/>
@@ -32368,37 +32360,41 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>最近还好吗</t>
+          <t>持续瞬间的永恒</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>S.H.E</t>
+          <t>鸣潮先约电台/jixwang/markmilian/Sophia</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>2026/02/20</t>
+          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/08/27，2026/09/26</t>
         </is>
       </c>
       <c r="F797" t="inlineStr"/>
       <c r="G797" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>BV14Tf3BWEef</t>
-        </is>
-      </c>
-      <c r="J797" t="inlineStr"/>
+          <t>BV1asjG6aEzV，BV1modkBzEQ9，BV1K7f6BgE9r</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -32408,41 +32404,37 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>持续瞬间的永恒</t>
+          <t>安静</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/jixwang/markmilian/Sophia</t>
+          <t>周杰伦</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01，2026/08/27，2026/09/26</t>
+          <t>2026/02/23</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
       <c r="G798" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>BV1asjG6aEzV，BV1modkBzEQ9，BV1K7f6BgE9r</t>
-        </is>
-      </c>
-      <c r="J798" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV11nf6BTE4b</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -32452,18 +32444,18 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>安静</t>
+          <t>可惜没如果</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>周杰伦</t>
+          <t>林俊杰</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>2026/02/23，2026/10/10</t>
+          <t>2026/02/23</t>
         </is>
       </c>
       <c r="F799" t="inlineStr"/>
@@ -32474,12 +32466,12 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>BV11nf6BTE4b</t>
+          <t>BV1w1fzBwEhj</t>
         </is>
       </c>
       <c r="J799" t="inlineStr"/>
@@ -32492,37 +32484,41 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>可惜没如果</t>
+          <t>星炬不熄</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>林俊杰</t>
+          <t>鸣潮先约电台/飞行雪绒/星炬学院毕业生</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>2026/02/23</t>
+          <t>2026/02/25，2026/02/28，2026/03/01，2026/04/20，2026/09/06</t>
         </is>
       </c>
       <c r="F800" t="inlineStr"/>
       <c r="G800" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>华语，日语，英语，韩语</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>BV1w1fzBwEhj</t>
-        </is>
-      </c>
-      <c r="J800" t="inlineStr"/>
+          <t>BV1bodkB6EMm，BV1WDfaByEfD</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -32532,41 +32528,37 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>星炬不熄</t>
+          <t>Everglow</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/飞行雪绒/星炬学院毕业生</t>
+          <t>Coldplay</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>2026/02/25，2026/02/28，2026/03/01，2026/04/20，2026/09/06</t>
+          <t>2026/02/27</t>
         </is>
       </c>
       <c r="F801" t="inlineStr"/>
       <c r="G801" t="inlineStr">
         <is>
-          <t>华语，日语，英语，韩语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>BV1bodkB6EMm，BV1WDfaByEfD</t>
-        </is>
-      </c>
-      <c r="J801" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1kcAXzVEXm</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -32576,18 +32568,18 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Everglow</t>
+          <t>远航星的告别</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Coldplay</t>
+          <t>鸣潮先约电台/jixwang/Tarokiki/Emi Evans</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>2026/02/27</t>
+          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16，2026/09/14，2026/09/14</t>
         </is>
       </c>
       <c r="F802" t="inlineStr"/>
@@ -32598,15 +32590,19 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
         <is>
-          <t>BV1kcAXzVEXm</t>
-        </is>
-      </c>
-      <c r="J802" t="inlineStr"/>
+          <t>BV1jpVT6mEHP，BV1ea9GBtE8q，BV1n5PMzSEAz</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -32616,41 +32612,37 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>远航星的告别</t>
-        </is>
-      </c>
-      <c r="C803" t="inlineStr"/>
+          <t>月迷風影</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>月迷风影</t>
+        </is>
+      </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/jixwang/Tarokiki/Emi Evans</t>
+          <t>有坂美香</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16，2026/09/14，2026/09/14</t>
+          <t>2026/03/04</t>
         </is>
       </c>
       <c r="F803" t="inlineStr"/>
       <c r="G803" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I803" t="inlineStr">
-        <is>
-          <t>BV1jpVT6mEHP，BV1ea9GBtE8q，BV1n5PMzSEAz</t>
-        </is>
-      </c>
-      <c r="J803" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -32660,17 +32652,13 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>月迷風影</t>
-        </is>
-      </c>
-      <c r="C804" t="inlineStr">
-        <is>
-          <t>月迷风影</t>
-        </is>
-      </c>
+          <t>我还想她</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>有坂美香</t>
+          <t>林俊杰</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -32681,7 +32669,7 @@
       <c r="F804" t="inlineStr"/>
       <c r="G804" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -32689,7 +32677,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I804" t="inlineStr"/>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>BV17uPizoEkm</t>
+        </is>
+      </c>
       <c r="J804" t="inlineStr"/>
     </row>
     <row r="805">
@@ -32700,13 +32692,17 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>我还想她</t>
-        </is>
-      </c>
-      <c r="C805" t="inlineStr"/>
+          <t>未来へ</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>向着未来</t>
+        </is>
+      </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>林俊杰</t>
+          <t>Kiroro</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -32717,7 +32713,7 @@
       <c r="F805" t="inlineStr"/>
       <c r="G805" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
@@ -32727,7 +32723,7 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>BV17uPizoEkm</t>
+          <t>BV1j3PizxEzc</t>
         </is>
       </c>
       <c r="J805" t="inlineStr"/>
@@ -32740,41 +32736,41 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>未来へ</t>
-        </is>
-      </c>
-      <c r="C806" t="inlineStr">
-        <is>
-          <t>向着未来</t>
-        </is>
-      </c>
+          <t>突然的陀螺</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Kiroro</t>
+          <t>蔚蓝边际</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>2026/03/04</t>
+          <t>2025/12/08，2026/01/09，2026/03/04，2026/07/05</t>
         </is>
       </c>
       <c r="F806" t="inlineStr"/>
       <c r="G806" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>BV1j3PizxEzc</t>
-        </is>
-      </c>
-      <c r="J806" t="inlineStr"/>
+          <t>BV13z2yBtEb1</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -32784,18 +32780,18 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>突然的陀螺</t>
+          <t>不为谁而做的歌</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr">
         <is>
-          <t>蔚蓝边际</t>
+          <t>林俊杰</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>2025/12/08，2026/01/09，2026/03/04，2026/07/05</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="F807" t="inlineStr"/>
@@ -32806,19 +32802,15 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>BV13z2yBtEb1</t>
-        </is>
-      </c>
-      <c r="J807" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV17UmJBME1o</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -32828,24 +32820,28 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>不为谁而做的歌</t>
-        </is>
-      </c>
-      <c r="C808" t="inlineStr"/>
+          <t>AS IF IT'S YOUR LAST</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>像最后一样</t>
+        </is>
+      </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>林俊杰</t>
+          <t>BLACKPINK</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2026/03/07</t>
         </is>
       </c>
       <c r="F808" t="inlineStr"/>
       <c r="G808" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -32855,7 +32851,7 @@
       </c>
       <c r="I808" t="inlineStr">
         <is>
-          <t>BV17UmJBME1o</t>
+          <t>BV1q7NAzKES6</t>
         </is>
       </c>
       <c r="J808" t="inlineStr"/>
@@ -32868,38 +32864,34 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>AS IF IT'S YOUR LAST</t>
-        </is>
-      </c>
-      <c r="C809" t="inlineStr">
-        <is>
-          <t>像最后一样</t>
-        </is>
-      </c>
+          <t>天下</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr">
         <is>
-          <t>BLACKPINK</t>
+          <t>张杰</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>2026/03/07</t>
+          <t>2026/03/07，2026/03/29</t>
         </is>
       </c>
       <c r="F809" t="inlineStr"/>
       <c r="G809" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>BV1q7NAzKES6</t>
+          <t>BV1zLNAzqEVL</t>
         </is>
       </c>
       <c r="J809" t="inlineStr"/>
@@ -32912,18 +32904,18 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>天下</t>
+          <t>多幸运</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr">
         <is>
-          <t>张杰</t>
+          <t>韩安旭</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>2026/03/07，2026/03/29</t>
+          <t>2026/03/09</t>
         </is>
       </c>
       <c r="F810" t="inlineStr"/>
@@ -32934,12 +32926,12 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>BV1zLNAzqEVL</t>
+          <t>BV1fEP9zCEL8</t>
         </is>
       </c>
       <c r="J810" t="inlineStr"/>
@@ -32952,37 +32944,41 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>多幸运</t>
+          <t>靛青宇宙</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr">
         <is>
-          <t>韩安旭</t>
+          <t>鸣潮先约电台/飞行雪绒</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2026/03/09</t>
+          <t>2026/03/13，2026/03/25，2026/03/28，2026/04/11，2026/04/20，2026/05/26，2026/07/05，2026/07/22，2026/09/23</t>
         </is>
       </c>
       <c r="F811" t="inlineStr"/>
       <c r="G811" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>BV1fEP9zCEL8</t>
-        </is>
-      </c>
-      <c r="J811" t="inlineStr"/>
+          <t>BV1MBVT6qE6B，BV1snXyBwEzu</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -32992,41 +32988,41 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>靛青宇宙</t>
-        </is>
-      </c>
-      <c r="C812" t="inlineStr"/>
+          <t>銀の龍の背に乗って</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>骑在银龙的背上</t>
+        </is>
+      </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/飞行雪绒</t>
+          <t>中岛美雪</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/25，2026/03/28，2026/04/11，2026/04/20，2026/05/26，2026/07/05，2026/07/22，2026/09/23</t>
+          <t>2026/03/13，2026/05/01</t>
         </is>
       </c>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>BV1MBVT6qE6B，BV1snXyBwEzu</t>
-        </is>
-      </c>
-      <c r="J812" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1SLRLBfEPP</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -33036,38 +33032,34 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>銀の龍の背に乗って</t>
-        </is>
-      </c>
-      <c r="C813" t="inlineStr">
-        <is>
-          <t>骑在银龙的背上</t>
-        </is>
-      </c>
+          <t>啊！美丽卡洛</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr"/>
       <c r="D813" t="inlineStr">
         <is>
-          <t>中岛美雪</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/05/01</t>
+          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11，2026/10/01，2026/10/10</t>
         </is>
       </c>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>BV1SLRLBfEPP</t>
+          <t>BV1Q47X6jEdD，BV1UzXLBxErn</t>
         </is>
       </c>
       <c r="J813" t="inlineStr"/>
@@ -33080,18 +33072,18 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>啊！美丽卡洛</t>
+          <t>十年</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
       <c r="D814" t="inlineStr">
         <is>
-          <t>ChiliChill</t>
+          <t>陈奕迅</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11，2026/08/27，2026/09/11，2026/10/01，2026/10/10</t>
+          <t>2026/03/14，2026/03/17</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -33102,14 +33094,10 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I814" t="inlineStr">
-        <is>
-          <t>BV1Q47X6jEdD，BV1UzXLBxErn</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr"/>
       <c r="J814" t="inlineStr"/>
     </row>
     <row r="815">
@@ -33120,29 +33108,29 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>十年</t>
+          <t>Yesterday Once More</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
       <c r="D815" t="inlineStr">
         <is>
-          <t>陈奕迅</t>
+          <t>Carpenters</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>2026/03/14，2026/03/17</t>
+          <t>2026/03/14</t>
         </is>
       </c>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I815" t="inlineStr"/>
@@ -33156,33 +33144,45 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Yesterday Once More</t>
-        </is>
-      </c>
-      <c r="C816" t="inlineStr"/>
+          <t>给你呀</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>for ya</t>
+        </is>
+      </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Carpenters</t>
+          <t>蒋小呢</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>2026/03/14</t>
+          <t>2026/03/15，2026/03/17</t>
         </is>
       </c>
       <c r="F816" t="inlineStr"/>
       <c r="G816" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I816" t="inlineStr"/>
-      <c r="J816" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>BV12nw7zSEaQ</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -33192,45 +33192,33 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>给你呀</t>
-        </is>
-      </c>
-      <c r="C817" t="inlineStr">
-        <is>
-          <t>for ya</t>
-        </is>
-      </c>
+          <t>Believer</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr"/>
       <c r="D817" t="inlineStr">
         <is>
-          <t>蒋小呢</t>
+          <t>Imagine Dragons</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>2026/03/15，2026/03/17</t>
+          <t>2026/03/15</t>
         </is>
       </c>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I817" t="inlineStr">
-        <is>
-          <t>BV12nw7zSEaQ</t>
-        </is>
-      </c>
-      <c r="J817" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr"/>
+      <c r="J817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -33240,32 +33228,36 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Believer</t>
+          <t>句号</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Imagine Dragons</t>
+          <t>G.E.M. 邓紫棋</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>2026/03/15</t>
+          <t>2026/03/17，2026/10/06</t>
         </is>
       </c>
       <c r="F818" t="inlineStr"/>
       <c r="G818" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I818" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>BV12BpM6ZEes</t>
+        </is>
+      </c>
       <c r="J818" t="inlineStr"/>
     </row>
     <row r="819">
@@ -33276,18 +33268,18 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>句号</t>
+          <t>相思</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>G.E.M. 邓紫棋</t>
+          <t>毛阿敏</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/10/06</t>
+          <t>2026/03/17</t>
         </is>
       </c>
       <c r="F819" t="inlineStr"/>
@@ -33298,12 +33290,12 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>BV12BpM6ZEes</t>
+          <t>BV1dXw9zYEn4</t>
         </is>
       </c>
       <c r="J819" t="inlineStr"/>
@@ -33316,18 +33308,18 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>相思</t>
+          <t>若梦</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>毛阿敏</t>
+          <t>周深</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/03/17，2026/06/17，2026/09/21</t>
         </is>
       </c>
       <c r="F820" t="inlineStr"/>
@@ -33338,12 +33330,12 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
         <is>
-          <t>BV1dXw9zYEn4</t>
+          <t>BV1frLR6oEwn</t>
         </is>
       </c>
       <c r="J820" t="inlineStr"/>
@@ -33356,18 +33348,18 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>若梦</t>
+          <t>唐·毒蛇</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="inlineStr">
         <is>
-          <t>周深</t>
+          <t>Bsh-1</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/06/17，2026/09/21</t>
+          <t>2026/03/17，2026/03/29</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
@@ -33378,12 +33370,12 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>BV1frLR6oEwn</t>
+          <t>BV12uwRzQEpw</t>
         </is>
       </c>
       <c r="J821" t="inlineStr"/>
@@ -33396,37 +33388,41 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>唐·毒蛇</t>
+          <t>小小奇迹</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Bsh-1</t>
+          <t>鸣潮先约电台/jixwang/飞行雪绒</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/03/29</t>
+          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21，2026/09/11，2026/10/06，2026/10/10</t>
         </is>
       </c>
       <c r="F822" t="inlineStr"/>
       <c r="G822" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>BV12uwRzQEpw</t>
-        </is>
-      </c>
-      <c r="J822" t="inlineStr"/>
+          <t>BV1huGC6uEka，BV1vKdvBhE88，BV1nCD7ByEXM，BV1ugQSBnE8x</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -33436,18 +33432,22 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>小小奇迹</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr"/>
+          <t>Deadline Disco</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>极限迪斯科</t>
+        </is>
+      </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/jixwang/飞行雪绒</t>
+          <t>鸣潮先约电台/飞行雪绒</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08，2026/08/21，2026/09/11，2026/10/06，2026/10/10</t>
+          <t>2026/03/25，2026/05/26</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -33458,12 +33458,12 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t>BV1huGC6uEka，BV1vKdvBhE88，BV1nCD7ByEXM，BV1ugQSBnE8x</t>
+          <t>BV1huGC6uEkt</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
@@ -33480,45 +33480,41 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Deadline Disco</t>
+          <t>シリウスの心臓</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>极限迪斯科</t>
+          <t>天狼星的心脏</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/飞行雪绒</t>
+          <t>ヰ世界情緒</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>2026/03/25，2026/05/26</t>
+          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07，2026/08/09，2026/08/25，2026/10/24</t>
         </is>
       </c>
       <c r="F824" t="inlineStr"/>
       <c r="G824" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>BV1huGC6uEkt</t>
-        </is>
-      </c>
-      <c r="J824" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1Hw7j6ZELx，BV1XYX7BMEZn</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -33528,22 +33524,18 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>シリウスの心臓</t>
-        </is>
-      </c>
-      <c r="C825" t="inlineStr">
-        <is>
-          <t>天狼星的心脏</t>
-        </is>
-      </c>
+          <t>又三郎</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr"/>
       <c r="D825" t="inlineStr">
         <is>
-          <t>ヰ世界情緒</t>
+          <t>ヨルシカ (Yorushika)</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07，2026/08/09，2026/08/25</t>
+          <t>2026/03/28，2026/04/14，2026/05/10，2026/06/12</t>
         </is>
       </c>
       <c r="F825" t="inlineStr"/>
@@ -33554,12 +33546,12 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>BV1Hw7j6ZELx，BV1XYX7BMEZn</t>
+          <t>BV1m6XLBREbN</t>
         </is>
       </c>
       <c r="J825" t="inlineStr"/>
@@ -33572,34 +33564,34 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>又三郎</t>
+          <t>八方来财</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
       <c r="D826" t="inlineStr">
         <is>
-          <t>ヨルシカ (Yorushika)</t>
+          <t>揽佬SKAI ISYOURGOD</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>2026/03/28，2026/04/14，2026/05/10，2026/06/12</t>
+          <t>2026/03/29</t>
         </is>
       </c>
       <c r="F826" t="inlineStr"/>
       <c r="G826" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>BV1m6XLBREbN</t>
+          <t>BV1cJXSBMEAK</t>
         </is>
       </c>
       <c r="J826" t="inlineStr"/>
@@ -33612,18 +33604,18 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>八方来财</t>
+          <t>勇气大爆发</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
       <c r="D827" t="inlineStr">
         <is>
-          <t>揽佬SKAI ISYOURGOD</t>
+          <t>贝乐虎儿歌/土豆王国小乐队</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>2026/03/29</t>
+          <t>2025/12/24，2025/12/25，2026/04/01，2026/09/13</t>
         </is>
       </c>
       <c r="F827" t="inlineStr"/>
@@ -33634,12 +33626,12 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>BV1cJXSBMEAK</t>
+          <t>BV1B997BUEMa，BV1DjB2BrEiu，BV1FGBRB7EuH</t>
         </is>
       </c>
       <c r="J827" t="inlineStr"/>
@@ -33652,34 +33644,34 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>勇气大爆发</t>
+          <t>吴哥窟</t>
         </is>
       </c>
       <c r="C828" t="inlineStr"/>
       <c r="D828" t="inlineStr">
         <is>
-          <t>贝乐虎儿歌/土豆王国小乐队</t>
+          <t>吴雨霏</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/25，2026/04/01，2026/09/13</t>
+          <t>2026/04/01，2026/06/10</t>
         </is>
       </c>
       <c r="F828" t="inlineStr"/>
       <c r="G828" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>粤语</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
         <is>
-          <t>BV1B997BUEMa，BV1DjB2BrEiu，BV1FGBRB7EuH</t>
+          <t>BV18qXfB2Epc</t>
         </is>
       </c>
       <c r="J828" t="inlineStr"/>
@@ -33692,37 +33684,41 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>吴哥窟</t>
+          <t>L!!!!ght</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
       <c r="D829" t="inlineStr">
         <is>
-          <t>吴雨霏</t>
+          <t>鸣潮先约电台/Meredith Bull</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>2026/04/01，2026/06/10</t>
+          <t>2026/04/01</t>
         </is>
       </c>
       <c r="F829" t="inlineStr"/>
       <c r="G829" t="inlineStr">
         <is>
-          <t>粤语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>BV18qXfB2Epc</t>
-        </is>
-      </c>
-      <c r="J829" t="inlineStr"/>
+          <t>BV1SqXfB2EWL</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -33732,24 +33728,24 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>L!!!!ght</t>
+          <t>假如爱有天意</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/Meredith Bull</t>
+          <t>李健</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>2026/04/01</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="F830" t="inlineStr"/>
       <c r="G830" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -33759,14 +33755,10 @@
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>BV1SqXfB2EWL</t>
-        </is>
-      </c>
-      <c r="J830" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV13x9KBME9P</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -33776,34 +33768,38 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>假如爱有天意</t>
-        </is>
-      </c>
-      <c r="C831" t="inlineStr"/>
+          <t>Poker Face</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>扑克脸</t>
+        </is>
+      </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>李健</t>
+          <t>Lady Gaga</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>2026/04/02</t>
+          <t>2026/04/09，2026/10/03</t>
         </is>
       </c>
       <c r="F831" t="inlineStr"/>
       <c r="G831" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>BV13x9KBME9P</t>
+          <t>BV1aYDWB1E8a</t>
         </is>
       </c>
       <c r="J831" t="inlineStr"/>
@@ -33816,38 +33812,34 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Poker Face</t>
-        </is>
-      </c>
-      <c r="C832" t="inlineStr">
-        <is>
-          <t>扑克脸</t>
-        </is>
-      </c>
+          <t>最炫民族风</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Lady Gaga</t>
+          <t>凤凰传奇</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>2026/04/09，2026/10/03</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F832" t="inlineStr"/>
       <c r="G832" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
         <is>
-          <t>BV1aYDWB1E8a</t>
+          <t>BV1UsD4BmEbA</t>
         </is>
       </c>
       <c r="J832" t="inlineStr"/>
@@ -33860,18 +33852,18 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>最炫民族风</t>
+          <t>不得不爱</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr">
         <is>
-          <t>凤凰传奇</t>
+          <t>潘玮柏/弦子</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/09，2026/09/27</t>
         </is>
       </c>
       <c r="F833" t="inlineStr"/>
@@ -33882,12 +33874,12 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
         <is>
-          <t>BV1UsD4BmEbA</t>
+          <t>BV1sXDxB6Ewz</t>
         </is>
       </c>
       <c r="J833" t="inlineStr"/>
@@ -33900,18 +33892,18 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>不得不爱</t>
+          <t>怎么办</t>
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
       <c r="D834" t="inlineStr">
         <is>
-          <t>潘玮柏/弦子</t>
+          <t>S.H.E</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>2026/04/09，2026/09/27</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F834" t="inlineStr"/>
@@ -33922,12 +33914,12 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
         <is>
-          <t>BV1sXDxB6Ewz</t>
+          <t>BV1HjDxBNENK</t>
         </is>
       </c>
       <c r="J834" t="inlineStr"/>
@@ -33940,18 +33932,18 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>怎么办</t>
+          <t>爱情买卖</t>
         </is>
       </c>
       <c r="C835" t="inlineStr"/>
       <c r="D835" t="inlineStr">
         <is>
-          <t>S.H.E</t>
+          <t>慕容晓晓</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/09，2026/06/20</t>
         </is>
       </c>
       <c r="F835" t="inlineStr"/>
@@ -33962,12 +33954,12 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
         <is>
-          <t>BV1HjDxBNENK</t>
+          <t>BV12TQFBuEhn</t>
         </is>
       </c>
       <c r="J835" t="inlineStr"/>
@@ -33980,34 +33972,34 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>爱情买卖</t>
+          <t>Bad Romance</t>
         </is>
       </c>
       <c r="C836" t="inlineStr"/>
       <c r="D836" t="inlineStr">
         <is>
-          <t>慕容晓晓</t>
+          <t>Lady Gaga</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>2026/04/09，2026/06/20</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F836" t="inlineStr"/>
       <c r="G836" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
         <is>
-          <t>BV12TQFBuEhn</t>
+          <t>BV14NQFB6EHA</t>
         </is>
       </c>
       <c r="J836" t="inlineStr"/>
@@ -34020,13 +34012,13 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Bad Romance</t>
+          <t>北京欢迎你</t>
         </is>
       </c>
       <c r="C837" t="inlineStr"/>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Lady Gaga</t>
+          <t>华语群星</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -34037,7 +34029,7 @@
       <c r="F837" t="inlineStr"/>
       <c r="G837" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -34047,7 +34039,7 @@
       </c>
       <c r="I837" t="inlineStr">
         <is>
-          <t>BV14NQFB6EHA</t>
+          <t>BV14NQFB6E2U</t>
         </is>
       </c>
       <c r="J837" t="inlineStr"/>
@@ -34060,18 +34052,18 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>北京欢迎你</t>
+          <t>一千零一夜</t>
         </is>
       </c>
       <c r="C838" t="inlineStr"/>
       <c r="D838" t="inlineStr">
         <is>
-          <t>华语群星</t>
+          <t>刘美麟</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>2026/04/09</t>
+          <t>2026/04/14</t>
         </is>
       </c>
       <c r="F838" t="inlineStr"/>
@@ -34087,7 +34079,7 @@
       </c>
       <c r="I838" t="inlineStr">
         <is>
-          <t>BV14NQFB6E2U</t>
+          <t>BV1kdQ3BNEUr</t>
         </is>
       </c>
       <c r="J838" t="inlineStr"/>
@@ -34100,34 +34092,34 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>一千零一夜</t>
+          <t>Take Me Hand</t>
         </is>
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="inlineStr">
         <is>
-          <t>刘美麟</t>
+          <t>DAISHI DANCE/Cécile Corbel</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>2026/04/14</t>
+          <t>2026/04/14，2026/06/14，2026/10/06</t>
         </is>
       </c>
       <c r="F839" t="inlineStr"/>
       <c r="G839" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
         <is>
-          <t>BV1kdQ3BNEUr</t>
+          <t>BV1mQQVB1EBB</t>
         </is>
       </c>
       <c r="J839" t="inlineStr"/>
@@ -34140,34 +34132,34 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Take Me Hand</t>
+          <t>爱人错过</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
       <c r="D840" t="inlineStr">
         <is>
-          <t>DAISHI DANCE/Cécile Corbel</t>
+          <t>告五人</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>2026/04/14，2026/06/14，2026/10/06</t>
+          <t>2026/04/14</t>
         </is>
       </c>
       <c r="F840" t="inlineStr"/>
       <c r="G840" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
         <is>
-          <t>BV1mQQVB1EBB</t>
+          <t>BV1UDQVBjEGt</t>
         </is>
       </c>
       <c r="J840" t="inlineStr"/>
@@ -34180,13 +34172,13 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>爱人错过</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
       <c r="D841" t="inlineStr">
         <is>
-          <t>告五人</t>
+          <t>容祖儿</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -34207,7 +34199,7 @@
       </c>
       <c r="I841" t="inlineStr">
         <is>
-          <t>BV1UDQVBjEGt</t>
+          <t>BV1PEQVBuEKU</t>
         </is>
       </c>
       <c r="J841" t="inlineStr"/>
@@ -34220,18 +34212,18 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>小小</t>
+          <t>想去海边</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
-          <t>容祖儿</t>
+          <t>夏日入侵企画</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>2026/04/14</t>
+          <t>2026/04/14，2026/04/14，2026/07/22</t>
         </is>
       </c>
       <c r="F842" t="inlineStr"/>
@@ -34242,12 +34234,12 @@
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
         <is>
-          <t>BV1PEQVBuEKU</t>
+          <t>BV1RWdaBHEsQ</t>
         </is>
       </c>
       <c r="J842" t="inlineStr"/>
@@ -34260,34 +34252,38 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>想去海边</t>
-        </is>
-      </c>
-      <c r="C843" t="inlineStr"/>
+          <t>착하다는 말이 제일 싫어</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>最讨厌善良这句话</t>
+        </is>
+      </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>夏日入侵企画</t>
+          <t>YENA</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>2026/04/14，2026/04/14，2026/07/22</t>
+          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25，2026/09/02</t>
         </is>
       </c>
       <c r="F843" t="inlineStr"/>
       <c r="G843" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>BV1RWdaBHEsQ</t>
+          <t>BV1qJ5i6KEKZ，BV1XsdaBDEAD</t>
         </is>
       </c>
       <c r="J843" t="inlineStr"/>
@@ -34300,41 +34296,41 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>착하다는 말이 제일 싫어</t>
-        </is>
-      </c>
-      <c r="C844" t="inlineStr">
-        <is>
-          <t>最讨厌善良这句话</t>
-        </is>
-      </c>
+          <t>星辉抵达之日</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>YENA</t>
+          <t>鸣潮先约电台/baitian/waka</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25，2026/09/02</t>
+          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02，2026/09/06，2026/10/13，2026/10/16，2026/10/16</t>
         </is>
       </c>
       <c r="F844" t="inlineStr"/>
       <c r="G844" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
         <is>
-          <t>BV1qJ5i6KEKZ，BV1XsdaBDEAD</t>
-        </is>
-      </c>
-      <c r="J844" t="inlineStr"/>
+          <t>BV1huGC6uE2a，BV1mKdLBfEPD</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -34344,18 +34340,18 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>星辉抵达之日</t>
+          <t>Daisy Crown</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
       <c r="D845" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/baitian/waka</t>
+          <t>鸣潮先约电台/Empty old City</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02，2026/09/06，2026/10/13，2026/10/16，2026/10/16</t>
+          <t>2026/04/19，2026/07/21</t>
         </is>
       </c>
       <c r="F845" t="inlineStr"/>
@@ -34366,12 +34362,12 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
         <is>
-          <t>BV1huGC6uE2a，BV1mKdLBfEPD</t>
+          <t>BV1nHocBjEU6</t>
         </is>
       </c>
       <c r="J845" t="inlineStr">
@@ -34388,41 +34384,37 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Daisy Crown</t>
+          <t>最初的梦想</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/Empty old City</t>
+          <t>范玮琪</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>2026/04/19，2026/07/21</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="F846" t="inlineStr"/>
       <c r="G846" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
         <is>
-          <t>BV1nHocBjEU6</t>
-        </is>
-      </c>
-      <c r="J846" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1UodkBzE3C</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -34432,13 +34424,13 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>最初的梦想</t>
+          <t>勿听</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
       <c r="D847" t="inlineStr">
         <is>
-          <t>范玮琪</t>
+          <t>张紫宁/赵紫骅/游戏科学</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -34459,10 +34451,14 @@
       </c>
       <c r="I847" t="inlineStr">
         <is>
-          <t>BV1UodkBzE3C</t>
-        </is>
-      </c>
-      <c r="J847" t="inlineStr"/>
+          <t>BV1ModkB6EDW</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -34472,24 +34468,24 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>勿听</t>
+          <t>Everywhere we go</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
       <c r="D848" t="inlineStr">
         <is>
-          <t>张紫宁/赵紫骅/游戏科学</t>
+          <t>陈冠希/MC仁/厨房仔/应采儿</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="F848" t="inlineStr"/>
       <c r="G848" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>粤语</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -34499,14 +34495,10 @@
       </c>
       <c r="I848" t="inlineStr">
         <is>
-          <t>BV1ModkB6EDW</t>
-        </is>
-      </c>
-      <c r="J848" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1iyoDByEWt</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -34516,13 +34508,17 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Everywhere we go</t>
-        </is>
-      </c>
-      <c r="C849" t="inlineStr"/>
+          <t>Komm, süsser Tod</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>来吧，甜蜜的死亡</t>
+        </is>
+      </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>陈冠希/MC仁/厨房仔/应采儿</t>
+          <t>ARIANNE</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -34533,7 +34529,7 @@
       <c r="F849" t="inlineStr"/>
       <c r="G849" t="inlineStr">
         <is>
-          <t>粤语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -34543,10 +34539,14 @@
       </c>
       <c r="I849" t="inlineStr">
         <is>
-          <t>BV1iyoDByEWt</t>
-        </is>
-      </c>
-      <c r="J849" t="inlineStr"/>
+          <t>BV1pSoSBHEJj</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>动漫</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -34556,45 +34556,37 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Komm, süsser Tod</t>
-        </is>
-      </c>
-      <c r="C850" t="inlineStr">
-        <is>
-          <t>来吧，甜蜜的死亡</t>
-        </is>
-      </c>
+          <t>突然好想你</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr"/>
       <c r="D850" t="inlineStr">
         <is>
-          <t>ARIANNE</t>
+          <t>五月天</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/04/24，2026/05/01</t>
         </is>
       </c>
       <c r="F850" t="inlineStr"/>
       <c r="G850" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
         <is>
-          <t>BV1pSoSBHEJj</t>
-        </is>
-      </c>
-      <c r="J850" t="inlineStr">
-        <is>
-          <t>动漫</t>
-        </is>
-      </c>
+          <t>BV169oSBUEmT</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -34604,18 +34596,18 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>突然好想你</t>
+          <t>连名带姓</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="inlineStr">
         <is>
-          <t>五月天</t>
+          <t>张惠妹</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>2026/04/24，2026/05/01</t>
+          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11，2026/08/25，2026/09/11，2026/10/19</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>
@@ -34626,12 +34618,12 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
         <is>
-          <t>BV169oSBUEmT</t>
+          <t>BV1tLRLBZEd6</t>
         </is>
       </c>
       <c r="J851" t="inlineStr"/>
@@ -34644,18 +34636,18 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>连名带姓</t>
+          <t>大香蕉</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="inlineStr">
         <is>
-          <t>张惠妹</t>
+          <t>龙智祥/吴非华</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11，2026/08/25，2026/09/11</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -34666,12 +34658,12 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
         <is>
-          <t>BV1tLRLBZEd6</t>
+          <t>BV1aBRuBSEj2</t>
         </is>
       </c>
       <c r="J852" t="inlineStr"/>
@@ -34684,18 +34676,18 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>大香蕉</t>
+          <t>大眠</t>
         </is>
       </c>
       <c r="C853" t="inlineStr"/>
       <c r="D853" t="inlineStr">
         <is>
-          <t>龙智祥/吴非华</t>
+          <t>王心凌</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/01，2026/08/02，2026/08/30，2026/10/13</t>
         </is>
       </c>
       <c r="F853" t="inlineStr"/>
@@ -34706,12 +34698,12 @@
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
         <is>
-          <t>BV1aBRuBSEj2</t>
+          <t>BV1bjRLBFEUZ</t>
         </is>
       </c>
       <c r="J853" t="inlineStr"/>
@@ -34724,34 +34716,34 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>大眠</t>
+          <t>Welcome To New York</t>
         </is>
       </c>
       <c r="C854" t="inlineStr"/>
       <c r="D854" t="inlineStr">
         <is>
-          <t>王心凌</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/08/02，2026/08/30，2026/10/13</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
       <c r="G854" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>BV1bjRLBFEUZ</t>
+          <t>BV1SLRLBfE71</t>
         </is>
       </c>
       <c r="J854" t="inlineStr"/>
@@ -34764,37 +34756,45 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Welcome To New York</t>
-        </is>
-      </c>
-      <c r="C855" t="inlineStr"/>
+          <t>ふわふわ時間</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>轻飘飘时间</t>
+        </is>
+      </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>放課後ティータイム</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/01，2026/09/13</t>
         </is>
       </c>
       <c r="F855" t="inlineStr"/>
       <c r="G855" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>BV1SLRLBfE71</t>
-        </is>
-      </c>
-      <c r="J855" t="inlineStr"/>
+          <t>BV1gjRLBFEG4</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>动漫</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -34804,45 +34804,37 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>ふわふわ時間</t>
-        </is>
-      </c>
-      <c r="C856" t="inlineStr">
-        <is>
-          <t>轻飘飘时间</t>
-        </is>
-      </c>
+          <t>咖喱咖喱</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr">
         <is>
-          <t>放課後ティータイム</t>
+          <t>牛奶咖啡</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>2026/05/01，2026/09/13</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="F856" t="inlineStr"/>
       <c r="G856" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>BV1gjRLBFEG4</t>
-        </is>
-      </c>
-      <c r="J856" t="inlineStr">
-        <is>
-          <t>动漫</t>
-        </is>
-      </c>
+          <t>BV1WK5s6jEUw</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -34852,24 +34844,28 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>咖喱咖喱</t>
-        </is>
-      </c>
-      <c r="C857" t="inlineStr"/>
+          <t xml:space="preserve">빌런 </t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>反派/Villain</t>
+        </is>
+      </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>牛奶咖啡</t>
+          <t>Stella Jang</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="F857" t="inlineStr"/>
       <c r="G857" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -34879,7 +34875,7 @@
       </c>
       <c r="I857" t="inlineStr">
         <is>
-          <t>BV1WK5s6jEUw</t>
+          <t>BV1k35B6JED4</t>
         </is>
       </c>
       <c r="J857" t="inlineStr"/>
@@ -34892,41 +34888,45 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t xml:space="preserve">빌런 </t>
+          <t>天ノ弱</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>反派/Villain</t>
+          <t>天之弱</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Stella Jang</t>
+          <t>Akie秋绘</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23，2026/09/11，2026/09/23</t>
         </is>
       </c>
       <c r="F858" t="inlineStr"/>
       <c r="G858" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
         <is>
-          <t>BV1k35B6JED4</t>
-        </is>
-      </c>
-      <c r="J858" t="inlineStr"/>
+          <t>BV1huGC6uECZ，BV1DPVw6sEPJ</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -34936,45 +34936,37 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>天ノ弱</t>
-        </is>
-      </c>
-      <c r="C859" t="inlineStr">
-        <is>
-          <t>天之弱</t>
-        </is>
-      </c>
+          <t>空心吉他</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr"/>
       <c r="D859" t="inlineStr">
         <is>
-          <t>Akie秋绘</t>
+          <t>张玉华</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16，2026/08/23，2026/08/23，2026/09/11，2026/09/23</t>
+          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02，2026/09/22</t>
         </is>
       </c>
       <c r="F859" t="inlineStr"/>
       <c r="G859" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
         <is>
-          <t>BV1huGC6uECZ，BV1DPVw6sEPJ</t>
-        </is>
-      </c>
-      <c r="J859" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1sFVN6REQi，BV1SNVw69EEk</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -34984,18 +34976,18 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>空心吉他</t>
+          <t>世纪末游戏</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
       <c r="D860" t="inlineStr">
         <is>
-          <t>张玉华</t>
+          <t>艾因Eine/七海Nana7mi/中单光一/星弥Hoshimi/弥希Miki/阿萨Aza/千春Chiharu/小可学妹/阿梓从小就很可爱/勾檀Mayumi/舒三妈Susam/诺莺Nox/桃星Tocci/瑞娅_Rhea/尤格Yog/希侑Kiyuu/雾深Girimi</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02，2026/09/22</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="F860" t="inlineStr"/>
@@ -35006,12 +34998,12 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
         <is>
-          <t>BV1sFVN6REQi，BV1SNVw69EEk</t>
+          <t>BV1KKEJ61EsR</t>
         </is>
       </c>
       <c r="J860" t="inlineStr"/>
@@ -35024,18 +35016,18 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>世纪末游戏</t>
+          <t>Rendezvous</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
       <c r="D861" t="inlineStr">
         <is>
-          <t>艾因Eine/七海Nana7mi/中单光一/星弥Hoshimi/弥希Miki/阿萨Aza/千春Chiharu/小可学妹/阿梓从小就很可爱/勾檀Mayumi/舒三妈Susam/诺莺Nox/桃星Tocci/瑞娅_Rhea/尤格Yog/希侑Kiyuu/雾深Girimi</t>
+          <t>瑞娅_Rhea/岁己SUI/栞栞Shiori/米汀Nagisa/花礼Harei/泽音Melody/三理Mit3uri</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>2026/06/06</t>
+          <t>2026/06/06，2026/10/06</t>
         </is>
       </c>
       <c r="F861" t="inlineStr"/>
@@ -35046,12 +35038,12 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
         <is>
-          <t>BV1KKEJ61EsR</t>
+          <t>BV1KKEJ61EBD</t>
         </is>
       </c>
       <c r="J861" t="inlineStr"/>
@@ -35064,24 +35056,24 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Rendezvous</t>
+          <t>DAY BY DAY</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr">
         <is>
-          <t>瑞娅_Rhea/岁己SUI/栞栞Shiori/米汀Nagisa/花礼Harei/泽音Melody/三理Mit3uri</t>
+          <t>T-ara</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>2026/06/06，2026/10/06</t>
+          <t>2026/06/10，2026/10/06</t>
         </is>
       </c>
       <c r="F862" t="inlineStr"/>
       <c r="G862" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H862" t="inlineStr">
@@ -35091,7 +35083,7 @@
       </c>
       <c r="I862" t="inlineStr">
         <is>
-          <t>BV1KKEJ61EBD</t>
+          <t>BV119Ed6EEBS</t>
         </is>
       </c>
       <c r="J862" t="inlineStr"/>
@@ -35104,24 +35096,24 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>DAY BY DAY</t>
+          <t>七色回响</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
       <c r="D863" t="inlineStr">
         <is>
-          <t>T-ara</t>
+          <t>艾因Eine/七海Nana7mi/中单光一/弥希Miki/阿萨Aza/雪绘Yukie/阿梓从小就很可爱/小可学妹/诺莺Nox/舒三妈Susam/桃星Tocci/瑞娅_Rhea/尤格Yog/雾深Girimi/莱恩Leo</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>2026/06/10，2026/10/06</t>
+          <t>2026/06/14，2026/06/14</t>
         </is>
       </c>
       <c r="F863" t="inlineStr"/>
       <c r="G863" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H863" t="inlineStr">
@@ -35131,7 +35123,7 @@
       </c>
       <c r="I863" t="inlineStr">
         <is>
-          <t>BV119Ed6EEBS</t>
+          <t>BV1U3Ju6sEsm</t>
         </is>
       </c>
       <c r="J863" t="inlineStr"/>
@@ -35144,18 +35136,18 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>七色回响</t>
+          <t>天灰</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
       <c r="D864" t="inlineStr">
         <is>
-          <t>艾因Eine/七海Nana7mi/中单光一/弥希Miki/阿萨Aza/雪绘Yukie/阿梓从小就很可爱/小可学妹/诺莺Nox/舒三妈Susam/桃星Tocci/瑞娅_Rhea/尤格Yog/雾深Girimi/莱恩Leo</t>
+          <t>S.H.E</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/06/14</t>
+          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/09/04，2026/10/10</t>
         </is>
       </c>
       <c r="F864" t="inlineStr"/>
@@ -35166,12 +35158,12 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
         <is>
-          <t>BV1U3Ju6sEsm</t>
+          <t>BV1U3Ju6sEn7</t>
         </is>
       </c>
       <c r="J864" t="inlineStr"/>
@@ -35184,37 +35176,41 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>天灰</t>
+          <t>愿戴荣光坠入天渊</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
-          <t>S.H.E</t>
+          <t>鸣潮先约电台/jixwang/VISION SOUND</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27，2026/09/04，2026/10/10</t>
+          <t>2026/06/14，2026/06/14，2026/08/02</t>
         </is>
       </c>
       <c r="F865" t="inlineStr"/>
       <c r="G865" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
         <is>
-          <t>BV1U3Ju6sEn7</t>
-        </is>
-      </c>
-      <c r="J865" t="inlineStr"/>
+          <t>BV1u3Ju6xEAo</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -35224,41 +35220,37 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>愿戴荣光坠入天渊</t>
+          <t>耳语</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
       <c r="D866" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/jixwang/VISION SOUND</t>
+          <t>锦零</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/06/14，2026/08/02</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="F866" t="inlineStr"/>
       <c r="G866" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
         <is>
-          <t>BV1u3Ju6xEAo</t>
-        </is>
-      </c>
-      <c r="J866" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1GhJG6uEjo</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -35268,34 +35260,34 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>耳语</t>
+          <t>My Jealousy</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
       <c r="D867" t="inlineStr">
         <is>
-          <t>锦零</t>
+          <t>3rd Coast</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16，2026/06/17，2026/06/25，2026/09/21</t>
         </is>
       </c>
       <c r="F867" t="inlineStr"/>
       <c r="G867" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
         <is>
-          <t>BV1GhJG6uEjo</t>
+          <t>BV1DzjT62EHE，BV1bHLR6rEFz</t>
         </is>
       </c>
       <c r="J867" t="inlineStr"/>
@@ -35308,34 +35300,34 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>My Jealousy</t>
+          <t>明年今日</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
-          <t>3rd Coast</t>
+          <t>陈奕迅</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>2026/06/16，2026/06/17，2026/06/25，2026/09/21</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="F868" t="inlineStr"/>
       <c r="G868" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>粤语</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>BV1DzjT62EHE，BV1bHLR6rEFz</t>
+          <t>BV1r4jw6nEZE</t>
         </is>
       </c>
       <c r="J868" t="inlineStr"/>
@@ -35348,37 +35340,41 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>明年今日</t>
+          <t>City Hunter 〜愛よ消えないで〜</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>陈奕迅</t>
+          <t>小比類巻かほる</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/20，2026/08/23</t>
         </is>
       </c>
       <c r="F869" t="inlineStr"/>
       <c r="G869" t="inlineStr">
         <is>
-          <t>粤语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
         <is>
-          <t>BV1r4jw6nEZE</t>
-        </is>
-      </c>
-      <c r="J869" t="inlineStr"/>
+          <t>BV19Gjb6yEgK</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>动漫</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -35388,41 +35384,37 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>City Hunter 〜愛よ消えないで〜</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>
       <c r="D870" t="inlineStr">
         <is>
-          <t>小比類巻かほる</t>
+          <t>林俊杰</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>2026/06/20，2026/08/23</t>
+          <t>2026/06/20</t>
         </is>
       </c>
       <c r="F870" t="inlineStr"/>
       <c r="G870" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
         <is>
-          <t>BV19Gjb6yEgK</t>
-        </is>
-      </c>
-      <c r="J870" t="inlineStr">
-        <is>
-          <t>动漫</t>
-        </is>
-      </c>
+          <t>BV1XGjb6yEbo</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -35432,18 +35424,18 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>三人游</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>林俊杰</t>
+          <t>方大同</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>2026/06/20</t>
+          <t>2026/06/20，2026/06/30，2026/09/27，2026/10/19</t>
         </is>
       </c>
       <c r="F871" t="inlineStr"/>
@@ -35454,12 +35446,12 @@
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
         <is>
-          <t>BV1XGjb6yEbo</t>
+          <t>BV1QLjb6kEJz</t>
         </is>
       </c>
       <c r="J871" t="inlineStr"/>
@@ -35472,18 +35464,18 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>三人游</t>
+          <t>想自由</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
-          <t>方大同</t>
+          <t>林宥嘉</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>2026/06/20，2026/06/30，2026/09/27</t>
+          <t>2026/06/25，2026/07/09，2026/07/18，2026/07/31，2026/08/25，2026/10/25，2026/10/25</t>
         </is>
       </c>
       <c r="F872" t="inlineStr"/>
@@ -35494,12 +35486,12 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
         <is>
-          <t>BV1QLjb6kEJz</t>
+          <t>BV1qq7h6FEBT</t>
         </is>
       </c>
       <c r="J872" t="inlineStr"/>
@@ -35512,18 +35504,18 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>想自由</t>
+          <t>小小虫</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>林宥嘉</t>
+          <t>方大同</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>2026/06/25，2026/07/09，2026/07/18，2026/07/31，2026/08/25</t>
+          <t>2026/06/25，2026/08/01，2026/08/11，2026/09/27</t>
         </is>
       </c>
       <c r="F873" t="inlineStr"/>
@@ -35534,12 +35526,12 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
         <is>
-          <t>BV1qq7h6FEBT</t>
+          <t>BV1Z9786bEfa</t>
         </is>
       </c>
       <c r="J873" t="inlineStr"/>
@@ -35552,34 +35544,38 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>小小虫</t>
-        </is>
-      </c>
-      <c r="C874" t="inlineStr"/>
+          <t>눈,코,입</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>眼，鼻，嘴</t>
+        </is>
+      </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>方大同</t>
+          <t>TAEYANG</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>2026/06/25，2026/08/01，2026/08/11，2026/09/27</t>
+          <t>2026/06/29，2026/07/28</t>
         </is>
       </c>
       <c r="F874" t="inlineStr"/>
       <c r="G874" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>BV1Z9786bEfa</t>
+          <t>BV1mAKX6kEg8</t>
         </is>
       </c>
       <c r="J874" t="inlineStr"/>
@@ -35592,38 +35588,34 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>눈,코,입</t>
-        </is>
-      </c>
-      <c r="C875" t="inlineStr">
-        <is>
-          <t>眼，鼻，嘴</t>
-        </is>
-      </c>
+          <t>海屿你</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr"/>
       <c r="D875" t="inlineStr">
         <is>
-          <t>TAEYANG</t>
+          <t>马也_Crabbit</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>2026/06/29，2026/07/28</t>
+          <t>2026/07/05，2026/07/07，2026/07/17，2026/09/23，2026/10/13</t>
         </is>
       </c>
       <c r="F875" t="inlineStr"/>
       <c r="G875" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
         <is>
-          <t>BV1mAKX6kEg8</t>
+          <t>BV1ZoTC6BELe</t>
         </is>
       </c>
       <c r="J875" t="inlineStr"/>
@@ -35636,18 +35628,18 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>海屿你</t>
+          <t>辞职信</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
-          <t>马也_Crabbit</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>2026/07/05，2026/07/07，2026/07/17，2026/09/23，2026/10/13</t>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11，2026/10/01，2026/10/07，2026/10/10，2026/10/15，2026/10/18，2026/10/25</t>
         </is>
       </c>
       <c r="F876" t="inlineStr"/>
@@ -35658,12 +35650,12 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
         <is>
-          <t>BV1ZoTC6BELe</t>
+          <t>BV19x3P6cEPV</t>
         </is>
       </c>
       <c r="J876" t="inlineStr"/>
@@ -35676,18 +35668,18 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>辞职信</t>
+          <t>定玄</t>
         </is>
       </c>
       <c r="C877" t="inlineStr"/>
       <c r="D877" t="inlineStr">
         <is>
-          <t>ChiliChill</t>
+          <t>鸣潮先约电台/黄霄雲/杨秉音</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11，2026/08/18，2026/08/23，2026/08/25，2026/08/28，2026/09/02，2026/09/11，2026/10/01，2026/10/07，2026/10/10，2026/10/15</t>
+          <t>2026/07/17，2026/07/18，2026/07/27，2026/08/02，2026/08/05</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
@@ -35698,15 +35690,19 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
         <is>
-          <t>BV19x3P6cEPV</t>
-        </is>
-      </c>
-      <c r="J877" t="inlineStr"/>
+          <t>BV1Xx3P6cEfK</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>游戏</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -35716,41 +35712,37 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>定玄</t>
+          <t>红日</t>
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
       <c r="D878" t="inlineStr">
         <is>
-          <t>鸣潮先约电台/黄霄雲/杨秉音</t>
+          <t>李克勤</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>2026/07/17，2026/07/18，2026/07/27，2026/08/02，2026/08/05</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="F878" t="inlineStr"/>
       <c r="G878" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>粤语</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>BV1Xx3P6cEfK</t>
-        </is>
-      </c>
-      <c r="J878" t="inlineStr">
-        <is>
-          <t>游戏</t>
-        </is>
-      </c>
+          <t>BV1D43w6QE1L</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -35760,34 +35752,34 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>红日</t>
+          <t>醉后喜欢我</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>李克勤</t>
+          <t>icyball 冰球乐团</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/09/14，2026/10/10，2026/10/15</t>
         </is>
       </c>
       <c r="F879" t="inlineStr"/>
       <c r="G879" t="inlineStr">
         <is>
-          <t>粤语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>BV1D43w6QE1L</t>
+          <t>BV1CU3B6VEPC</t>
         </is>
       </c>
       <c r="J879" t="inlineStr"/>
@@ -35800,37 +35792,41 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>醉后喜欢我</t>
+          <t>NIGHT DANCER</t>
         </is>
       </c>
       <c r="C880" t="inlineStr"/>
       <c r="D880" t="inlineStr">
         <is>
-          <t>icyball 冰球乐团</t>
+          <t>imase</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08，2026/08/28，2026/09/14，2026/10/10，2026/10/15</t>
+          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/09/02，2026/10/09</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
       <c r="G880" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
         <is>
-          <t>BV1CU3B6VEPC</t>
-        </is>
-      </c>
-      <c r="J880" t="inlineStr"/>
+          <t>BV19x3P6cENj</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>动漫</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -35840,41 +35836,37 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>NIGHT DANCER</t>
+          <t>我们没有在一起</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
       <c r="D881" t="inlineStr">
         <is>
-          <t>imase</t>
+          <t>刘若英</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03，2026/09/02，2026/10/09</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="F881" t="inlineStr"/>
       <c r="G881" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
         <is>
-          <t>BV19x3P6cENj</t>
-        </is>
-      </c>
-      <c r="J881" t="inlineStr">
-        <is>
-          <t>动漫</t>
-        </is>
-      </c>
+          <t>BV1g8gX6fEqx</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -35884,18 +35876,18 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>我们没有在一起</t>
+          <t>圈住你</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
       <c r="D882" t="inlineStr">
         <is>
-          <t>刘若英</t>
+          <t>一口甜</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/27，2026/07/31，2026/09/13</t>
         </is>
       </c>
       <c r="F882" t="inlineStr"/>
@@ -35906,12 +35898,12 @@
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
         <is>
-          <t>BV1g8gX6fEqx</t>
+          <t>BV19x3P6cESt</t>
         </is>
       </c>
       <c r="J882" t="inlineStr"/>
@@ -35924,18 +35916,18 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>圈住你</t>
+          <t>蝴蝶泉边</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>
       <c r="D883" t="inlineStr">
         <is>
-          <t>一口甜</t>
+          <t>黄雅莉</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>2026/07/27，2026/07/31，2026/09/13</t>
+          <t>2026/08/02</t>
         </is>
       </c>
       <c r="F883" t="inlineStr"/>
@@ -35946,12 +35938,12 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>BV19x3P6cESt</t>
+          <t>BV1Qm3Z61Exc</t>
         </is>
       </c>
       <c r="J883" t="inlineStr"/>
@@ -35964,18 +35956,18 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>蝴蝶泉边</t>
+          <t>麦恩莉</t>
         </is>
       </c>
       <c r="C884" t="inlineStr"/>
       <c r="D884" t="inlineStr">
         <is>
-          <t>黄雅莉</t>
+          <t>方大同</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>2026/08/02</t>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22，2026/09/27，2026/10/10</t>
         </is>
       </c>
       <c r="F884" t="inlineStr"/>
@@ -35986,12 +35978,12 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
         <is>
-          <t>BV1Qm3Z61Exc</t>
+          <t>BV1BTMo6VELH</t>
         </is>
       </c>
       <c r="J884" t="inlineStr"/>
@@ -36004,18 +35996,18 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>麦恩莉</t>
+          <t>中国人会飞</t>
         </is>
       </c>
       <c r="C885" t="inlineStr"/>
       <c r="D885" t="inlineStr">
         <is>
-          <t>方大同</t>
+          <t>Chalky Wong/揽佬SKAI ISYOURGOD</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11，2026/08/18，2026/08/25，2026/09/08，2026/09/22，2026/09/27，2026/10/10</t>
+          <t>2026/08/05，2026/08/05</t>
         </is>
       </c>
       <c r="F885" t="inlineStr"/>
@@ -36026,12 +36018,12 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
         <is>
-          <t>BV1BTMo6VELH</t>
+          <t>BV1cZMy6DE4V</t>
         </is>
       </c>
       <c r="J885" t="inlineStr"/>
@@ -36044,24 +36036,24 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>中国人会飞</t>
+          <t>Enemy</t>
         </is>
       </c>
       <c r="C886" t="inlineStr"/>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Chalky Wong/揽佬SKAI ISYOURGOD</t>
+          <t>Imagine Dragons/JID/英雄联盟/双城之战</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>2026/08/05，2026/08/05</t>
+          <t>2025/05/03，2026/08/05</t>
         </is>
       </c>
       <c r="F886" t="inlineStr"/>
       <c r="G886" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
@@ -36071,7 +36063,7 @@
       </c>
       <c r="I886" t="inlineStr">
         <is>
-          <t>BV1cZMy6DE4V</t>
+          <t>BV1scGdzVEjo</t>
         </is>
       </c>
       <c r="J886" t="inlineStr"/>
@@ -36084,34 +36076,34 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Enemy</t>
+          <t>悲伤的五个步骤</t>
         </is>
       </c>
       <c r="C887" t="inlineStr"/>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Imagine Dragons/JID/英雄联盟/双城之战</t>
+          <t>艾薇Ivy</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>2025/05/03，2026/08/05</t>
+          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/09/14，2026/09/21，2026/10/05，2026/10/10，2026/10/16，2026/10/21，2026/10/25</t>
         </is>
       </c>
       <c r="F887" t="inlineStr"/>
       <c r="G887" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
         <is>
-          <t>BV1scGdzVEjo</t>
+          <t>BV1oBui6sEzT</t>
         </is>
       </c>
       <c r="J887" t="inlineStr"/>
@@ -36124,18 +36116,18 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>悲伤的五个步骤</t>
+          <t>讨厌</t>
         </is>
       </c>
       <c r="C888" t="inlineStr"/>
       <c r="D888" t="inlineStr">
         <is>
-          <t>艾薇Ivy</t>
+          <t>芮恩</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/08/11，2026/08/18，2026/08/25，2026/09/06，2026/09/11，2026/09/14，2026/09/21，2026/10/05，2026/10/10，2026/10/16</t>
+          <t>2026/08/11，2026/09/06，2026/09/27，2026/10/01，2026/10/16</t>
         </is>
       </c>
       <c r="F888" t="inlineStr"/>
@@ -36146,12 +36138,12 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
         <is>
-          <t>BV1oBui6sEzT</t>
+          <t>BV1DQui61EPb</t>
         </is>
       </c>
       <c r="J888" t="inlineStr"/>
@@ -36164,18 +36156,18 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>讨厌</t>
+          <t>迷宫</t>
         </is>
       </c>
       <c r="C889" t="inlineStr"/>
       <c r="D889" t="inlineStr">
         <is>
-          <t>芮恩</t>
+          <t>step.jad依加</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>2026/08/11，2026/09/06，2026/09/27，2026/10/01，2026/10/16</t>
+          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11，2026/09/27，2026/10/10，2026/10/16</t>
         </is>
       </c>
       <c r="F889" t="inlineStr"/>
@@ -36186,12 +36178,12 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
         <is>
-          <t>BV1DQui61EPb</t>
+          <t>BV1UL836dEFE</t>
         </is>
       </c>
       <c r="J889" t="inlineStr"/>
@@ -36204,18 +36196,18 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>迷宫</t>
+          <t>爱你但说不出口</t>
         </is>
       </c>
       <c r="C890" t="inlineStr"/>
       <c r="D890" t="inlineStr">
         <is>
-          <t>step.jad依加</t>
+          <t>Karencici</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/08/19，2026/08/23，2026/08/30，2026/09/11，2026/09/27，2026/10/10，2026/10/16</t>
+          <t>2026/08/18，2026/09/27，2026/10/16</t>
         </is>
       </c>
       <c r="F890" t="inlineStr"/>
@@ -36226,12 +36218,12 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
         <is>
-          <t>BV1UL836dEFE</t>
+          <t>BV1e1836KEbJ</t>
         </is>
       </c>
       <c r="J890" t="inlineStr"/>
@@ -36244,18 +36236,18 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>爱你但说不出口</t>
+          <t>写一首歌April 5,1969</t>
         </is>
       </c>
       <c r="C891" t="inlineStr"/>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Karencici</t>
+          <t>顺子</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>2026/08/18，2026/09/27，2026/10/16</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="F891" t="inlineStr"/>
@@ -36266,12 +36258,12 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
         <is>
-          <t>BV1e1836KEbJ</t>
+          <t>BV1xw8G6sEvA</t>
         </is>
       </c>
       <c r="J891" t="inlineStr"/>
@@ -36284,13 +36276,13 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>写一首歌April 5,1969</t>
+          <t>Black Sheep</t>
         </is>
       </c>
       <c r="C892" t="inlineStr"/>
       <c r="D892" t="inlineStr">
         <is>
-          <t>顺子</t>
+          <t>Gin Wigmore</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -36301,7 +36293,7 @@
       <c r="F892" t="inlineStr"/>
       <c r="G892" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
@@ -36311,7 +36303,7 @@
       </c>
       <c r="I892" t="inlineStr">
         <is>
-          <t>BV1xw8G6sEvA</t>
+          <t>BV1Ps836DEGr</t>
         </is>
       </c>
       <c r="J892" t="inlineStr"/>
@@ -36324,18 +36316,18 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Black Sheep</t>
+          <t>Get Jinxed</t>
         </is>
       </c>
       <c r="C893" t="inlineStr"/>
       <c r="D893" t="inlineStr">
         <is>
-          <t>Gin Wigmore</t>
+          <t>Agnete Kjolsund</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/19，2026/10/23</t>
         </is>
       </c>
       <c r="F893" t="inlineStr"/>
@@ -36346,12 +36338,12 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>BV1Ps836DEGr</t>
+          <t>BV1t58n6EEBo</t>
         </is>
       </c>
       <c r="J893" t="inlineStr"/>
@@ -36364,18 +36356,22 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Get Jinxed</t>
-        </is>
-      </c>
-      <c r="C894" t="inlineStr"/>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>涅槃</t>
+        </is>
+      </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>Agnete Kjolsund</t>
+          <t>英雄联盟/Cailin Russo/Chrissy Costanza</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/19，2026/08/21，2026/10/23</t>
         </is>
       </c>
       <c r="F894" t="inlineStr"/>
@@ -36386,12 +36382,12 @@
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
         <is>
-          <t>BV1t58n6EEBo</t>
+          <t>BV1zA8B6SEvE</t>
         </is>
       </c>
       <c r="J894" t="inlineStr"/>
@@ -36404,38 +36400,34 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="C895" t="inlineStr">
-        <is>
-          <t>涅槃</t>
-        </is>
-      </c>
+          <t>才二十三</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr"/>
       <c r="D895" t="inlineStr">
         <is>
-          <t>英雄联盟/Cailin Russo/Chrissy Costanza</t>
+          <t>方大同</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>2026/08/19，2026/08/21</t>
+          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21，2026/09/27，2026/10/09，2026/10/13，2026/10/19</t>
         </is>
       </c>
       <c r="F895" t="inlineStr"/>
       <c r="G895" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>BV1zA8B6SEvE</t>
+          <t>BV1Ko886rE7j</t>
         </is>
       </c>
       <c r="J895" t="inlineStr"/>
@@ -36448,18 +36440,18 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>才二十三</t>
+          <t>入秋的第一场雨真让人矫情</t>
         </is>
       </c>
       <c r="C896" t="inlineStr"/>
       <c r="D896" t="inlineStr">
         <is>
-          <t>方大同</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/08/25，2026/09/02，2026/09/11，2026/09/21，2026/09/27，2026/10/09，2026/10/13</t>
+          <t>2026/08/23</t>
         </is>
       </c>
       <c r="F896" t="inlineStr"/>
@@ -36470,12 +36462,12 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>BV1Ko886rE7j</t>
+          <t>BV1cs886YEQS</t>
         </is>
       </c>
       <c r="J896" t="inlineStr"/>
@@ -36488,7 +36480,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>入秋的第一场雨真让人矫情</t>
+          <t>芭蕉夜雨</t>
         </is>
       </c>
       <c r="C897" t="inlineStr"/>
@@ -36499,7 +36491,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>2026/08/23</t>
+          <t>2026/08/23，2026/09/21，2026/09/26，2026/09/29，2026/10/09，2026/10/18，2026/10/25</t>
         </is>
       </c>
       <c r="F897" t="inlineStr"/>
@@ -36510,12 +36502,12 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
         <is>
-          <t>BV1cs886YEQS</t>
+          <t>BV1ns886YEqh</t>
         </is>
       </c>
       <c r="J897" t="inlineStr"/>
@@ -36528,34 +36520,34 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>芭蕉夜雨</t>
+          <t>Summer Vibe</t>
         </is>
       </c>
       <c r="C898" t="inlineStr"/>
       <c r="D898" t="inlineStr">
         <is>
-          <t>ChiliChill</t>
+          <t>Walk off the Earth</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>2026/08/23，2026/09/21，2026/09/26，2026/09/29，2026/10/09</t>
+          <t>2026/08/25</t>
         </is>
       </c>
       <c r="F898" t="inlineStr"/>
       <c r="G898" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
         <is>
-          <t>BV1ns886YEqh</t>
+          <t>BV1mY496eEud</t>
         </is>
       </c>
       <c r="J898" t="inlineStr"/>
@@ -36568,18 +36560,18 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Summer Vibe</t>
+          <t>Love Me Like You Do</t>
         </is>
       </c>
       <c r="C899" t="inlineStr"/>
       <c r="D899" t="inlineStr">
         <is>
-          <t>Walk off the Earth</t>
+          <t>Ellie Goulding</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>2026/08/25</t>
+          <t>2026/08/30，2026/09/11，2026/10/02，2026/10/03</t>
         </is>
       </c>
       <c r="F899" t="inlineStr"/>
@@ -36590,12 +36582,12 @@
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>BV1mY496eEud</t>
+          <t>BV1W2tn6zEBJ，BV12wta6uEUK</t>
         </is>
       </c>
       <c r="J899" t="inlineStr"/>
@@ -36608,18 +36600,18 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Love Me Like You Do</t>
+          <t>Honeymoon Avenue</t>
         </is>
       </c>
       <c r="C900" t="inlineStr"/>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Ellie Goulding</t>
+          <t>Ariana Grande</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/09/11，2026/10/02，2026/10/03</t>
+          <t>2026/08/30，2026/10/13</t>
         </is>
       </c>
       <c r="F900" t="inlineStr"/>
@@ -36630,12 +36622,12 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
         <is>
-          <t>BV1W2tn6zEBJ，BV12wta6uEUK</t>
+          <t>BV1WhtW67ECn，BV1k8th6cEpk</t>
         </is>
       </c>
       <c r="J900" t="inlineStr"/>
@@ -36648,18 +36640,18 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Honeymoon Avenue</t>
+          <t>Tik Tok</t>
         </is>
       </c>
       <c r="C901" t="inlineStr"/>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Ariana Grande</t>
+          <t>Kesha</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/10/13</t>
+          <t>2026/08/30，2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F901" t="inlineStr"/>
@@ -36670,12 +36662,12 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>BV1WhtW67ECn，BV1k8th6cEpk</t>
+          <t>BV1wvtW6yE7K，BV1w8th6wERB</t>
         </is>
       </c>
       <c r="J901" t="inlineStr"/>
@@ -36688,18 +36680,18 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Tik Tok</t>
+          <t>Last Friday Night (T.G.I.F.)</t>
         </is>
       </c>
       <c r="C902" t="inlineStr"/>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Kesha</t>
+          <t>Katy Perry</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/08/30，2026/10/03</t>
+          <t>2026/08/30，2026/10/03</t>
         </is>
       </c>
       <c r="F902" t="inlineStr"/>
@@ -36710,12 +36702,12 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>BV1wvtW6yE7K，BV1w8th6wERB</t>
+          <t>BV12Hth6iEup</t>
         </is>
       </c>
       <c r="J902" t="inlineStr"/>
@@ -36728,18 +36720,18 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Last Friday Night (T.G.I.F.)</t>
+          <t>All About That Bass</t>
         </is>
       </c>
       <c r="C903" t="inlineStr"/>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Katy Perry</t>
+          <t>Meghan Trainor</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/10/03</t>
+          <t>2026/08/30，2026/09/02，2026/10/16</t>
         </is>
       </c>
       <c r="F903" t="inlineStr"/>
@@ -36750,12 +36742,12 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>BV12Hth6iEup</t>
+          <t>BV14Hth6qEwH，BV1y4th6AEz2</t>
         </is>
       </c>
       <c r="J903" t="inlineStr"/>
@@ -36768,18 +36760,22 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>All About That Bass</t>
-        </is>
-      </c>
-      <c r="C904" t="inlineStr"/>
+          <t>California King Bed</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>加州王床</t>
+        </is>
+      </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>Meghan Trainor</t>
+          <t>Rihanna</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>2026/08/30，2026/09/02，2026/10/16</t>
+          <t>2026/09/02</t>
         </is>
       </c>
       <c r="F904" t="inlineStr"/>
@@ -36790,12 +36786,12 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>BV14Hth6qEwH，BV1y4th6AEz2</t>
+          <t>BV1oetS6gEcN，BV15eto6sEMB</t>
         </is>
       </c>
       <c r="J904" t="inlineStr"/>
@@ -36808,38 +36804,34 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>California King Bed</t>
-        </is>
-      </c>
-      <c r="C905" t="inlineStr">
-        <is>
-          <t>加州王床</t>
-        </is>
-      </c>
+          <t>社畜少女</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr"/>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Rihanna</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>2026/09/02</t>
+          <t>2026/09/11，2026/10/06，2026/10/09，2026/10/19</t>
         </is>
       </c>
       <c r="F905" t="inlineStr"/>
       <c r="G905" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>BV1oetS6gEcN，BV15eto6sEMB</t>
+          <t>BV1cJY26QEG7</t>
         </is>
       </c>
       <c r="J905" t="inlineStr"/>
@@ -36852,18 +36844,18 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>社畜少女</t>
+          <t>还是会寂寞</t>
         </is>
       </c>
       <c r="C906" t="inlineStr"/>
       <c r="D906" t="inlineStr">
         <is>
-          <t>ChiliChill</t>
+          <t>陈绮贞</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>2026/09/11，2026/10/06，2026/10/09</t>
+          <t>2026/09/06，2026/09/11，2026/09/16，2026/10/11，2026/10/14</t>
         </is>
       </c>
       <c r="F906" t="inlineStr"/>
@@ -36874,12 +36866,12 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
         <is>
-          <t>BV1cJY26QEG7</t>
+          <t>BV13fY16KELD</t>
         </is>
       </c>
       <c r="J906" t="inlineStr"/>
@@ -36892,34 +36884,38 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>还是会寂寞</t>
-        </is>
-      </c>
-      <c r="C907" t="inlineStr"/>
+          <t>粛聖!! ロリ神レクイエム</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>肃静！萝莉神的镇魂曲</t>
+        </is>
+      </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>陈绮贞</t>
+          <t>しぐれうい</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>2026/09/06，2026/09/11，2026/09/16，2026/10/11，2026/10/14</t>
+          <t>2026/09/13，2026/09/21</t>
         </is>
       </c>
       <c r="F907" t="inlineStr"/>
       <c r="G907" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
         <is>
-          <t>BV13fY16KELD</t>
+          <t>BV1FwY16LEko</t>
         </is>
       </c>
       <c r="J907" t="inlineStr"/>
@@ -36932,38 +36928,34 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>粛聖!! ロリ神レクイエム</t>
-        </is>
-      </c>
-      <c r="C908" t="inlineStr">
-        <is>
-          <t>肃静！萝莉神的镇魂曲</t>
-        </is>
-      </c>
+          <t>willow</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr"/>
       <c r="D908" t="inlineStr">
         <is>
-          <t>しぐれうい</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>2026/09/13，2026/09/21</t>
+          <t>2026/09/04，2026/09/16，2026/09/22</t>
         </is>
       </c>
       <c r="F908" t="inlineStr"/>
       <c r="G908" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
         <is>
-          <t>BV1FwY16LEko</t>
+          <t>BV1Setr6MEBW</t>
         </is>
       </c>
       <c r="J908" t="inlineStr"/>
@@ -36976,18 +36968,22 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>willow</t>
-        </is>
-      </c>
-      <c r="C909" t="inlineStr"/>
+          <t>Better Dig Two</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>最好挖两座坟</t>
+        </is>
+      </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>The Band Perry</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>2026/09/04，2026/09/16，2026/09/22</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="F909" t="inlineStr"/>
@@ -36998,12 +36994,12 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
         <is>
-          <t>BV1Setr6MEBW</t>
+          <t>BV1Pjen6QEeh</t>
         </is>
       </c>
       <c r="J909" t="inlineStr"/>
@@ -37016,22 +37012,18 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Better Dig Two</t>
-        </is>
-      </c>
-      <c r="C910" t="inlineStr">
-        <is>
-          <t>最好挖两座坟</t>
-        </is>
-      </c>
+          <t>Let Her Go</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr"/>
       <c r="D910" t="inlineStr">
         <is>
-          <t>The Band Perry</t>
+          <t>Passenger</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="F910" t="inlineStr"/>
@@ -37047,7 +37039,7 @@
       </c>
       <c r="I910" t="inlineStr">
         <is>
-          <t>BV1Pjen6QEeh</t>
+          <t>BV1MBeA6CEhH</t>
         </is>
       </c>
       <c r="J910" t="inlineStr"/>
@@ -37060,13 +37052,13 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Let Her Go</t>
+          <t>Say Something</t>
         </is>
       </c>
       <c r="C911" t="inlineStr"/>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Passenger</t>
+          <t>A Great Big World</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -37087,7 +37079,7 @@
       </c>
       <c r="I911" t="inlineStr">
         <is>
-          <t>BV1MBeA6CEhH</t>
+          <t>BV1d7eg6gEGu</t>
         </is>
       </c>
       <c r="J911" t="inlineStr"/>
@@ -37100,24 +37092,24 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Say Something</t>
+          <t>U&amp;I</t>
         </is>
       </c>
       <c r="C912" t="inlineStr"/>
       <c r="D912" t="inlineStr">
         <is>
-          <t>A Great Big World</t>
+          <t>放課後ティータイム</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/21</t>
         </is>
       </c>
       <c r="F912" t="inlineStr"/>
       <c r="G912" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>日语</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
@@ -37127,7 +37119,7 @@
       </c>
       <c r="I912" t="inlineStr">
         <is>
-          <t>BV1d7eg6gEGu</t>
+          <t>BV1mzht6MEds</t>
         </is>
       </c>
       <c r="J912" t="inlineStr"/>
@@ -37140,34 +37132,34 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>U&amp;I</t>
+          <t>天天</t>
         </is>
       </c>
       <c r="C913" t="inlineStr"/>
       <c r="D913" t="inlineStr">
         <is>
-          <t>放課後ティータイム</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>2026/09/21</t>
+          <t>2026/09/21，2026/10/13</t>
         </is>
       </c>
       <c r="F913" t="inlineStr"/>
       <c r="G913" t="inlineStr">
         <is>
-          <t>日语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
         <is>
-          <t>BV1mzht6MEds</t>
+          <t>BV1kThz6fEeg</t>
         </is>
       </c>
       <c r="J913" t="inlineStr"/>
@@ -37180,18 +37172,18 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>天天</t>
+          <t>荷塘月色</t>
         </is>
       </c>
       <c r="C914" t="inlineStr"/>
       <c r="D914" t="inlineStr">
         <is>
-          <t>陶喆</t>
+          <t>凤凰传奇</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>2026/09/21，2026/10/13</t>
+          <t>2026/09/26</t>
         </is>
       </c>
       <c r="F914" t="inlineStr"/>
@@ -37202,12 +37194,12 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
         <is>
-          <t>BV1kThz6fEeg</t>
+          <t>BV1S7ax6BEWj</t>
         </is>
       </c>
       <c r="J914" t="inlineStr"/>
@@ -37220,18 +37212,18 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>荷塘月色</t>
+          <t>二十二</t>
         </is>
       </c>
       <c r="C915" t="inlineStr"/>
       <c r="D915" t="inlineStr">
         <is>
-          <t>凤凰传奇</t>
+          <t>陶喆</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>2026/09/26</t>
+          <t>2026/09/27，2026/10/19</t>
         </is>
       </c>
       <c r="F915" t="inlineStr"/>
@@ -37242,12 +37234,12 @@
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
         <is>
-          <t>BV1S7ax6BEWj</t>
+          <t>BV1RWa36MEU2</t>
         </is>
       </c>
       <c r="J915" t="inlineStr"/>
@@ -37260,13 +37252,13 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>二十二</t>
+          <t>American Boy</t>
         </is>
       </c>
       <c r="C916" t="inlineStr"/>
       <c r="D916" t="inlineStr">
         <is>
-          <t>陶喆</t>
+          <t>Estelle/Kanye West</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -37277,7 +37269,7 @@
       <c r="F916" t="inlineStr"/>
       <c r="G916" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H916" t="inlineStr">
@@ -37287,7 +37279,7 @@
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>BV1RWa36MEU2</t>
+          <t>BV1BLa36CEdd</t>
         </is>
       </c>
       <c r="J916" t="inlineStr"/>
@@ -37300,18 +37292,18 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>American Boy</t>
+          <t>What Do You Mean?</t>
         </is>
       </c>
       <c r="C917" t="inlineStr"/>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Estelle/Kanye West</t>
+          <t>Justin Bieber</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>2026/09/27</t>
+          <t>2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F917" t="inlineStr"/>
@@ -37322,12 +37314,12 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
         <is>
-          <t>BV1BLa36CEdd</t>
+          <t>BV1RAaW6gECq</t>
         </is>
       </c>
       <c r="J917" t="inlineStr"/>
@@ -37340,18 +37332,18 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>What Do You Mean?</t>
+          <t>Say So</t>
         </is>
       </c>
       <c r="C918" t="inlineStr"/>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Justin Bieber</t>
+          <t>Doja Cat/Nicki Minaj</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>2026/09/29，2026/10/03</t>
+          <t>2026/09/29，2026/10/23</t>
         </is>
       </c>
       <c r="F918" t="inlineStr"/>
@@ -37367,7 +37359,7 @@
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>BV1RAaW6gECq</t>
+          <t>BV1mnaW6ZEKs</t>
         </is>
       </c>
       <c r="J918" t="inlineStr"/>
@@ -37380,18 +37372,18 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Say So</t>
+          <t>STAY</t>
         </is>
       </c>
       <c r="C919" t="inlineStr"/>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Doja Cat/Nicki Minaj</t>
+          <t>The Kid LAROI/Justin Bieber</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F919" t="inlineStr"/>
@@ -37402,12 +37394,12 @@
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>BV1mnaW6ZEKs</t>
+          <t>BV1fRap61EJi</t>
         </is>
       </c>
       <c r="J919" t="inlineStr"/>
@@ -37420,13 +37412,13 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>STAY</t>
+          <t>Galway Girl</t>
         </is>
       </c>
       <c r="C920" t="inlineStr"/>
       <c r="D920" t="inlineStr">
         <is>
-          <t>The Kid LAROI/Justin Bieber</t>
+          <t>Ed Sheeran</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -37447,7 +37439,7 @@
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>BV1fRap61EJi</t>
+          <t>BV1mnaW6ZENW</t>
         </is>
       </c>
       <c r="J920" t="inlineStr"/>
@@ -37460,13 +37452,13 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Galway Girl</t>
+          <t>Stitches</t>
         </is>
       </c>
       <c r="C921" t="inlineStr"/>
       <c r="D921" t="inlineStr">
         <is>
-          <t>Ed Sheeran</t>
+          <t>Shawn Mendes</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -37487,7 +37479,7 @@
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>BV1mnaW6ZENW</t>
+          <t>BV19KaW6MEw2</t>
         </is>
       </c>
       <c r="J921" t="inlineStr"/>
@@ -37500,18 +37492,18 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Stitches</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="C922" t="inlineStr"/>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Shawn Mendes</t>
+          <t>Charlie Puth</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/09/29，2026/10/03</t>
         </is>
       </c>
       <c r="F922" t="inlineStr"/>
@@ -37522,12 +37514,12 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>BV19KaW6MEw2</t>
+          <t>BV1aQaW6qEXq</t>
         </is>
       </c>
       <c r="J922" t="inlineStr"/>
@@ -37540,34 +37532,34 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>当你穿过我的身体</t>
         </is>
       </c>
       <c r="C923" t="inlineStr"/>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Charlie Puth</t>
+          <t>汉堡黄</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>2026/09/29，2026/10/03</t>
+          <t>2026/09/29，2026/10/02，2026/10/05，2026/10/14</t>
         </is>
       </c>
       <c r="F923" t="inlineStr"/>
       <c r="G923" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
         <is>
-          <t>BV1aQaW6qEXq</t>
+          <t>BV1MhaX6yEgC</t>
         </is>
       </c>
       <c r="J923" t="inlineStr"/>
@@ -37580,34 +37572,34 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>当你穿过我的身体</t>
+          <t>Lights</t>
         </is>
       </c>
       <c r="C924" t="inlineStr"/>
       <c r="D924" t="inlineStr">
         <is>
-          <t>汉堡黄</t>
+          <t>Ellie Goulding</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>2026/09/29，2026/10/02，2026/10/05，2026/10/14</t>
+          <t>2026/10/02，2026/10/03</t>
         </is>
       </c>
       <c r="F924" t="inlineStr"/>
       <c r="G924" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>英语</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
         <is>
-          <t>BV1MhaX6yEgC</t>
+          <t>BV118H86SE3N，BV1SFHB6VETv</t>
         </is>
       </c>
       <c r="J924" t="inlineStr"/>
@@ -37620,7 +37612,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Lights</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="C925" t="inlineStr"/>
@@ -37647,7 +37639,7 @@
       </c>
       <c r="I925" t="inlineStr">
         <is>
-          <t>BV118H86SE3N，BV1SFHB6VETv</t>
+          <t>BV1vDH86KEfx，BV1TAHB63EY6</t>
         </is>
       </c>
       <c r="J925" t="inlineStr"/>
@@ -37660,18 +37652,18 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Beauty And A Beat</t>
         </is>
       </c>
       <c r="C926" t="inlineStr"/>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Ellie Goulding</t>
+          <t>Justin Bieber/Nicki Minaj</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>2026/10/02，2026/10/03</t>
+          <t>2026/10/03</t>
         </is>
       </c>
       <c r="F926" t="inlineStr"/>
@@ -37682,12 +37674,12 @@
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>BV1vDH86KEfx，BV1TAHB63EY6</t>
+          <t>BV1uZHq6yEpC</t>
         </is>
       </c>
       <c r="J926" t="inlineStr"/>
@@ -37700,13 +37692,13 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Beauty And A Beat</t>
+          <t>Ass Back Home</t>
         </is>
       </c>
       <c r="C927" t="inlineStr"/>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Justin Bieber/Nicki Minaj</t>
+          <t>Gym Class Heroes/Neon Hitch</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -37727,7 +37719,7 @@
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>BV1uZHq6yEpC</t>
+          <t>BV1uZHq6yEor</t>
         </is>
       </c>
       <c r="J927" t="inlineStr"/>
@@ -37740,13 +37732,13 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>Ass Back Home</t>
+          <t>Maps</t>
         </is>
       </c>
       <c r="C928" t="inlineStr"/>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Gym Class Heroes/Neon Hitch</t>
+          <t>Maroon 5</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -37767,7 +37759,7 @@
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>BV1uZHq6yEor</t>
+          <t>BV1uZHq6yEDC</t>
         </is>
       </c>
       <c r="J928" t="inlineStr"/>
@@ -37780,13 +37772,13 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Maps</t>
+          <t>Just Dance</t>
         </is>
       </c>
       <c r="C929" t="inlineStr"/>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Maroon 5</t>
+          <t>Lady Gaga/Colby O'Donis/RedOne</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -37807,7 +37799,7 @@
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>BV1uZHq6yEDC</t>
+          <t>BV1TAHB63Epz</t>
         </is>
       </c>
       <c r="J929" t="inlineStr"/>
@@ -37820,13 +37812,13 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Just Dance</t>
+          <t>We Found Love</t>
         </is>
       </c>
       <c r="C930" t="inlineStr"/>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Lady Gaga/Colby O'Donis/RedOne</t>
+          <t>Rihanna/Calvin Harris</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -37847,7 +37839,7 @@
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>BV1TAHB63Epz</t>
+          <t>BV1TAHB63Ehs</t>
         </is>
       </c>
       <c r="J930" t="inlineStr"/>
@@ -37860,13 +37852,13 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>We Found Love</t>
+          <t>Hit The Lights</t>
         </is>
       </c>
       <c r="C931" t="inlineStr"/>
       <c r="D931" t="inlineStr">
         <is>
-          <t>Rihanna/Calvin Harris</t>
+          <t>Selena Gomez &amp; The Scene</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -37887,7 +37879,7 @@
       </c>
       <c r="I931" t="inlineStr">
         <is>
-          <t>BV1TAHB63Ehs</t>
+          <t>BV1TAHB63EGB</t>
         </is>
       </c>
       <c r="J931" t="inlineStr"/>
@@ -37900,24 +37892,28 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>Hit The Lights</t>
-        </is>
-      </c>
-      <c r="C932" t="inlineStr"/>
+          <t>Love wins all</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>爱胜过一切</t>
+        </is>
+      </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>Selena Gomez &amp; The Scene</t>
+          <t>IU</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>2026/10/03</t>
+          <t>2026/10/05</t>
         </is>
       </c>
       <c r="F932" t="inlineStr"/>
       <c r="G932" t="inlineStr">
         <is>
-          <t>英语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
@@ -37927,7 +37923,7 @@
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>BV1TAHB63EGB</t>
+          <t>BV1SjHt6DEsu</t>
         </is>
       </c>
       <c r="J932" t="inlineStr"/>
@@ -37940,28 +37936,24 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Love wins all</t>
-        </is>
-      </c>
-      <c r="C933" t="inlineStr">
-        <is>
-          <t>爱胜过一切</t>
-        </is>
-      </c>
+          <t>娱乐人生</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr"/>
       <c r="D933" t="inlineStr">
         <is>
-          <t>IU</t>
+          <t>陈蕾</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>2026/10/05</t>
+          <t>2026/10/06</t>
         </is>
       </c>
       <c r="F933" t="inlineStr"/>
       <c r="G933" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>粤语</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -37971,7 +37963,7 @@
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>BV1SjHt6DEsu</t>
+          <t>BV1GkpN6bEaa</t>
         </is>
       </c>
       <c r="J933" t="inlineStr"/>
@@ -37984,13 +37976,13 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>娱乐人生</t>
+          <t>让她降落</t>
         </is>
       </c>
       <c r="C934" t="inlineStr"/>
       <c r="D934" t="inlineStr">
         <is>
-          <t>陈蕾</t>
+          <t>何璐</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -38001,7 +37993,7 @@
       <c r="F934" t="inlineStr"/>
       <c r="G934" t="inlineStr">
         <is>
-          <t>粤语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -38011,7 +38003,7 @@
       </c>
       <c r="I934" t="inlineStr">
         <is>
-          <t>BV1GkpN6bEaa</t>
+          <t>BV1GkpN6bE8n</t>
         </is>
       </c>
       <c r="J934" t="inlineStr"/>
@@ -38024,13 +38016,13 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>让她降落</t>
+          <t>你若成风</t>
         </is>
       </c>
       <c r="C935" t="inlineStr"/>
       <c r="D935" t="inlineStr">
         <is>
-          <t>何璐</t>
+          <t>许嵩/莫诗旎</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -38051,7 +38043,7 @@
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>BV1GkpN6bE8n</t>
+          <t>BV1HwpK61Ega</t>
         </is>
       </c>
       <c r="J935" t="inlineStr"/>
@@ -38064,34 +38056,34 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>你若成风</t>
+          <t>0+0</t>
         </is>
       </c>
       <c r="C936" t="inlineStr"/>
       <c r="D936" t="inlineStr">
         <is>
-          <t>许嵩/莫诗旎</t>
+          <t>한로로</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>2026/10/06</t>
+          <t>2026/10/09，2026/10/10，2026/10/14，2026/10/21</t>
         </is>
       </c>
       <c r="F936" t="inlineStr"/>
       <c r="G936" t="inlineStr">
         <is>
-          <t>华语</t>
+          <t>韩语</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>BV1HwpK61Ega</t>
+          <t>BV1kWp86mE6M</t>
         </is>
       </c>
       <c r="J936" t="inlineStr"/>
@@ -38104,37 +38096,277 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>0+0</t>
+          <t>酸的。</t>
         </is>
       </c>
       <c r="C937" t="inlineStr"/>
       <c r="D937" t="inlineStr">
         <is>
-          <t>한로로</t>
+          <t>ChiliChill</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>2026/10/09，2026/10/10，2026/10/14</t>
+          <t>2026/10/19</t>
         </is>
       </c>
       <c r="F937" t="inlineStr"/>
       <c r="G937" t="inlineStr">
         <is>
-          <t>韩语</t>
+          <t>华语</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
         <is>
-          <t>BV1kWp86mE6M</t>
+          <t>BV1zYJo61EQ8</t>
         </is>
       </c>
       <c r="J937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>娃娃脸</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr"/>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>后弦</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>2026/10/21</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>BV19znB6QEcr</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>挥着翅膀的女孩</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr"/>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>容祖儿</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>2026/10/21</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>BV1PEnB6TESo</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>将军令</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr"/>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>吴克群</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>2026/10/21</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>BV1ozn668ErA</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>那些年</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr"/>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>胡夏</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>2026/10/21</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>BV1Zzn668E3X</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>舍不得</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr"/>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>弦子</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>2026/10/22</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>BV1Tmnp6wEXp</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Baby don't cry</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr"/>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>张钰琪</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>BV1GCnf66E4Z</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
